--- a/reports/2026-09-24.xlsx
+++ b/reports/2026-09-24.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30513"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EF303241-DF76-F147-8AED-0A1BF5BC7BA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="20730" windowHeight="11760"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="20730" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRC(9)" sheetId="1" r:id="rId1"/>
@@ -15,7 +16,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">'DRC(9)'!$A$1:$R$96</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">Loading!$A$1:$AE$56</definedName>
   </definedNames>
-  <calcPr calcId="125725"/>
+  <calcPr calcId="191028"/>
   <fileRecoveryPr autoRecover="0"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -922,7 +923,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="8">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="164" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
@@ -933,7 +934,7 @@
     <numFmt numFmtId="169" formatCode="0.0"/>
     <numFmt numFmtId="170" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="107">
+  <fonts count="107" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -3523,45 +3524,391 @@
     <xf numFmtId="2" fontId="25" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="45" fillId="18" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="45" fillId="18" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="43" fillId="10" borderId="66" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="43" fillId="10" borderId="64" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="43" fillId="10" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="43" fillId="10" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="43" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="10" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="10" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="10" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="10" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="18" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="18" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="18" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="60" fillId="17" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="60" fillId="17" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="60" fillId="17" borderId="59" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="60" fillId="17" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="105" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="105" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="17" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="17" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="17" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="20" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="20" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="20" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="20" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="20" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="20" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="3" fontId="39" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="59" fillId="17" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -3577,30 +3924,6 @@
     <xf numFmtId="3" fontId="44" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="20" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="20" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="20" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="20" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="20" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="20" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="48" fillId="17" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3610,327 +3933,344 @@
     <xf numFmtId="0" fontId="48" fillId="17" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="106" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="23" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="76" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="76" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="76" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="81" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="81" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="81" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="94" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="94" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="91" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="91" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="103" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="103" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="91" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="17" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="17" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="17" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="18" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="18" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="66" fillId="12" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="18" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="66" fillId="12" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="66" fillId="12" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="105" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="105" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="66" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="66" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="60" fillId="17" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="60" fillId="17" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="60" fillId="17" borderId="59" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="60" fillId="17" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="45" fillId="18" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="45" fillId="18" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="43" fillId="10" borderId="66" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="43" fillId="10" borderId="64" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="43" fillId="10" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="43" fillId="10" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="43" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="10" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="10" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="10" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="10" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="104" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3944,12 +4284,6 @@
     <xf numFmtId="14" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="1" fontId="66" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="66" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="17" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3962,15 +4296,6 @@
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="2" fontId="66" fillId="12" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3988,330 +4313,6 @@
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="66" fillId="12" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="66" fillId="12" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="66" fillId="12" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="91" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="91" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="91" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="17" fontId="94" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="17" fontId="94" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="67" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="103" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="103" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="75" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="75" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="75" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="75" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="75" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="75" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="77" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="77" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="77" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="77" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="77" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="77" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="77" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="77" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="77" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="23" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="76" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="76" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="76" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="81" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="81" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="81" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="80" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="80" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="80" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="106" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4410,9 +4411,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -4450,7 +4451,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -4484,6 +4485,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -4518,9 +4520,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -4693,47 +4696,47 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:W190"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="9.03515625" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="1.5703125" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="7.28515625" customWidth="1"/>
-    <col min="3" max="3" width="29.7109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" customWidth="1"/>
-    <col min="6" max="6" width="17.5703125" customWidth="1"/>
-    <col min="7" max="7" width="16.5703125" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" customWidth="1"/>
-    <col min="9" max="9" width="5" customWidth="1"/>
-    <col min="10" max="10" width="12.5703125" style="2" customWidth="1"/>
-    <col min="11" max="11" width="24.7109375" style="2" customWidth="1"/>
+    <col min="1" max="1" width="1.6171875" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="7.28125" customWidth="1"/>
+    <col min="3" max="3" width="29.66796875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="14.83203125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14.29296875" customWidth="1"/>
+    <col min="6" max="6" width="17.52734375" customWidth="1"/>
+    <col min="7" max="7" width="16.5859375" customWidth="1"/>
+    <col min="8" max="8" width="14.83203125" customWidth="1"/>
+    <col min="9" max="9" width="4.98828125" customWidth="1"/>
+    <col min="10" max="10" width="12.5390625" style="2" customWidth="1"/>
+    <col min="11" max="11" width="24.67578125" style="2" customWidth="1"/>
     <col min="12" max="12" width="16.85546875" style="2" customWidth="1"/>
-    <col min="13" max="13" width="16.42578125" style="2" customWidth="1"/>
-    <col min="14" max="14" width="16.28515625" customWidth="1"/>
-    <col min="15" max="15" width="19" customWidth="1"/>
-    <col min="16" max="16" width="20" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" customWidth="1"/>
-    <col min="18" max="18" width="10.5703125" customWidth="1"/>
-    <col min="19" max="19" width="10.28515625" customWidth="1"/>
-    <col min="21" max="21" width="17" customWidth="1"/>
-    <col min="22" max="22" width="15.140625" customWidth="1"/>
-    <col min="23" max="23" width="15.5703125" customWidth="1"/>
+    <col min="13" max="13" width="16.44921875" style="2" customWidth="1"/>
+    <col min="14" max="14" width="16.31640625" customWidth="1"/>
+    <col min="15" max="15" width="19.01171875" customWidth="1"/>
+    <col min="16" max="16" width="19.95703125" customWidth="1"/>
+    <col min="17" max="17" width="14.6953125" customWidth="1"/>
+    <col min="18" max="18" width="10.515625" customWidth="1"/>
+    <col min="19" max="19" width="10.24609375" customWidth="1"/>
+    <col min="21" max="21" width="16.98828125" customWidth="1"/>
+    <col min="22" max="22" width="15.1015625" customWidth="1"/>
+    <col min="23" max="23" width="15.5078125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="30" customHeight="1">
+    <row r="1" spans="1:23" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3"/>
       <c r="B1" s="4"/>
-      <c r="C1" s="419" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="419"/>
-      <c r="E1" s="419"/>
-      <c r="F1" s="419"/>
-      <c r="G1" s="419"/>
-      <c r="H1" s="419"/>
-      <c r="I1" s="419"/>
-      <c r="J1" s="419"/>
+      <c r="C1" s="359" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="359"/>
+      <c r="E1" s="359"/>
+      <c r="F1" s="359"/>
+      <c r="G1" s="359"/>
+      <c r="H1" s="359"/>
+      <c r="I1" s="359"/>
+      <c r="J1" s="359"/>
       <c r="K1" s="67" t="s">
         <v>237</v>
       </c>
@@ -4744,7 +4747,7 @@
       <c r="P1" s="64"/>
       <c r="Q1" s="64"/>
     </row>
-    <row r="2" spans="1:23" ht="15.6" customHeight="1" thickBot="1">
+    <row r="2" spans="1:23" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -4761,14 +4764,14 @@
       <c r="N2" s="7"/>
       <c r="O2" s="7"/>
     </row>
-    <row r="3" spans="1:23" ht="26.25" customHeight="1">
+    <row r="3" spans="1:23" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
       <c r="B3" s="4"/>
-      <c r="C3" s="422" t="s">
+      <c r="C3" s="362" t="s">
         <v>91</v>
       </c>
-      <c r="D3" s="423"/>
-      <c r="E3" s="423"/>
+      <c r="D3" s="363"/>
+      <c r="E3" s="363"/>
       <c r="F3" s="89" t="s">
         <v>1</v>
       </c>
@@ -4781,24 +4784,24 @@
       <c r="I3" s="59" t="s">
         <v>100</v>
       </c>
-      <c r="J3" s="420" t="s">
+      <c r="J3" s="360" t="s">
         <v>101</v>
       </c>
-      <c r="K3" s="420"/>
-      <c r="L3" s="420"/>
-      <c r="M3" s="420"/>
-      <c r="N3" s="420"/>
-      <c r="O3" s="421"/>
-      <c r="P3" s="421"/>
-    </row>
-    <row r="4" spans="1:23" ht="48" customHeight="1">
+      <c r="K3" s="360"/>
+      <c r="L3" s="360"/>
+      <c r="M3" s="360"/>
+      <c r="N3" s="360"/>
+      <c r="O3" s="361"/>
+      <c r="P3" s="361"/>
+    </row>
+    <row r="4" spans="1:23" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
-      <c r="B4" s="362"/>
-      <c r="C4" s="424" t="s">
+      <c r="B4" s="425"/>
+      <c r="C4" s="364" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="425"/>
-      <c r="E4" s="425"/>
+      <c r="D4" s="365"/>
+      <c r="E4" s="365"/>
       <c r="F4" s="91">
         <v>54</v>
       </c>
@@ -4807,10 +4810,10 @@
       </c>
       <c r="H4" s="92"/>
       <c r="I4" s="4"/>
-      <c r="J4" s="429" t="s">
+      <c r="J4" s="372" t="s">
         <v>93</v>
       </c>
-      <c r="K4" s="429"/>
+      <c r="K4" s="372"/>
       <c r="L4" s="280" t="s">
         <v>181</v>
       </c>
@@ -4830,14 +4833,14 @@
       <c r="R4" s="45"/>
       <c r="S4" s="45"/>
     </row>
-    <row r="5" spans="1:23" ht="42.6" customHeight="1">
+    <row r="5" spans="1:23" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
-      <c r="B5" s="362"/>
-      <c r="C5" s="383" t="s">
+      <c r="B5" s="425"/>
+      <c r="C5" s="377" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="384"/>
-      <c r="E5" s="384"/>
+      <c r="D5" s="378"/>
+      <c r="E5" s="378"/>
       <c r="F5" s="91">
         <v>525</v>
       </c>
@@ -4848,10 +4851,10 @@
         <v>7</v>
       </c>
       <c r="I5" s="4"/>
-      <c r="J5" s="434" t="s">
+      <c r="J5" s="379" t="s">
         <v>56</v>
       </c>
-      <c r="K5" s="434"/>
+      <c r="K5" s="379"/>
       <c r="L5" s="289" t="s">
         <v>182</v>
       </c>
@@ -4871,14 +4874,14 @@
       <c r="R5" s="46"/>
       <c r="S5" s="46"/>
     </row>
-    <row r="6" spans="1:23" ht="23.45" customHeight="1">
+    <row r="6" spans="1:23" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3"/>
-      <c r="B6" s="362"/>
-      <c r="C6" s="424" t="s">
+      <c r="B6" s="425"/>
+      <c r="C6" s="364" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="425"/>
-      <c r="E6" s="425"/>
+      <c r="D6" s="365"/>
+      <c r="E6" s="365"/>
       <c r="F6" s="91">
         <v>401</v>
       </c>
@@ -4889,10 +4892,10 @@
         <v>7</v>
       </c>
       <c r="I6" s="4"/>
-      <c r="J6" s="363" t="s">
+      <c r="J6" s="386" t="s">
         <v>9</v>
       </c>
-      <c r="K6" s="363"/>
+      <c r="K6" s="386"/>
       <c r="L6" s="290" t="s">
         <v>183</v>
       </c>
@@ -4912,14 +4915,14 @@
       <c r="R6" s="47"/>
       <c r="S6" s="47"/>
     </row>
-    <row r="7" spans="1:23" ht="22.9" customHeight="1">
+    <row r="7" spans="1:23" ht="22.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3"/>
-      <c r="B7" s="362"/>
-      <c r="C7" s="424" t="s">
+      <c r="B7" s="425"/>
+      <c r="C7" s="364" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="425"/>
-      <c r="E7" s="425"/>
+      <c r="D7" s="365"/>
+      <c r="E7" s="365"/>
       <c r="F7" s="164">
         <f>F4+F5-F6</f>
         <v>178</v>
@@ -4932,10 +4935,10 @@
         <v>7</v>
       </c>
       <c r="I7" s="8"/>
-      <c r="J7" s="440" t="s">
+      <c r="J7" s="385" t="s">
         <v>57</v>
       </c>
-      <c r="K7" s="440"/>
+      <c r="K7" s="385"/>
       <c r="L7" s="291">
         <v>419.32</v>
       </c>
@@ -4955,14 +4958,14 @@
       <c r="R7" s="48"/>
       <c r="S7" s="48"/>
     </row>
-    <row r="8" spans="1:23" ht="26.25" customHeight="1" thickBot="1">
+    <row r="8" spans="1:23" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3"/>
       <c r="B8" s="4"/>
-      <c r="C8" s="432" t="s">
+      <c r="C8" s="375" t="s">
         <v>116</v>
       </c>
-      <c r="D8" s="433"/>
-      <c r="E8" s="433"/>
+      <c r="D8" s="376"/>
+      <c r="E8" s="376"/>
       <c r="F8" s="103">
         <v>35</v>
       </c>
@@ -4971,10 +4974,10 @@
       </c>
       <c r="H8" s="95"/>
       <c r="I8" s="9"/>
-      <c r="J8" s="363" t="s">
+      <c r="J8" s="386" t="s">
         <v>59</v>
       </c>
-      <c r="K8" s="363"/>
+      <c r="K8" s="386"/>
       <c r="L8" s="291">
         <v>49922</v>
       </c>
@@ -4994,17 +4997,17 @@
       <c r="R8" s="48"/>
       <c r="S8" s="48"/>
     </row>
-    <row r="9" spans="1:23" ht="27" customHeight="1" thickBot="1">
+    <row r="9" spans="1:23" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3"/>
       <c r="B9" s="4"/>
       <c r="C9" s="10"/>
       <c r="D9" s="10"/>
       <c r="E9" s="4"/>
       <c r="I9" s="11"/>
-      <c r="J9" s="363" t="s">
+      <c r="J9" s="386" t="s">
         <v>58</v>
       </c>
-      <c r="K9" s="363"/>
+      <c r="K9" s="386"/>
       <c r="L9" s="292">
         <f>49922-L8</f>
         <v>0</v>
@@ -5029,14 +5032,14 @@
       <c r="R9" s="49"/>
       <c r="S9" s="49"/>
     </row>
-    <row r="10" spans="1:23" ht="20.100000000000001" customHeight="1">
+    <row r="10" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
-      <c r="B10" s="362"/>
-      <c r="C10" s="426" t="s">
+      <c r="B10" s="425"/>
+      <c r="C10" s="366" t="s">
         <v>92</v>
       </c>
-      <c r="D10" s="427"/>
-      <c r="E10" s="428"/>
+      <c r="D10" s="367"/>
+      <c r="E10" s="368"/>
       <c r="F10" s="89" t="s">
         <v>1</v>
       </c>
@@ -5047,14 +5050,14 @@
         <v>3</v>
       </c>
       <c r="I10" s="12"/>
-      <c r="J10" s="436" t="s">
+      <c r="J10" s="381" t="s">
         <v>144</v>
       </c>
-      <c r="K10" s="437"/>
-      <c r="L10" s="430">
+      <c r="K10" s="382"/>
+      <c r="L10" s="373">
         <v>14600</v>
       </c>
-      <c r="M10" s="431"/>
+      <c r="M10" s="374"/>
       <c r="N10" s="104"/>
       <c r="O10" s="104"/>
       <c r="P10" s="104"/>
@@ -5062,14 +5065,14 @@
       <c r="R10" s="104"/>
       <c r="S10" s="104"/>
     </row>
-    <row r="11" spans="1:23" ht="23.45" customHeight="1" thickBot="1">
+    <row r="11" spans="1:23" ht="23.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3"/>
-      <c r="B11" s="362"/>
-      <c r="C11" s="338" t="s">
+      <c r="B11" s="425"/>
+      <c r="C11" s="369" t="s">
         <v>4</v>
       </c>
-      <c r="D11" s="339"/>
-      <c r="E11" s="340"/>
+      <c r="D11" s="370"/>
+      <c r="E11" s="371"/>
       <c r="F11" s="69">
         <v>87871</v>
       </c>
@@ -5080,29 +5083,29 @@
         <v>160166.66</v>
       </c>
       <c r="I11" s="12"/>
-      <c r="J11" s="438" t="s">
+      <c r="J11" s="383" t="s">
         <v>60</v>
       </c>
-      <c r="K11" s="439"/>
-      <c r="L11" s="441">
+      <c r="K11" s="384"/>
+      <c r="L11" s="387">
         <v>13500</v>
       </c>
-      <c r="M11" s="442"/>
+      <c r="M11" s="388"/>
       <c r="N11" s="104"/>
       <c r="O11" s="86"/>
-      <c r="P11" s="435"/>
-      <c r="Q11" s="435"/>
-      <c r="R11" s="435"/>
+      <c r="P11" s="380"/>
+      <c r="Q11" s="380"/>
+      <c r="R11" s="380"/>
       <c r="S11" s="107"/>
     </row>
-    <row r="12" spans="1:23" ht="24" thickBot="1">
+    <row r="12" spans="1:23" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3"/>
-      <c r="B12" s="362"/>
-      <c r="C12" s="383" t="s">
+      <c r="B12" s="425"/>
+      <c r="C12" s="377" t="s">
         <v>6</v>
       </c>
-      <c r="D12" s="384"/>
-      <c r="E12" s="384"/>
+      <c r="D12" s="378"/>
+      <c r="E12" s="378"/>
       <c r="F12" s="69">
         <v>27523</v>
       </c>
@@ -5115,10 +5118,10 @@
       <c r="I12" s="12"/>
       <c r="N12" s="105"/>
       <c r="O12" s="86"/>
-      <c r="T12" s="400" t="s">
+      <c r="T12" s="395" t="s">
         <v>187</v>
       </c>
-      <c r="U12" s="400"/>
+      <c r="U12" s="395"/>
       <c r="V12" s="301" t="s">
         <v>49</v>
       </c>
@@ -5126,14 +5129,14 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:23" ht="37.15" customHeight="1" thickBot="1">
+    <row r="13" spans="1:23" ht="37.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3"/>
-      <c r="B13" s="362"/>
-      <c r="C13" s="338" t="s">
+      <c r="B13" s="425"/>
+      <c r="C13" s="369" t="s">
         <v>11</v>
       </c>
-      <c r="D13" s="339"/>
-      <c r="E13" s="340"/>
+      <c r="D13" s="370"/>
+      <c r="E13" s="371"/>
       <c r="F13" s="69">
         <v>29679</v>
       </c>
@@ -5144,20 +5147,20 @@
         <v>23207</v>
       </c>
       <c r="I13" s="12"/>
-      <c r="J13" s="426" t="s">
+      <c r="J13" s="366" t="s">
         <v>175</v>
       </c>
-      <c r="K13" s="427"/>
-      <c r="L13" s="427"/>
-      <c r="M13" s="428"/>
+      <c r="K13" s="367"/>
+      <c r="L13" s="367"/>
+      <c r="M13" s="368"/>
       <c r="N13" s="143" t="s">
         <v>95</v>
       </c>
       <c r="O13" s="106"/>
-      <c r="T13" s="400" t="s">
+      <c r="T13" s="395" t="s">
         <v>188</v>
       </c>
-      <c r="U13" s="400"/>
+      <c r="U13" s="395"/>
       <c r="V13" s="296">
         <f>N19+N20</f>
         <v>136858</v>
@@ -5167,14 +5170,14 @@
         <v>149830</v>
       </c>
     </row>
-    <row r="14" spans="1:23" s="13" customFormat="1" ht="24.6" customHeight="1" thickBot="1">
+    <row r="14" spans="1:23" s="13" customFormat="1" ht="24.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="14"/>
-      <c r="B14" s="364"/>
-      <c r="C14" s="416" t="s">
+      <c r="B14" s="426"/>
+      <c r="C14" s="420" t="s">
         <v>12</v>
       </c>
-      <c r="D14" s="417"/>
-      <c r="E14" s="418"/>
+      <c r="D14" s="421"/>
+      <c r="E14" s="422"/>
       <c r="F14" s="73">
         <f>F11+F12-F13</f>
         <v>85715</v>
@@ -5188,44 +5191,44 @@
         <v>148534.66</v>
       </c>
       <c r="I14" s="15"/>
-      <c r="J14" s="346" t="s">
-        <v>2</v>
-      </c>
-      <c r="K14" s="347"/>
-      <c r="L14" s="347"/>
-      <c r="M14" s="330"/>
+      <c r="J14" s="417" t="s">
+        <v>2</v>
+      </c>
+      <c r="K14" s="418"/>
+      <c r="L14" s="418"/>
+      <c r="M14" s="419"/>
       <c r="N14" s="144"/>
       <c r="O14" s="16"/>
       <c r="P14" s="288"/>
-      <c r="T14" s="414"/>
-      <c r="U14" s="415"/>
+      <c r="T14" s="415"/>
+      <c r="U14" s="416"/>
       <c r="V14" s="299"/>
       <c r="W14" s="299"/>
     </row>
-    <row r="15" spans="1:23" ht="20.100000000000001" customHeight="1" thickBot="1">
+    <row r="15" spans="1:23" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3"/>
-      <c r="B15" s="362"/>
-      <c r="C15" s="394"/>
-      <c r="D15" s="395"/>
-      <c r="E15" s="396"/>
+      <c r="B15" s="425"/>
+      <c r="C15" s="389"/>
+      <c r="D15" s="390"/>
+      <c r="E15" s="391"/>
       <c r="F15" s="75"/>
       <c r="G15" s="76"/>
       <c r="H15" s="76"/>
       <c r="I15" s="17"/>
-      <c r="J15" s="408" t="s">
+      <c r="J15" s="406" t="s">
         <v>137</v>
       </c>
-      <c r="K15" s="409"/>
-      <c r="L15" s="409"/>
-      <c r="M15" s="410"/>
+      <c r="K15" s="407"/>
+      <c r="L15" s="407"/>
+      <c r="M15" s="408"/>
       <c r="N15" s="153">
         <v>58738</v>
       </c>
       <c r="O15" s="18"/>
-      <c r="T15" s="400" t="s">
+      <c r="T15" s="395" t="s">
         <v>231</v>
       </c>
-      <c r="U15" s="400"/>
+      <c r="U15" s="395"/>
       <c r="V15" s="295">
         <f>N31+N32</f>
         <v>8063</v>
@@ -5235,14 +5238,14 @@
         <v>41423</v>
       </c>
     </row>
-    <row r="16" spans="1:23" ht="21">
+    <row r="16" spans="1:23" ht="21" x14ac:dyDescent="0.25">
       <c r="A16" s="3"/>
-      <c r="B16" s="362"/>
-      <c r="C16" s="335" t="s">
+      <c r="B16" s="425"/>
+      <c r="C16" s="409" t="s">
         <v>118</v>
       </c>
-      <c r="D16" s="336"/>
-      <c r="E16" s="337"/>
+      <c r="D16" s="410"/>
+      <c r="E16" s="411"/>
       <c r="F16" s="89" t="s">
         <v>49</v>
       </c>
@@ -5253,12 +5256,12 @@
         <v>3</v>
       </c>
       <c r="I16" s="17"/>
-      <c r="J16" s="411" t="s">
+      <c r="J16" s="412" t="s">
         <v>146</v>
       </c>
-      <c r="K16" s="412"/>
-      <c r="L16" s="412"/>
-      <c r="M16" s="413"/>
+      <c r="K16" s="413"/>
+      <c r="L16" s="413"/>
+      <c r="M16" s="414"/>
       <c r="N16" s="154">
         <v>79332</v>
       </c>
@@ -5266,19 +5269,19 @@
       <c r="Q16" s="65"/>
       <c r="R16" s="65"/>
       <c r="S16" s="65"/>
-      <c r="T16" s="406"/>
-      <c r="U16" s="407"/>
+      <c r="T16" s="401"/>
+      <c r="U16" s="402"/>
       <c r="V16" s="300"/>
       <c r="W16" s="300"/>
     </row>
-    <row r="17" spans="1:23" ht="20.100000000000001" customHeight="1">
+    <row r="17" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3"/>
-      <c r="B17" s="362"/>
-      <c r="C17" s="338" t="s">
+      <c r="B17" s="425"/>
+      <c r="C17" s="369" t="s">
         <v>122</v>
       </c>
-      <c r="D17" s="339"/>
-      <c r="E17" s="340"/>
+      <c r="D17" s="370"/>
+      <c r="E17" s="371"/>
       <c r="F17" s="71">
         <v>63739</v>
       </c>
@@ -5290,12 +5293,12 @@
         <v>59660.52</v>
       </c>
       <c r="I17" s="17"/>
-      <c r="J17" s="397" t="s">
+      <c r="J17" s="392" t="s">
         <v>147</v>
       </c>
-      <c r="K17" s="398"/>
-      <c r="L17" s="398"/>
-      <c r="M17" s="399"/>
+      <c r="K17" s="393"/>
+      <c r="L17" s="393"/>
+      <c r="M17" s="394"/>
       <c r="N17" s="154">
         <v>11760</v>
       </c>
@@ -5303,10 +5306,10 @@
       <c r="Q17" s="65"/>
       <c r="R17" s="65"/>
       <c r="S17" s="65"/>
-      <c r="T17" s="402" t="s">
+      <c r="T17" s="397" t="s">
         <v>232</v>
       </c>
-      <c r="U17" s="403"/>
+      <c r="U17" s="398"/>
       <c r="V17" s="294">
         <f>N41</f>
         <v>0</v>
@@ -5316,14 +5319,14 @@
         <v>79548</v>
       </c>
     </row>
-    <row r="18" spans="1:23" ht="21">
+    <row r="18" spans="1:23" ht="21" x14ac:dyDescent="0.25">
       <c r="A18" s="3"/>
-      <c r="B18" s="362"/>
-      <c r="C18" s="338" t="s">
+      <c r="B18" s="425"/>
+      <c r="C18" s="369" t="s">
         <v>119</v>
       </c>
-      <c r="D18" s="339"/>
-      <c r="E18" s="340"/>
+      <c r="D18" s="370"/>
+      <c r="E18" s="371"/>
       <c r="F18" s="71">
         <v>10941</v>
       </c>
@@ -5334,17 +5337,17 @@
         <v>64403.56</v>
       </c>
       <c r="I18" s="17"/>
-      <c r="J18" s="357" t="s">
+      <c r="J18" s="403" t="s">
         <v>94</v>
       </c>
-      <c r="K18" s="358"/>
-      <c r="L18" s="358"/>
-      <c r="M18" s="359"/>
+      <c r="K18" s="404"/>
+      <c r="L18" s="404"/>
+      <c r="M18" s="405"/>
       <c r="N18" s="150"/>
-      <c r="T18" s="404" t="s">
+      <c r="T18" s="399" t="s">
         <v>5</v>
       </c>
-      <c r="U18" s="405"/>
+      <c r="U18" s="400"/>
       <c r="V18" s="303">
         <f>SUM(V13:V17)</f>
         <v>144921</v>
@@ -5354,14 +5357,14 @@
         <v>270801</v>
       </c>
     </row>
-    <row r="19" spans="1:23" ht="20.100000000000001" customHeight="1">
+    <row r="19" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3"/>
-      <c r="B19" s="362"/>
-      <c r="C19" s="338" t="s">
+      <c r="B19" s="425"/>
+      <c r="C19" s="369" t="s">
         <v>120</v>
       </c>
-      <c r="D19" s="339"/>
-      <c r="E19" s="340"/>
+      <c r="D19" s="370"/>
+      <c r="E19" s="371"/>
       <c r="F19" s="71">
         <v>11035</v>
       </c>
@@ -5372,24 +5375,24 @@
         <v>24470.58</v>
       </c>
       <c r="I19" s="19"/>
-      <c r="J19" s="397" t="s">
+      <c r="J19" s="392" t="s">
         <v>148</v>
       </c>
-      <c r="K19" s="398"/>
-      <c r="L19" s="398"/>
-      <c r="M19" s="399"/>
+      <c r="K19" s="393"/>
+      <c r="L19" s="393"/>
+      <c r="M19" s="394"/>
       <c r="N19" s="150">
         <v>61008</v>
       </c>
     </row>
-    <row r="20" spans="1:23" ht="25.5" customHeight="1">
+    <row r="20" spans="1:23" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3"/>
-      <c r="B20" s="362"/>
-      <c r="C20" s="338" t="s">
+      <c r="B20" s="425"/>
+      <c r="C20" s="369" t="s">
         <v>155</v>
       </c>
-      <c r="D20" s="339"/>
-      <c r="E20" s="340"/>
+      <c r="D20" s="370"/>
+      <c r="E20" s="371"/>
       <c r="F20" s="71">
         <v>0</v>
       </c>
@@ -5398,34 +5401,34 @@
       </c>
       <c r="H20" s="69"/>
       <c r="I20" s="19"/>
-      <c r="J20" s="397" t="s">
+      <c r="J20" s="392" t="s">
         <v>161</v>
       </c>
-      <c r="K20" s="398"/>
-      <c r="L20" s="398"/>
-      <c r="M20" s="399"/>
+      <c r="K20" s="393"/>
+      <c r="L20" s="393"/>
+      <c r="M20" s="394"/>
       <c r="N20" s="150">
         <v>75850</v>
       </c>
-      <c r="S20" s="401" t="s">
+      <c r="S20" s="396" t="s">
         <v>211</v>
       </c>
-      <c r="T20" s="401"/>
-      <c r="U20" s="401"/>
-      <c r="V20" s="333">
+      <c r="T20" s="396"/>
+      <c r="U20" s="396"/>
+      <c r="V20" s="453">
         <f>V18+W18</f>
         <v>415722</v>
       </c>
-      <c r="W20" s="333"/>
-    </row>
-    <row r="21" spans="1:23" ht="20.100000000000001" customHeight="1">
+      <c r="W20" s="453"/>
+    </row>
+    <row r="21" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3"/>
-      <c r="B21" s="362"/>
-      <c r="C21" s="338" t="s">
+      <c r="B21" s="425"/>
+      <c r="C21" s="369" t="s">
         <v>121</v>
       </c>
-      <c r="D21" s="339"/>
-      <c r="E21" s="340"/>
+      <c r="D21" s="370"/>
+      <c r="E21" s="371"/>
       <c r="F21" s="71" t="s">
         <v>117</v>
       </c>
@@ -5434,21 +5437,21 @@
         <v>0</v>
       </c>
       <c r="I21" s="19"/>
-      <c r="J21" s="397"/>
-      <c r="K21" s="398"/>
-      <c r="L21" s="398"/>
-      <c r="M21" s="399"/>
+      <c r="J21" s="392"/>
+      <c r="K21" s="393"/>
+      <c r="L21" s="393"/>
+      <c r="M21" s="394"/>
       <c r="N21" s="150"/>
       <c r="P21" s="285"/>
     </row>
-    <row r="22" spans="1:23" ht="23.45" customHeight="1" thickBot="1">
+    <row r="22" spans="1:23" ht="23.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3"/>
-      <c r="B22" s="362"/>
-      <c r="C22" s="388" t="s">
+      <c r="B22" s="425"/>
+      <c r="C22" s="443" t="s">
         <v>123</v>
       </c>
-      <c r="D22" s="389"/>
-      <c r="E22" s="390"/>
+      <c r="D22" s="444"/>
+      <c r="E22" s="445"/>
       <c r="F22" s="73">
         <f>SUM(F17:F21)</f>
         <v>85715</v>
@@ -5462,21 +5465,21 @@
         <v>148534.65999999997</v>
       </c>
       <c r="I22" s="19"/>
-      <c r="J22" s="341" t="s">
+      <c r="J22" s="455" t="s">
         <v>141</v>
       </c>
-      <c r="K22" s="342"/>
-      <c r="L22" s="342"/>
-      <c r="M22" s="343"/>
+      <c r="K22" s="456"/>
+      <c r="L22" s="456"/>
+      <c r="M22" s="457"/>
       <c r="N22" s="155">
         <f>SUM(N15:N21)</f>
         <v>286688</v>
       </c>
       <c r="P22" s="285"/>
     </row>
-    <row r="23" spans="1:23" ht="20.100000000000001" customHeight="1" thickBot="1">
+    <row r="23" spans="1:23" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3"/>
-      <c r="B23" s="362"/>
+      <c r="B23" s="425"/>
       <c r="C23" s="52"/>
       <c r="D23" s="53"/>
       <c r="E23" s="54"/>
@@ -5486,14 +5489,14 @@
       <c r="I23" s="19"/>
       <c r="N23" s="146"/>
     </row>
-    <row r="24" spans="1:23" ht="24" customHeight="1">
+    <row r="24" spans="1:23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3"/>
-      <c r="B24" s="362"/>
-      <c r="C24" s="335" t="s">
+      <c r="B24" s="425"/>
+      <c r="C24" s="409" t="s">
         <v>124</v>
       </c>
-      <c r="D24" s="336"/>
-      <c r="E24" s="337"/>
+      <c r="D24" s="410"/>
+      <c r="E24" s="411"/>
       <c r="F24" s="89" t="s">
         <v>1</v>
       </c>
@@ -5504,29 +5507,29 @@
         <v>3</v>
       </c>
       <c r="I24" s="7"/>
-      <c r="J24" s="354" t="s">
+      <c r="J24" s="460" t="s">
         <v>143</v>
       </c>
-      <c r="K24" s="355"/>
-      <c r="L24" s="355"/>
-      <c r="M24" s="356"/>
+      <c r="K24" s="461"/>
+      <c r="L24" s="461"/>
+      <c r="M24" s="462"/>
       <c r="N24" s="147" t="s">
         <v>96</v>
       </c>
-      <c r="O24" s="344"/>
-      <c r="P24" s="345"/>
+      <c r="O24" s="458"/>
+      <c r="P24" s="459"/>
       <c r="Q24" s="58"/>
       <c r="R24" s="66"/>
       <c r="S24" s="66"/>
     </row>
-    <row r="25" spans="1:23" ht="24" customHeight="1">
+    <row r="25" spans="1:23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3"/>
       <c r="B25" s="20"/>
-      <c r="C25" s="338" t="s">
+      <c r="C25" s="369" t="s">
         <v>129</v>
       </c>
-      <c r="D25" s="339"/>
-      <c r="E25" s="340"/>
+      <c r="D25" s="370"/>
+      <c r="E25" s="371"/>
       <c r="F25" s="71">
         <f>F13-F26-F28-F29</f>
         <v>14520</v>
@@ -5536,12 +5539,12 @@
         <v>3308</v>
       </c>
       <c r="I25" s="7"/>
-      <c r="J25" s="346" t="s">
-        <v>2</v>
-      </c>
-      <c r="K25" s="347"/>
-      <c r="L25" s="347"/>
-      <c r="M25" s="330"/>
+      <c r="J25" s="417" t="s">
+        <v>2</v>
+      </c>
+      <c r="K25" s="418"/>
+      <c r="L25" s="418"/>
+      <c r="M25" s="419"/>
       <c r="N25" s="145"/>
       <c r="O25" s="58"/>
       <c r="P25" s="58"/>
@@ -5549,14 +5552,14 @@
       <c r="R25" s="66"/>
       <c r="S25" s="66"/>
     </row>
-    <row r="26" spans="1:23" ht="24" customHeight="1">
+    <row r="26" spans="1:23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3"/>
       <c r="B26" s="20"/>
-      <c r="C26" s="338" t="s">
+      <c r="C26" s="369" t="s">
         <v>125</v>
       </c>
-      <c r="D26" s="339"/>
-      <c r="E26" s="340"/>
+      <c r="D26" s="370"/>
+      <c r="E26" s="371"/>
       <c r="F26" s="71">
         <v>10894</v>
       </c>
@@ -5566,12 +5569,12 @@
         <v>12786</v>
       </c>
       <c r="I26" s="7"/>
-      <c r="J26" s="348" t="s">
+      <c r="J26" s="432" t="s">
         <v>206</v>
       </c>
-      <c r="K26" s="349"/>
-      <c r="L26" s="349"/>
-      <c r="M26" s="350"/>
+      <c r="K26" s="433"/>
+      <c r="L26" s="433"/>
+      <c r="M26" s="434"/>
       <c r="N26" s="150">
         <v>2546</v>
       </c>
@@ -5580,7 +5583,7 @@
       <c r="R26" s="66"/>
       <c r="S26" s="66"/>
     </row>
-    <row r="27" spans="1:23" ht="24" customHeight="1">
+    <row r="27" spans="1:23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3"/>
       <c r="B27" s="179"/>
       <c r="C27" s="176"/>
@@ -5590,12 +5593,12 @@
       <c r="G27" s="181"/>
       <c r="H27" s="121"/>
       <c r="I27" s="7"/>
-      <c r="J27" s="348" t="s">
+      <c r="J27" s="432" t="s">
         <v>207</v>
       </c>
-      <c r="K27" s="349"/>
-      <c r="L27" s="349"/>
-      <c r="M27" s="350"/>
+      <c r="K27" s="433"/>
+      <c r="L27" s="433"/>
+      <c r="M27" s="434"/>
       <c r="N27" s="150">
         <v>1065</v>
       </c>
@@ -5604,14 +5607,14 @@
       <c r="R27" s="66"/>
       <c r="S27" s="66"/>
     </row>
-    <row r="28" spans="1:23" ht="24" customHeight="1">
+    <row r="28" spans="1:23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3"/>
       <c r="B28" s="20"/>
-      <c r="C28" s="338" t="s">
+      <c r="C28" s="369" t="s">
         <v>126</v>
       </c>
-      <c r="D28" s="339"/>
-      <c r="E28" s="340"/>
+      <c r="D28" s="370"/>
+      <c r="E28" s="371"/>
       <c r="F28" s="71">
         <v>4265</v>
       </c>
@@ -5621,12 +5624,12 @@
         <v>7113</v>
       </c>
       <c r="I28" s="7"/>
-      <c r="J28" s="348" t="s">
+      <c r="J28" s="432" t="s">
         <v>208</v>
       </c>
-      <c r="K28" s="349"/>
-      <c r="L28" s="349"/>
-      <c r="M28" s="350"/>
+      <c r="K28" s="433"/>
+      <c r="L28" s="433"/>
+      <c r="M28" s="434"/>
       <c r="N28" s="150">
         <v>37812</v>
       </c>
@@ -5635,14 +5638,14 @@
       <c r="R28" s="66"/>
       <c r="S28" s="66"/>
     </row>
-    <row r="29" spans="1:23" ht="37.5" customHeight="1">
+    <row r="29" spans="1:23" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3"/>
       <c r="B29" s="20"/>
-      <c r="C29" s="338" t="s">
+      <c r="C29" s="369" t="s">
         <v>127</v>
       </c>
-      <c r="D29" s="339"/>
-      <c r="E29" s="340"/>
+      <c r="D29" s="370"/>
+      <c r="E29" s="371"/>
       <c r="F29" s="71">
         <v>0</v>
       </c>
@@ -5651,62 +5654,62 @@
         <v>0</v>
       </c>
       <c r="I29" s="7"/>
-      <c r="J29" s="348"/>
-      <c r="K29" s="349"/>
-      <c r="L29" s="349"/>
-      <c r="M29" s="350"/>
+      <c r="J29" s="432"/>
+      <c r="K29" s="433"/>
+      <c r="L29" s="433"/>
+      <c r="M29" s="434"/>
       <c r="N29" s="150"/>
       <c r="P29" s="58"/>
       <c r="Q29" s="58"/>
       <c r="R29" s="66"/>
       <c r="S29" s="66"/>
     </row>
-    <row r="30" spans="1:23" ht="23.25" customHeight="1">
+    <row r="30" spans="1:23" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3"/>
       <c r="B30" s="20"/>
-      <c r="C30" s="338" t="s">
+      <c r="C30" s="369" t="s">
         <v>128</v>
       </c>
-      <c r="D30" s="339"/>
-      <c r="E30" s="340"/>
+      <c r="D30" s="370"/>
+      <c r="E30" s="371"/>
       <c r="F30" s="71"/>
       <c r="G30" s="102"/>
       <c r="H30" s="123">
         <v>0</v>
       </c>
       <c r="I30" s="7"/>
-      <c r="J30" s="357" t="s">
+      <c r="J30" s="403" t="s">
         <v>94</v>
       </c>
-      <c r="K30" s="358"/>
-      <c r="L30" s="358"/>
-      <c r="M30" s="359"/>
+      <c r="K30" s="404"/>
+      <c r="L30" s="404"/>
+      <c r="M30" s="405"/>
       <c r="N30" s="151"/>
       <c r="P30" s="58"/>
       <c r="Q30" s="58"/>
       <c r="R30" s="66"/>
       <c r="S30" s="66"/>
     </row>
-    <row r="31" spans="1:23" ht="23.25" customHeight="1" thickBot="1">
+    <row r="31" spans="1:23" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="3"/>
       <c r="B31" s="20"/>
-      <c r="C31" s="338" t="s">
+      <c r="C31" s="369" t="s">
         <v>130</v>
       </c>
-      <c r="D31" s="339"/>
-      <c r="E31" s="340"/>
+      <c r="D31" s="370"/>
+      <c r="E31" s="371"/>
       <c r="F31" s="71"/>
       <c r="G31" s="99"/>
       <c r="H31" s="121">
         <v>0</v>
       </c>
       <c r="I31" s="7"/>
-      <c r="J31" s="351" t="s">
+      <c r="J31" s="446" t="s">
         <v>209</v>
       </c>
-      <c r="K31" s="352"/>
-      <c r="L31" s="352"/>
-      <c r="M31" s="353"/>
+      <c r="K31" s="447"/>
+      <c r="L31" s="447"/>
+      <c r="M31" s="448"/>
       <c r="N31" s="150">
         <v>6549</v>
       </c>
@@ -5715,14 +5718,14 @@
       <c r="R31" s="66"/>
       <c r="S31" s="66"/>
     </row>
-    <row r="32" spans="1:23" ht="19.5" customHeight="1" thickBot="1">
+    <row r="32" spans="1:23" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="3"/>
       <c r="B32" s="20"/>
-      <c r="C32" s="388" t="s">
+      <c r="C32" s="443" t="s">
         <v>131</v>
       </c>
-      <c r="D32" s="389"/>
-      <c r="E32" s="390"/>
+      <c r="D32" s="444"/>
+      <c r="E32" s="445"/>
       <c r="F32" s="71">
         <f>SUM(F25:F31)</f>
         <v>29679</v>
@@ -5736,12 +5739,12 @@
         <v>23207</v>
       </c>
       <c r="I32" s="7"/>
-      <c r="J32" s="351" t="s">
+      <c r="J32" s="446" t="s">
         <v>210</v>
       </c>
-      <c r="K32" s="352"/>
-      <c r="L32" s="352"/>
-      <c r="M32" s="353"/>
+      <c r="K32" s="447"/>
+      <c r="L32" s="447"/>
+      <c r="M32" s="448"/>
       <c r="N32" s="150">
         <v>1514</v>
       </c>
@@ -5750,14 +5753,14 @@
       <c r="R32" s="66"/>
       <c r="S32" s="66"/>
     </row>
-    <row r="33" spans="1:19" ht="8.25" customHeight="1" thickBot="1">
+    <row r="33" spans="1:19" ht="8.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="3"/>
       <c r="B33" s="20"/>
       <c r="I33" s="7"/>
-      <c r="J33" s="351"/>
-      <c r="K33" s="352"/>
-      <c r="L33" s="352"/>
-      <c r="M33" s="353"/>
+      <c r="J33" s="446"/>
+      <c r="K33" s="447"/>
+      <c r="L33" s="447"/>
+      <c r="M33" s="448"/>
       <c r="N33" s="152"/>
       <c r="O33" s="61"/>
       <c r="P33" s="61"/>
@@ -5765,14 +5768,14 @@
       <c r="R33" s="61"/>
       <c r="S33" s="61"/>
     </row>
-    <row r="34" spans="1:19" ht="19.5" customHeight="1" thickBot="1">
+    <row r="34" spans="1:19" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="3"/>
       <c r="B34" s="20"/>
-      <c r="C34" s="385" t="s">
+      <c r="C34" s="440" t="s">
         <v>103</v>
       </c>
-      <c r="D34" s="386"/>
-      <c r="E34" s="387"/>
+      <c r="D34" s="441"/>
+      <c r="E34" s="442"/>
       <c r="F34" s="77" t="str">
         <f>K1</f>
         <v>24.09.2026</v>
@@ -5784,12 +5787,12 @@
         <v>238</v>
       </c>
       <c r="I34" s="7"/>
-      <c r="J34" s="391" t="s">
+      <c r="J34" s="449" t="s">
         <v>140</v>
       </c>
-      <c r="K34" s="392"/>
-      <c r="L34" s="392"/>
-      <c r="M34" s="393"/>
+      <c r="K34" s="450"/>
+      <c r="L34" s="450"/>
+      <c r="M34" s="451"/>
       <c r="N34" s="163">
         <f>SUM(N26:N33)</f>
         <v>49486</v>
@@ -5798,7 +5801,7 @@
       <c r="R34" s="61"/>
       <c r="S34" s="61"/>
     </row>
-    <row r="35" spans="1:19" ht="27" customHeight="1" thickBot="1">
+    <row r="35" spans="1:19" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="3"/>
       <c r="B35" s="20"/>
       <c r="C35" s="124" t="s">
@@ -5825,7 +5828,7 @@
       <c r="R35" s="61"/>
       <c r="S35" s="61"/>
     </row>
-    <row r="36" spans="1:19" ht="42" customHeight="1">
+    <row r="36" spans="1:19" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3"/>
       <c r="B36" s="20"/>
       <c r="C36" s="125" t="s">
@@ -5848,11 +5851,11 @@
         <v>0</v>
       </c>
       <c r="I36" s="7"/>
-      <c r="J36" s="366" t="s">
+      <c r="J36" s="428" t="s">
         <v>156</v>
       </c>
-      <c r="K36" s="367"/>
-      <c r="L36" s="368"/>
+      <c r="K36" s="429"/>
+      <c r="L36" s="430"/>
       <c r="M36" s="112" t="s">
         <v>115</v>
       </c>
@@ -5865,13 +5868,13 @@
       <c r="P36" s="165" t="s">
         <v>138</v>
       </c>
-      <c r="Q36" s="446" t="s">
+      <c r="Q36" s="333" t="s">
         <v>149</v>
       </c>
-      <c r="R36" s="447"/>
+      <c r="R36" s="334"/>
       <c r="S36" s="61"/>
     </row>
-    <row r="37" spans="1:19" ht="36.75" customHeight="1">
+    <row r="37" spans="1:19" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="3"/>
       <c r="B37" s="20"/>
       <c r="C37" s="125" t="s">
@@ -5887,11 +5890,11 @@
       <c r="G37" s="134"/>
       <c r="H37" s="134"/>
       <c r="I37" s="7"/>
-      <c r="J37" s="369" t="s">
+      <c r="J37" s="349" t="s">
         <v>200</v>
       </c>
-      <c r="K37" s="370"/>
-      <c r="L37" s="371"/>
+      <c r="K37" s="350"/>
+      <c r="L37" s="351"/>
       <c r="M37" s="149">
         <v>79548</v>
       </c>
@@ -5904,13 +5907,13 @@
       <c r="P37" s="256" t="s">
         <v>221</v>
       </c>
-      <c r="Q37" s="454" t="s">
+      <c r="Q37" s="341" t="s">
         <v>230</v>
       </c>
-      <c r="R37" s="454"/>
+      <c r="R37" s="341"/>
       <c r="S37" s="61"/>
     </row>
-    <row r="38" spans="1:19" ht="30" customHeight="1">
+    <row r="38" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3"/>
       <c r="B38" s="20"/>
       <c r="C38" s="125" t="s">
@@ -5929,11 +5932,11 @@
       </c>
       <c r="H38" s="134"/>
       <c r="I38" s="7"/>
-      <c r="J38" s="369" t="s">
+      <c r="J38" s="349" t="s">
         <v>217</v>
       </c>
-      <c r="K38" s="370"/>
-      <c r="L38" s="371"/>
+      <c r="K38" s="350"/>
+      <c r="L38" s="351"/>
       <c r="M38" s="149">
         <v>75203</v>
       </c>
@@ -5944,13 +5947,13 @@
       <c r="P38" s="256" t="s">
         <v>221</v>
       </c>
-      <c r="Q38" s="454" t="s">
+      <c r="Q38" s="341" t="s">
         <v>216</v>
       </c>
-      <c r="R38" s="454"/>
+      <c r="R38" s="341"/>
       <c r="S38" s="61"/>
     </row>
-    <row r="39" spans="1:19" ht="22.5" customHeight="1">
+    <row r="39" spans="1:19" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="3"/>
       <c r="B39" s="20"/>
       <c r="C39" s="125" t="s">
@@ -5969,18 +5972,18 @@
       </c>
       <c r="H39" s="134"/>
       <c r="I39" s="7"/>
-      <c r="J39" s="369"/>
-      <c r="K39" s="370"/>
-      <c r="L39" s="371"/>
+      <c r="J39" s="349"/>
+      <c r="K39" s="350"/>
+      <c r="L39" s="351"/>
       <c r="M39" s="149"/>
       <c r="N39" s="149"/>
       <c r="O39" s="264"/>
       <c r="P39" s="256"/>
-      <c r="Q39" s="454"/>
-      <c r="R39" s="454"/>
+      <c r="Q39" s="341"/>
+      <c r="R39" s="341"/>
       <c r="S39" s="61"/>
     </row>
-    <row r="40" spans="1:19" ht="22.5" customHeight="1">
+    <row r="40" spans="1:19" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="3"/>
       <c r="B40" s="298"/>
       <c r="C40" s="125"/>
@@ -5990,18 +5993,18 @@
       <c r="G40" s="134"/>
       <c r="H40" s="134"/>
       <c r="I40" s="7"/>
-      <c r="J40" s="369"/>
-      <c r="K40" s="370"/>
-      <c r="L40" s="371"/>
+      <c r="J40" s="349"/>
+      <c r="K40" s="350"/>
+      <c r="L40" s="351"/>
       <c r="M40" s="149"/>
       <c r="N40" s="149"/>
       <c r="O40" s="264"/>
       <c r="P40" s="256"/>
-      <c r="Q40" s="450"/>
-      <c r="R40" s="451"/>
+      <c r="Q40" s="337"/>
+      <c r="R40" s="338"/>
       <c r="S40" s="61"/>
     </row>
-    <row r="41" spans="1:19" ht="22.5" customHeight="1">
+    <row r="41" spans="1:19" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="3"/>
       <c r="B41" s="279"/>
       <c r="C41" s="125"/>
@@ -6011,11 +6014,11 @@
       <c r="G41" s="134"/>
       <c r="H41" s="134"/>
       <c r="I41" s="7"/>
-      <c r="J41" s="455" t="s">
+      <c r="J41" s="342" t="s">
         <v>229</v>
       </c>
-      <c r="K41" s="455"/>
-      <c r="L41" s="455"/>
+      <c r="K41" s="342"/>
+      <c r="L41" s="342"/>
       <c r="M41" s="149">
         <v>78480</v>
       </c>
@@ -6026,13 +6029,13 @@
       <c r="P41" s="256" t="s">
         <v>221</v>
       </c>
-      <c r="Q41" s="454" t="s">
+      <c r="Q41" s="341" t="s">
         <v>216</v>
       </c>
-      <c r="R41" s="454"/>
+      <c r="R41" s="341"/>
       <c r="S41" s="61"/>
     </row>
-    <row r="42" spans="1:19" ht="24.75" customHeight="1">
+    <row r="42" spans="1:19" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="3"/>
       <c r="B42" s="20"/>
       <c r="C42" s="125" t="s">
@@ -6053,23 +6056,23 @@
         <v>0</v>
       </c>
       <c r="I42" s="7"/>
-      <c r="J42" s="456" t="s">
+      <c r="J42" s="345" t="s">
         <v>98</v>
       </c>
-      <c r="K42" s="457"/>
-      <c r="L42" s="457"/>
-      <c r="M42" s="457"/>
+      <c r="K42" s="346"/>
+      <c r="L42" s="346"/>
+      <c r="M42" s="346"/>
       <c r="N42" s="166"/>
       <c r="O42" s="167">
         <f>SUM(N37:N41)</f>
         <v>79548</v>
       </c>
       <c r="P42" s="254"/>
-      <c r="Q42" s="448"/>
-      <c r="R42" s="448"/>
+      <c r="Q42" s="335"/>
+      <c r="R42" s="335"/>
       <c r="S42" s="61"/>
     </row>
-    <row r="43" spans="1:19" ht="26.25" customHeight="1" thickBot="1">
+    <row r="43" spans="1:19" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="3"/>
       <c r="B43" s="20"/>
       <c r="C43" s="125" t="s">
@@ -6085,23 +6088,23 @@
       </c>
       <c r="H43" s="136"/>
       <c r="I43" s="7"/>
-      <c r="J43" s="460" t="s">
+      <c r="J43" s="352" t="s">
         <v>99</v>
       </c>
-      <c r="K43" s="461"/>
-      <c r="L43" s="461"/>
-      <c r="M43" s="461"/>
-      <c r="N43" s="462"/>
+      <c r="K43" s="353"/>
+      <c r="L43" s="353"/>
+      <c r="M43" s="353"/>
+      <c r="N43" s="354"/>
       <c r="O43" s="148">
         <f>N22+N34+O42</f>
         <v>415722</v>
       </c>
       <c r="P43" s="255"/>
-      <c r="Q43" s="449"/>
-      <c r="R43" s="449"/>
+      <c r="Q43" s="336"/>
+      <c r="R43" s="336"/>
       <c r="S43" s="61"/>
     </row>
-    <row r="44" spans="1:19" ht="19.5" customHeight="1" thickBot="1">
+    <row r="44" spans="1:19" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="3"/>
       <c r="B44" s="20"/>
       <c r="C44" s="125" t="s">
@@ -6130,7 +6133,7 @@
       <c r="R44" s="22"/>
       <c r="S44" s="22"/>
     </row>
-    <row r="45" spans="1:19" ht="27.6" customHeight="1">
+    <row r="45" spans="1:19" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="3"/>
       <c r="C45" s="125" t="s">
         <v>113</v>
@@ -6148,10 +6151,10 @@
       <c r="H45" s="134">
         <v>0</v>
       </c>
-      <c r="J45" s="458" t="s">
+      <c r="J45" s="347" t="s">
         <v>102</v>
       </c>
-      <c r="K45" s="459"/>
+      <c r="K45" s="348"/>
       <c r="L45" s="116" t="s">
         <v>1</v>
       </c>
@@ -6175,7 +6178,7 @@
       </c>
       <c r="S45" s="96"/>
     </row>
-    <row r="46" spans="1:19" ht="23.25" customHeight="1" thickBot="1">
+    <row r="46" spans="1:19" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="3"/>
       <c r="C46" s="126" t="s">
         <v>114</v>
@@ -6189,10 +6192,10 @@
       <c r="H46" s="134">
         <v>2</v>
       </c>
-      <c r="J46" s="380" t="s">
+      <c r="J46" s="343" t="s">
         <v>15</v>
       </c>
-      <c r="K46" s="381"/>
+      <c r="K46" s="344"/>
       <c r="L46" s="156">
         <v>37.18</v>
       </c>
@@ -6219,7 +6222,7 @@
       </c>
       <c r="S46" s="115"/>
     </row>
-    <row r="47" spans="1:19" ht="23.25" customHeight="1" thickBot="1">
+    <row r="47" spans="1:19" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="3"/>
       <c r="C47" s="127" t="s">
         <v>136</v>
@@ -6244,10 +6247,10 @@
         <f>SUM(H36:H46)</f>
         <v>2</v>
       </c>
-      <c r="J47" s="380" t="s">
+      <c r="J47" s="343" t="s">
         <v>16</v>
       </c>
-      <c r="K47" s="381"/>
+      <c r="K47" s="344"/>
       <c r="L47" s="156">
         <v>33.978999999999999</v>
       </c>
@@ -6273,7 +6276,7 @@
       </c>
       <c r="S47" s="115"/>
     </row>
-    <row r="48" spans="1:19" ht="20.25" customHeight="1">
+    <row r="48" spans="1:19" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3"/>
       <c r="C48" s="83" t="s">
         <v>132</v>
@@ -6283,10 +6286,10 @@
       <c r="F48" s="80"/>
       <c r="G48" s="84"/>
       <c r="H48" s="85"/>
-      <c r="J48" s="380" t="s">
+      <c r="J48" s="343" t="s">
         <v>17</v>
       </c>
-      <c r="K48" s="381"/>
+      <c r="K48" s="344"/>
       <c r="L48" s="156">
         <f>(L46-L47)/L46*100</f>
         <v>8.6094674556213029</v>
@@ -6311,7 +6314,7 @@
       <c r="R48" s="157"/>
       <c r="S48" s="108"/>
     </row>
-    <row r="49" spans="1:19" ht="21" customHeight="1" thickBot="1">
+    <row r="49" spans="1:19" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="3"/>
       <c r="C49" s="81" t="s">
         <v>133</v>
@@ -6333,10 +6336,10 @@
         <v>3</v>
       </c>
       <c r="I49" s="64"/>
-      <c r="J49" s="443" t="s">
+      <c r="J49" s="330" t="s">
         <v>18</v>
       </c>
-      <c r="K49" s="444"/>
+      <c r="K49" s="331"/>
       <c r="L49" s="156">
         <f>F13/L46/1000</f>
         <v>0.79825174825174827</v>
@@ -6361,7 +6364,7 @@
       <c r="R49" s="157"/>
       <c r="S49" s="108"/>
     </row>
-    <row r="50" spans="1:19" ht="23.45" customHeight="1" thickBot="1">
+    <row r="50" spans="1:19" ht="23.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="3"/>
       <c r="C50" s="82" t="s">
         <v>108</v>
@@ -6384,20 +6387,20 @@
       </c>
       <c r="J50" s="140"/>
       <c r="K50" s="141"/>
-      <c r="L50" s="380" t="s">
+      <c r="L50" s="343" t="s">
         <v>145</v>
       </c>
-      <c r="M50" s="381"/>
-      <c r="N50" s="382"/>
+      <c r="M50" s="344"/>
+      <c r="N50" s="439"/>
       <c r="O50" s="158">
         <v>192.18799999999999</v>
       </c>
       <c r="P50" s="142"/>
-      <c r="Q50" s="452"/>
-      <c r="R50" s="453"/>
+      <c r="Q50" s="339"/>
+      <c r="R50" s="340"/>
       <c r="S50" s="109"/>
     </row>
-    <row r="51" spans="1:19" ht="6" customHeight="1" thickBot="1">
+    <row r="51" spans="1:19" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="3"/>
       <c r="B51" s="23"/>
       <c r="C51" s="161"/>
@@ -6412,167 +6415,167 @@
       <c r="R51" s="60"/>
       <c r="S51" s="60"/>
     </row>
-    <row r="52" spans="1:19" ht="22.15" customHeight="1">
+    <row r="52" spans="1:19" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="3"/>
-      <c r="B52" s="377" t="s">
+      <c r="B52" s="355" t="s">
         <v>134</v>
       </c>
-      <c r="C52" s="378"/>
-      <c r="D52" s="378"/>
-      <c r="E52" s="378"/>
-      <c r="F52" s="378"/>
-      <c r="G52" s="379"/>
+      <c r="C52" s="356"/>
+      <c r="D52" s="356"/>
+      <c r="E52" s="356"/>
+      <c r="F52" s="356"/>
+      <c r="G52" s="357"/>
       <c r="H52" s="68"/>
-      <c r="J52" s="377" t="s">
+      <c r="J52" s="355" t="s">
         <v>135</v>
       </c>
-      <c r="K52" s="378"/>
-      <c r="L52" s="378"/>
-      <c r="M52" s="378"/>
-      <c r="N52" s="378"/>
-      <c r="O52" s="378"/>
-      <c r="P52" s="379"/>
+      <c r="K52" s="356"/>
+      <c r="L52" s="356"/>
+      <c r="M52" s="356"/>
+      <c r="N52" s="356"/>
+      <c r="O52" s="356"/>
+      <c r="P52" s="357"/>
       <c r="Q52" s="60"/>
       <c r="R52" s="60"/>
       <c r="S52" s="60"/>
     </row>
-    <row r="53" spans="1:19" ht="21">
+    <row r="53" spans="1:19" ht="21" x14ac:dyDescent="0.25">
       <c r="A53" s="3"/>
       <c r="B53" s="120" t="s">
         <v>23</v>
       </c>
-      <c r="C53" s="373" t="s">
+      <c r="C53" s="435" t="s">
         <v>21</v>
       </c>
-      <c r="D53" s="374"/>
+      <c r="D53" s="436"/>
       <c r="E53" s="168" t="s">
         <v>50</v>
       </c>
-      <c r="F53" s="329" t="s">
+      <c r="F53" s="328" t="s">
         <v>22</v>
       </c>
-      <c r="G53" s="331"/>
+      <c r="G53" s="329"/>
       <c r="H53" s="60"/>
       <c r="J53" s="160" t="s">
         <v>23</v>
       </c>
-      <c r="K53" s="445" t="s">
+      <c r="K53" s="332" t="s">
         <v>21</v>
       </c>
-      <c r="L53" s="445"/>
-      <c r="M53" s="445"/>
+      <c r="L53" s="332"/>
+      <c r="M53" s="332"/>
       <c r="N53" s="159" t="s">
         <v>142</v>
       </c>
-      <c r="O53" s="375" t="s">
+      <c r="O53" s="437" t="s">
         <v>22</v>
       </c>
-      <c r="P53" s="376"/>
+      <c r="P53" s="438"/>
       <c r="Q53" s="60"/>
       <c r="R53" s="60"/>
       <c r="S53" s="60"/>
     </row>
-    <row r="54" spans="1:19" ht="21">
+    <row r="54" spans="1:19" ht="21" x14ac:dyDescent="0.25">
       <c r="A54" s="3"/>
       <c r="B54" s="182">
         <v>1</v>
       </c>
-      <c r="C54" s="329" t="s">
+      <c r="C54" s="328" t="s">
         <v>250</v>
       </c>
-      <c r="D54" s="330"/>
+      <c r="D54" s="419"/>
       <c r="E54" s="257" t="s">
         <v>252</v>
       </c>
-      <c r="F54" s="329" t="s">
+      <c r="F54" s="328" t="s">
         <v>256</v>
       </c>
-      <c r="G54" s="331"/>
+      <c r="G54" s="329"/>
       <c r="H54" s="44"/>
       <c r="J54" s="318">
         <v>1</v>
       </c>
-      <c r="K54" s="332" t="s">
+      <c r="K54" s="358" t="s">
         <v>248</v>
       </c>
-      <c r="L54" s="332"/>
-      <c r="M54" s="332"/>
+      <c r="L54" s="358"/>
+      <c r="M54" s="358"/>
       <c r="N54" s="257" t="s">
         <v>246</v>
       </c>
-      <c r="O54" s="332" t="s">
+      <c r="O54" s="358" t="s">
         <v>288</v>
       </c>
-      <c r="P54" s="332"/>
+      <c r="P54" s="358"/>
       <c r="Q54" s="60"/>
       <c r="R54" s="60"/>
       <c r="S54" s="60"/>
     </row>
-    <row r="55" spans="1:19" ht="21">
+    <row r="55" spans="1:19" ht="21" x14ac:dyDescent="0.25">
       <c r="A55" s="3"/>
       <c r="B55" s="302">
         <v>2</v>
       </c>
-      <c r="C55" s="329" t="s">
+      <c r="C55" s="328" t="s">
         <v>251</v>
       </c>
-      <c r="D55" s="330"/>
+      <c r="D55" s="419"/>
       <c r="E55" s="169" t="s">
         <v>249</v>
       </c>
-      <c r="F55" s="329" t="s">
+      <c r="F55" s="328" t="s">
         <v>213</v>
       </c>
-      <c r="G55" s="331"/>
+      <c r="G55" s="329"/>
       <c r="H55" s="44"/>
       <c r="J55" s="324">
         <v>2</v>
       </c>
-      <c r="K55" s="332" t="s">
+      <c r="K55" s="358" t="s">
         <v>248</v>
       </c>
-      <c r="L55" s="332"/>
-      <c r="M55" s="332"/>
+      <c r="L55" s="358"/>
+      <c r="M55" s="358"/>
       <c r="N55" s="257" t="s">
         <v>247</v>
       </c>
-      <c r="O55" s="332" t="s">
+      <c r="O55" s="358" t="s">
         <v>233</v>
       </c>
-      <c r="P55" s="332"/>
+      <c r="P55" s="358"/>
       <c r="Q55" s="60"/>
       <c r="R55" s="60"/>
       <c r="S55" s="60"/>
     </row>
-    <row r="56" spans="1:19" ht="21">
+    <row r="56" spans="1:19" ht="21" x14ac:dyDescent="0.25">
       <c r="A56" s="3"/>
       <c r="B56" s="316">
         <v>3</v>
       </c>
-      <c r="C56" s="329" t="s">
+      <c r="C56" s="328" t="s">
         <v>220</v>
       </c>
-      <c r="D56" s="330"/>
+      <c r="D56" s="419"/>
       <c r="E56" s="169" t="s">
         <v>253</v>
       </c>
-      <c r="F56" s="329" t="s">
+      <c r="F56" s="328" t="s">
         <v>213</v>
       </c>
-      <c r="G56" s="331"/>
+      <c r="G56" s="329"/>
       <c r="H56" s="44"/>
       <c r="J56" s="324"/>
-      <c r="K56" s="332"/>
-      <c r="L56" s="332"/>
-      <c r="M56" s="332"/>
+      <c r="K56" s="358"/>
+      <c r="L56" s="358"/>
+      <c r="M56" s="358"/>
       <c r="N56" s="257"/>
-      <c r="O56" s="332"/>
-      <c r="P56" s="332"/>
+      <c r="O56" s="358"/>
+      <c r="P56" s="358"/>
       <c r="Q56" s="60"/>
       <c r="R56" s="60"/>
       <c r="S56" s="60"/>
     </row>
-    <row r="57" spans="1:19" ht="21">
+    <row r="57" spans="1:19" ht="21" x14ac:dyDescent="0.25">
       <c r="A57" s="3"/>
       <c r="B57" s="325"/>
       <c r="C57" s="322"/>
@@ -6592,27 +6595,27 @@
       <c r="R57" s="60"/>
       <c r="S57" s="60"/>
     </row>
-    <row r="58" spans="1:19" ht="21.75" customHeight="1">
+    <row r="58" spans="1:19" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="3"/>
-      <c r="B58" s="372" t="s">
+      <c r="B58" s="431" t="s">
         <v>239</v>
       </c>
-      <c r="C58" s="372"/>
-      <c r="D58" s="372"/>
-      <c r="E58" s="372"/>
-      <c r="F58" s="372"/>
-      <c r="G58" s="372"/>
-      <c r="H58" s="372"/>
-      <c r="I58" s="372"/>
-      <c r="J58" s="372"/>
-      <c r="K58" s="372"/>
-      <c r="L58" s="372"/>
-      <c r="M58" s="372"/>
-      <c r="N58" s="372"/>
-      <c r="O58" s="372"/>
-      <c r="P58" s="372"/>
-    </row>
-    <row r="59" spans="1:19" ht="6.75" customHeight="1">
+      <c r="C58" s="431"/>
+      <c r="D58" s="431"/>
+      <c r="E58" s="431"/>
+      <c r="F58" s="431"/>
+      <c r="G58" s="431"/>
+      <c r="H58" s="431"/>
+      <c r="I58" s="431"/>
+      <c r="J58" s="431"/>
+      <c r="K58" s="431"/>
+      <c r="L58" s="431"/>
+      <c r="M58" s="431"/>
+      <c r="N58" s="431"/>
+      <c r="O58" s="431"/>
+      <c r="P58" s="431"/>
+    </row>
+    <row r="59" spans="1:19" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="3"/>
       <c r="B59" s="253"/>
       <c r="C59" s="253"/>
@@ -6630,51 +6633,51 @@
       <c r="O59" s="253"/>
       <c r="P59" s="253"/>
     </row>
-    <row r="60" spans="1:19" ht="15.6" customHeight="1">
+    <row r="60" spans="1:19" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B60" s="3"/>
-      <c r="C60" s="334" t="s">
+      <c r="C60" s="454" t="s">
         <v>94</v>
       </c>
-      <c r="D60" s="334"/>
-      <c r="E60" s="334"/>
-      <c r="F60" s="334"/>
+      <c r="D60" s="454"/>
+      <c r="E60" s="454"/>
+      <c r="F60" s="454"/>
       <c r="G60" s="40"/>
       <c r="H60" s="40"/>
       <c r="I60" s="3"/>
-      <c r="J60" s="334" t="s">
+      <c r="J60" s="454" t="s">
         <v>89</v>
       </c>
-      <c r="K60" s="334"/>
-      <c r="L60" s="334"/>
-      <c r="M60" s="334"/>
-      <c r="N60" s="334"/>
+      <c r="K60" s="454"/>
+      <c r="L60" s="454"/>
+      <c r="M60" s="454"/>
+      <c r="N60" s="454"/>
       <c r="O60" s="42"/>
     </row>
-    <row r="61" spans="1:19" ht="28.5">
+    <row r="61" spans="1:19" ht="25.5" x14ac:dyDescent="0.2">
       <c r="B61" s="110" t="s">
         <v>23</v>
       </c>
-      <c r="C61" s="365" t="s">
+      <c r="C61" s="427" t="s">
         <v>78</v>
       </c>
-      <c r="D61" s="365"/>
-      <c r="E61" s="365"/>
-      <c r="F61" s="365"/>
+      <c r="D61" s="427"/>
+      <c r="E61" s="427"/>
+      <c r="F61" s="427"/>
       <c r="G61" s="40"/>
       <c r="H61" s="40"/>
       <c r="I61" s="110" t="s">
         <v>23</v>
       </c>
-      <c r="J61" s="365" t="s">
+      <c r="J61" s="427" t="s">
         <v>78</v>
       </c>
-      <c r="K61" s="365"/>
-      <c r="L61" s="365"/>
-      <c r="M61" s="365"/>
-      <c r="N61" s="365"/>
+      <c r="K61" s="427"/>
+      <c r="L61" s="427"/>
+      <c r="M61" s="427"/>
+      <c r="N61" s="427"/>
       <c r="O61" s="42"/>
     </row>
-    <row r="62" spans="1:19" ht="28.5">
+    <row r="62" spans="1:19" ht="25.5" x14ac:dyDescent="0.2">
       <c r="B62" s="110"/>
       <c r="C62" s="304"/>
       <c r="D62" s="304"/>
@@ -6690,7 +6693,7 @@
       <c r="N62" s="304"/>
       <c r="O62" s="42"/>
     </row>
-    <row r="63" spans="1:19" ht="16.149999999999999" customHeight="1">
+    <row r="63" spans="1:19" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B63" s="111">
         <v>1</v>
       </c>
@@ -6718,7 +6721,7 @@
       <c r="R63" s="39"/>
       <c r="S63" s="39"/>
     </row>
-    <row r="64" spans="1:19" ht="16.149999999999999" customHeight="1">
+    <row r="64" spans="1:19" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B64" s="111">
         <v>2</v>
       </c>
@@ -6746,7 +6749,7 @@
       <c r="R64" s="39"/>
       <c r="S64" s="39"/>
     </row>
-    <row r="65" spans="2:15" ht="16.149999999999999" customHeight="1">
+    <row r="65" spans="2:15" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B65" s="111">
         <v>3</v>
       </c>
@@ -6770,7 +6773,7 @@
       <c r="N65" s="281"/>
       <c r="O65" s="42"/>
     </row>
-    <row r="66" spans="2:15" ht="16.149999999999999" customHeight="1">
+    <row r="66" spans="2:15" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B66" s="111">
         <v>4</v>
       </c>
@@ -6794,7 +6797,7 @@
       <c r="N66" s="281"/>
       <c r="O66" s="42"/>
     </row>
-    <row r="67" spans="2:15" ht="16.149999999999999" customHeight="1">
+    <row r="67" spans="2:15" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B67" s="111">
         <v>5</v>
       </c>
@@ -6818,7 +6821,7 @@
       <c r="N67" s="281"/>
       <c r="O67" s="42"/>
     </row>
-    <row r="68" spans="2:15" ht="16.149999999999999" customHeight="1">
+    <row r="68" spans="2:15" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B68" s="111">
         <v>6</v>
       </c>
@@ -6842,7 +6845,7 @@
       <c r="N68" s="281"/>
       <c r="O68" s="42"/>
     </row>
-    <row r="69" spans="2:15" ht="16.149999999999999" customHeight="1">
+    <row r="69" spans="2:15" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B69" s="111">
         <v>7</v>
       </c>
@@ -6866,7 +6869,7 @@
       <c r="N69" s="281"/>
       <c r="O69" s="42"/>
     </row>
-    <row r="70" spans="2:15" ht="16.149999999999999" customHeight="1">
+    <row r="70" spans="2:15" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B70" s="111">
         <v>8</v>
       </c>
@@ -6890,7 +6893,7 @@
       <c r="N70" s="281"/>
       <c r="O70" s="39"/>
     </row>
-    <row r="71" spans="2:15" ht="16.149999999999999" customHeight="1">
+    <row r="71" spans="2:15" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B71" s="111">
         <v>9</v>
       </c>
@@ -6914,7 +6917,7 @@
       <c r="N71" s="281"/>
       <c r="O71" s="39"/>
     </row>
-    <row r="72" spans="2:15" ht="16.149999999999999" customHeight="1">
+    <row r="72" spans="2:15" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B72" s="111">
         <v>10</v>
       </c>
@@ -6938,7 +6941,7 @@
       <c r="N72" s="282"/>
       <c r="O72" s="39"/>
     </row>
-    <row r="73" spans="2:15" ht="16.149999999999999" customHeight="1">
+    <row r="73" spans="2:15" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B73" s="111">
         <v>11</v>
       </c>
@@ -6958,7 +6961,7 @@
       <c r="N73" s="323"/>
       <c r="O73" s="323"/>
     </row>
-    <row r="74" spans="2:15" ht="16.149999999999999" customHeight="1">
+    <row r="74" spans="2:15" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B74" s="111">
         <v>12</v>
       </c>
@@ -6978,7 +6981,7 @@
       <c r="N74" s="282"/>
       <c r="O74" s="39"/>
     </row>
-    <row r="75" spans="2:15" ht="16.149999999999999" customHeight="1">
+    <row r="75" spans="2:15" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B75" s="111">
         <v>13</v>
       </c>
@@ -6998,7 +7001,7 @@
       <c r="N75" s="282"/>
       <c r="O75" s="39"/>
     </row>
-    <row r="76" spans="2:15" ht="16.149999999999999" customHeight="1">
+    <row r="76" spans="2:15" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B76" s="111">
         <v>14</v>
       </c>
@@ -7018,7 +7021,7 @@
       <c r="N76" s="283"/>
       <c r="O76" s="39"/>
     </row>
-    <row r="77" spans="2:15" ht="16.149999999999999" customHeight="1">
+    <row r="77" spans="2:15" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B77" s="111">
         <v>15</v>
       </c>
@@ -7037,7 +7040,7 @@
       <c r="N77" s="283"/>
       <c r="O77" s="273"/>
     </row>
-    <row r="78" spans="2:15" ht="16.149999999999999" customHeight="1">
+    <row r="78" spans="2:15" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B78" s="111">
         <v>16</v>
       </c>
@@ -7057,7 +7060,7 @@
       <c r="N78" s="283"/>
       <c r="O78" s="39"/>
     </row>
-    <row r="79" spans="2:15" ht="16.149999999999999" customHeight="1">
+    <row r="79" spans="2:15" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B79" s="111">
         <v>17</v>
       </c>
@@ -7077,7 +7080,7 @@
       <c r="N79" s="283"/>
       <c r="O79" s="278"/>
     </row>
-    <row r="80" spans="2:15" ht="16.149999999999999" customHeight="1">
+    <row r="80" spans="2:15" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B80" s="111">
         <v>18</v>
       </c>
@@ -7097,7 +7100,7 @@
       <c r="N80" s="277"/>
       <c r="O80" s="278"/>
     </row>
-    <row r="81" spans="2:16" ht="16.149999999999999" customHeight="1">
+    <row r="81" spans="2:16" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B81" s="111">
         <v>19</v>
       </c>
@@ -7117,7 +7120,7 @@
       <c r="N81" s="317"/>
       <c r="O81" s="278"/>
     </row>
-    <row r="82" spans="2:16" ht="16.149999999999999" customHeight="1">
+    <row r="82" spans="2:16" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B82" s="111">
         <v>20</v>
       </c>
@@ -7137,7 +7140,7 @@
       <c r="N82" s="321"/>
       <c r="O82" s="284"/>
     </row>
-    <row r="83" spans="2:16" ht="16.149999999999999" customHeight="1">
+    <row r="83" spans="2:16" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B83" s="111">
         <v>21</v>
       </c>
@@ -7159,7 +7162,7 @@
       <c r="N83" s="272"/>
       <c r="O83" s="284"/>
     </row>
-    <row r="84" spans="2:16" ht="16.149999999999999" customHeight="1">
+    <row r="84" spans="2:16" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B84" s="111">
         <v>22</v>
       </c>
@@ -7179,7 +7182,7 @@
       <c r="N84" s="283"/>
       <c r="O84" s="284"/>
     </row>
-    <row r="85" spans="2:16" ht="16.149999999999999" customHeight="1">
+    <row r="85" spans="2:16" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B85" s="111">
         <v>23</v>
       </c>
@@ -7192,16 +7195,16 @@
       <c r="G85" s="252"/>
       <c r="H85" s="276"/>
       <c r="I85" s="270"/>
-      <c r="J85" s="589" t="s">
+      <c r="J85" s="463" t="s">
         <v>255</v>
       </c>
-      <c r="K85" s="589"/>
-      <c r="L85" s="589"/>
-      <c r="M85" s="589"/>
-      <c r="N85" s="589"/>
-      <c r="O85" s="589"/>
-    </row>
-    <row r="86" spans="2:16" ht="16.149999999999999" customHeight="1">
+      <c r="K85" s="463"/>
+      <c r="L85" s="463"/>
+      <c r="M85" s="463"/>
+      <c r="N85" s="463"/>
+      <c r="O85" s="463"/>
+    </row>
+    <row r="86" spans="2:16" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B86" s="111">
         <v>24</v>
       </c>
@@ -7214,14 +7217,14 @@
       <c r="G86" s="287"/>
       <c r="H86" s="276"/>
       <c r="I86" s="270"/>
-      <c r="J86" s="328"/>
-      <c r="K86" s="328"/>
-      <c r="L86" s="328"/>
-      <c r="M86" s="328"/>
-      <c r="N86" s="328"/>
-      <c r="O86" s="328"/>
-    </row>
-    <row r="87" spans="2:16" ht="16.149999999999999" customHeight="1">
+      <c r="J86" s="452"/>
+      <c r="K86" s="452"/>
+      <c r="L86" s="452"/>
+      <c r="M86" s="452"/>
+      <c r="N86" s="452"/>
+      <c r="O86" s="452"/>
+    </row>
+    <row r="87" spans="2:16" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B87" s="111">
         <v>25</v>
       </c>
@@ -7234,14 +7237,14 @@
       <c r="G87" s="252"/>
       <c r="H87" s="252"/>
       <c r="I87" s="270"/>
-      <c r="J87" s="328"/>
-      <c r="K87" s="328"/>
-      <c r="L87" s="328"/>
-      <c r="M87" s="328"/>
-      <c r="N87" s="328"/>
-      <c r="O87" s="328"/>
-    </row>
-    <row r="88" spans="2:16" ht="16.149999999999999" customHeight="1">
+      <c r="J87" s="452"/>
+      <c r="K87" s="452"/>
+      <c r="L87" s="452"/>
+      <c r="M87" s="452"/>
+      <c r="N87" s="452"/>
+      <c r="O87" s="452"/>
+    </row>
+    <row r="88" spans="2:16" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B88" s="111">
         <v>26</v>
       </c>
@@ -7254,14 +7257,14 @@
       <c r="G88" s="287"/>
       <c r="H88" s="252"/>
       <c r="I88" s="270"/>
-      <c r="J88" s="328"/>
-      <c r="K88" s="328"/>
-      <c r="L88" s="328"/>
-      <c r="M88" s="328"/>
-      <c r="N88" s="328"/>
-      <c r="O88" s="328"/>
-    </row>
-    <row r="89" spans="2:16" ht="16.149999999999999" customHeight="1">
+      <c r="J88" s="452"/>
+      <c r="K88" s="452"/>
+      <c r="L88" s="452"/>
+      <c r="M88" s="452"/>
+      <c r="N88" s="452"/>
+      <c r="O88" s="452"/>
+    </row>
+    <row r="89" spans="2:16" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B89" s="111">
         <v>27</v>
       </c>
@@ -7270,14 +7273,14 @@
       </c>
       <c r="H89" s="276"/>
       <c r="I89" s="270"/>
-      <c r="J89" s="328"/>
-      <c r="K89" s="328"/>
-      <c r="L89" s="328"/>
-      <c r="M89" s="328"/>
-      <c r="N89" s="328"/>
-      <c r="O89" s="328"/>
-    </row>
-    <row r="90" spans="2:16" ht="16.149999999999999" customHeight="1">
+      <c r="J89" s="452"/>
+      <c r="K89" s="452"/>
+      <c r="L89" s="452"/>
+      <c r="M89" s="452"/>
+      <c r="N89" s="452"/>
+      <c r="O89" s="452"/>
+    </row>
+    <row r="90" spans="2:16" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B90" s="111">
         <v>28</v>
       </c>
@@ -7290,15 +7293,15 @@
       <c r="G90" s="286"/>
       <c r="H90" s="276"/>
       <c r="I90" s="270"/>
-      <c r="J90" s="328"/>
-      <c r="K90" s="328"/>
-      <c r="L90" s="328"/>
-      <c r="M90" s="328"/>
-      <c r="N90" s="328"/>
-      <c r="O90" s="328"/>
+      <c r="J90" s="452"/>
+      <c r="K90" s="452"/>
+      <c r="L90" s="452"/>
+      <c r="M90" s="452"/>
+      <c r="N90" s="452"/>
+      <c r="O90" s="452"/>
       <c r="P90" s="265"/>
     </row>
-    <row r="91" spans="2:16" ht="16.149999999999999" customHeight="1">
+    <row r="91" spans="2:16" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B91" s="111">
         <v>29</v>
       </c>
@@ -7311,14 +7314,14 @@
       <c r="G91" s="286"/>
       <c r="H91" s="276"/>
       <c r="I91" s="270"/>
-      <c r="J91" s="328"/>
-      <c r="K91" s="328"/>
-      <c r="L91" s="328"/>
-      <c r="M91" s="328"/>
-      <c r="N91" s="328"/>
-      <c r="O91" s="328"/>
-    </row>
-    <row r="92" spans="2:16" ht="23.25">
+      <c r="J91" s="452"/>
+      <c r="K91" s="452"/>
+      <c r="L91" s="452"/>
+      <c r="M91" s="452"/>
+      <c r="N91" s="452"/>
+      <c r="O91" s="452"/>
+    </row>
+    <row r="92" spans="2:16" ht="24" x14ac:dyDescent="0.15">
       <c r="B92" s="111">
         <v>30</v>
       </c>
@@ -7331,14 +7334,14 @@
       <c r="G92" s="286"/>
       <c r="H92" s="276"/>
       <c r="I92" s="270"/>
-      <c r="J92" s="328"/>
-      <c r="K92" s="328"/>
-      <c r="L92" s="328"/>
-      <c r="M92" s="328"/>
-      <c r="N92" s="328"/>
-      <c r="O92" s="328"/>
-    </row>
-    <row r="93" spans="2:16" ht="20.25" customHeight="1">
+      <c r="J92" s="452"/>
+      <c r="K92" s="452"/>
+      <c r="L92" s="452"/>
+      <c r="M92" s="452"/>
+      <c r="N92" s="452"/>
+      <c r="O92" s="452"/>
+    </row>
+    <row r="93" spans="2:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B93" s="111">
         <v>31</v>
       </c>
@@ -7351,14 +7354,14 @@
       <c r="G93" s="287"/>
       <c r="H93" s="276"/>
       <c r="I93" s="270"/>
-      <c r="J93" s="328"/>
-      <c r="K93" s="328"/>
-      <c r="L93" s="328"/>
-      <c r="M93" s="328"/>
-      <c r="N93" s="328"/>
-      <c r="O93" s="328"/>
-    </row>
-    <row r="94" spans="2:16" ht="18" customHeight="1">
+      <c r="J93" s="452"/>
+      <c r="K93" s="452"/>
+      <c r="L93" s="452"/>
+      <c r="M93" s="452"/>
+      <c r="N93" s="452"/>
+      <c r="O93" s="452"/>
+    </row>
+    <row r="94" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B94" s="111">
         <v>32</v>
       </c>
@@ -7371,14 +7374,14 @@
       <c r="G94" s="287"/>
       <c r="H94" s="276"/>
       <c r="I94" s="265"/>
-      <c r="J94" s="361"/>
-      <c r="K94" s="361"/>
-      <c r="L94" s="361"/>
-      <c r="M94" s="361"/>
-      <c r="N94" s="361"/>
+      <c r="J94" s="424"/>
+      <c r="K94" s="424"/>
+      <c r="L94" s="424"/>
+      <c r="M94" s="424"/>
+      <c r="N94" s="424"/>
       <c r="O94" s="39"/>
     </row>
-    <row r="95" spans="2:16" ht="23.25">
+    <row r="95" spans="2:16" ht="24" x14ac:dyDescent="0.15">
       <c r="B95" s="111">
         <v>33</v>
       </c>
@@ -7390,14 +7393,14 @@
       <c r="F95" s="287"/>
       <c r="G95" s="287"/>
       <c r="H95" s="276"/>
-      <c r="J95" s="361"/>
-      <c r="K95" s="361"/>
-      <c r="L95" s="361"/>
-      <c r="M95" s="361"/>
-      <c r="N95" s="361"/>
+      <c r="J95" s="424"/>
+      <c r="K95" s="424"/>
+      <c r="L95" s="424"/>
+      <c r="M95" s="424"/>
+      <c r="N95" s="424"/>
       <c r="O95" s="39"/>
     </row>
-    <row r="96" spans="2:16" ht="23.25">
+    <row r="96" spans="2:16" ht="24" x14ac:dyDescent="0.15">
       <c r="B96" s="111">
         <v>34</v>
       </c>
@@ -7409,14 +7412,14 @@
       <c r="F96" s="276"/>
       <c r="G96" s="276"/>
       <c r="H96" s="276"/>
-      <c r="J96" s="361"/>
-      <c r="K96" s="361"/>
-      <c r="L96" s="361"/>
-      <c r="M96" s="361"/>
-      <c r="N96" s="361"/>
+      <c r="J96" s="424"/>
+      <c r="K96" s="424"/>
+      <c r="L96" s="424"/>
+      <c r="M96" s="424"/>
+      <c r="N96" s="424"/>
       <c r="O96" s="39"/>
     </row>
-    <row r="97" spans="2:15" ht="23.25">
+    <row r="97" spans="2:15" ht="24" x14ac:dyDescent="0.15">
       <c r="B97" s="111"/>
       <c r="C97" s="251"/>
       <c r="D97" s="266"/>
@@ -7424,14 +7427,14 @@
       <c r="F97" s="266"/>
       <c r="G97" s="266"/>
       <c r="H97" s="266"/>
-      <c r="J97" s="361"/>
-      <c r="K97" s="361"/>
-      <c r="L97" s="361"/>
-      <c r="M97" s="361"/>
-      <c r="N97" s="361"/>
+      <c r="J97" s="424"/>
+      <c r="K97" s="424"/>
+      <c r="L97" s="424"/>
+      <c r="M97" s="424"/>
+      <c r="N97" s="424"/>
       <c r="O97" s="39"/>
     </row>
-    <row r="98" spans="2:15" ht="23.25">
+    <row r="98" spans="2:15" ht="22.5" x14ac:dyDescent="0.15">
       <c r="B98" s="111"/>
       <c r="C98" s="251"/>
       <c r="D98" s="251"/>
@@ -7447,7 +7450,7 @@
       <c r="N98" s="267"/>
       <c r="O98" s="39"/>
     </row>
-    <row r="99" spans="2:15" ht="23.25">
+    <row r="99" spans="2:15" ht="22.5" x14ac:dyDescent="0.15">
       <c r="B99" s="111"/>
       <c r="C99" s="251"/>
       <c r="D99" s="251"/>
@@ -7455,14 +7458,14 @@
       <c r="F99" s="251"/>
       <c r="G99" s="251"/>
       <c r="H99" s="251"/>
-      <c r="J99" s="361"/>
-      <c r="K99" s="361"/>
-      <c r="L99" s="361"/>
-      <c r="M99" s="361"/>
-      <c r="N99" s="361"/>
+      <c r="J99" s="424"/>
+      <c r="K99" s="424"/>
+      <c r="L99" s="424"/>
+      <c r="M99" s="424"/>
+      <c r="N99" s="424"/>
       <c r="O99" s="39"/>
     </row>
-    <row r="100" spans="2:15" ht="23.25">
+    <row r="100" spans="2:15" ht="22.5" x14ac:dyDescent="0.15">
       <c r="B100" s="111"/>
       <c r="C100" s="251"/>
       <c r="D100" s="251"/>
@@ -7470,14 +7473,14 @@
       <c r="F100" s="251"/>
       <c r="G100" s="251"/>
       <c r="H100" s="251"/>
-      <c r="J100" s="361"/>
-      <c r="K100" s="361"/>
-      <c r="L100" s="361"/>
-      <c r="M100" s="361"/>
-      <c r="N100" s="361"/>
+      <c r="J100" s="424"/>
+      <c r="K100" s="424"/>
+      <c r="L100" s="424"/>
+      <c r="M100" s="424"/>
+      <c r="N100" s="424"/>
       <c r="O100" s="39"/>
     </row>
-    <row r="101" spans="2:15" ht="23.25">
+    <row r="101" spans="2:15" ht="22.5" x14ac:dyDescent="0.15">
       <c r="B101" s="111"/>
       <c r="C101" s="251"/>
       <c r="D101" s="251"/>
@@ -7485,1324 +7488,1477 @@
       <c r="F101" s="251"/>
       <c r="G101" s="251"/>
       <c r="H101" s="251"/>
-      <c r="J101" s="361"/>
-      <c r="K101" s="361"/>
-      <c r="L101" s="361"/>
-      <c r="M101" s="361"/>
-      <c r="N101" s="361"/>
+      <c r="J101" s="424"/>
+      <c r="K101" s="424"/>
+      <c r="L101" s="424"/>
+      <c r="M101" s="424"/>
+      <c r="N101" s="424"/>
       <c r="O101" s="39"/>
     </row>
-    <row r="102" spans="2:15" ht="23.25">
-      <c r="C102" s="360"/>
-      <c r="D102" s="360"/>
-      <c r="E102" s="360"/>
-      <c r="F102" s="360"/>
-      <c r="G102" s="360"/>
-      <c r="H102" s="360"/>
-      <c r="J102" s="361"/>
-      <c r="K102" s="361"/>
-      <c r="L102" s="361"/>
-      <c r="M102" s="361"/>
-      <c r="N102" s="361"/>
+    <row r="102" spans="2:15" ht="24" x14ac:dyDescent="0.15">
+      <c r="C102" s="423"/>
+      <c r="D102" s="423"/>
+      <c r="E102" s="423"/>
+      <c r="F102" s="423"/>
+      <c r="G102" s="423"/>
+      <c r="H102" s="423"/>
+      <c r="J102" s="424"/>
+      <c r="K102" s="424"/>
+      <c r="L102" s="424"/>
+      <c r="M102" s="424"/>
+      <c r="N102" s="424"/>
       <c r="O102" s="39"/>
     </row>
-    <row r="103" spans="2:15" ht="23.25">
-      <c r="C103" s="360"/>
-      <c r="D103" s="360"/>
-      <c r="E103" s="360"/>
-      <c r="F103" s="360"/>
-      <c r="G103" s="360"/>
-      <c r="H103" s="360"/>
-      <c r="J103" s="361"/>
-      <c r="K103" s="361"/>
-      <c r="L103" s="361"/>
-      <c r="M103" s="361"/>
-      <c r="N103" s="361"/>
+    <row r="103" spans="2:15" ht="24" x14ac:dyDescent="0.15">
+      <c r="C103" s="423"/>
+      <c r="D103" s="423"/>
+      <c r="E103" s="423"/>
+      <c r="F103" s="423"/>
+      <c r="G103" s="423"/>
+      <c r="H103" s="423"/>
+      <c r="J103" s="424"/>
+      <c r="K103" s="424"/>
+      <c r="L103" s="424"/>
+      <c r="M103" s="424"/>
+      <c r="N103" s="424"/>
       <c r="O103" s="39"/>
     </row>
-    <row r="104" spans="2:15" ht="23.25">
-      <c r="C104" s="360"/>
-      <c r="D104" s="360"/>
-      <c r="E104" s="360"/>
-      <c r="F104" s="360"/>
-      <c r="G104" s="360"/>
-      <c r="H104" s="360"/>
-      <c r="J104" s="361"/>
-      <c r="K104" s="361"/>
-      <c r="L104" s="361"/>
-      <c r="M104" s="361"/>
-      <c r="N104" s="361"/>
+    <row r="104" spans="2:15" ht="24" x14ac:dyDescent="0.15">
+      <c r="C104" s="423"/>
+      <c r="D104" s="423"/>
+      <c r="E104" s="423"/>
+      <c r="F104" s="423"/>
+      <c r="G104" s="423"/>
+      <c r="H104" s="423"/>
+      <c r="J104" s="424"/>
+      <c r="K104" s="424"/>
+      <c r="L104" s="424"/>
+      <c r="M104" s="424"/>
+      <c r="N104" s="424"/>
       <c r="O104" s="39"/>
     </row>
-    <row r="105" spans="2:15" ht="23.25">
-      <c r="C105" s="360"/>
-      <c r="D105" s="360"/>
-      <c r="E105" s="360"/>
-      <c r="F105" s="360"/>
-      <c r="G105" s="360"/>
-      <c r="H105" s="360"/>
-      <c r="J105" s="361"/>
-      <c r="K105" s="361"/>
-      <c r="L105" s="361"/>
-      <c r="M105" s="361"/>
-      <c r="N105" s="361"/>
+    <row r="105" spans="2:15" ht="24" x14ac:dyDescent="0.15">
+      <c r="C105" s="423"/>
+      <c r="D105" s="423"/>
+      <c r="E105" s="423"/>
+      <c r="F105" s="423"/>
+      <c r="G105" s="423"/>
+      <c r="H105" s="423"/>
+      <c r="J105" s="424"/>
+      <c r="K105" s="424"/>
+      <c r="L105" s="424"/>
+      <c r="M105" s="424"/>
+      <c r="N105" s="424"/>
       <c r="O105" s="39"/>
     </row>
-    <row r="106" spans="2:15" ht="23.25">
-      <c r="C106" s="360"/>
-      <c r="D106" s="360"/>
-      <c r="E106" s="360"/>
-      <c r="F106" s="360"/>
-      <c r="G106" s="360"/>
-      <c r="H106" s="360"/>
-      <c r="J106" s="361"/>
-      <c r="K106" s="361"/>
-      <c r="L106" s="361"/>
-      <c r="M106" s="361"/>
-      <c r="N106" s="361"/>
+    <row r="106" spans="2:15" ht="24" x14ac:dyDescent="0.15">
+      <c r="C106" s="423"/>
+      <c r="D106" s="423"/>
+      <c r="E106" s="423"/>
+      <c r="F106" s="423"/>
+      <c r="G106" s="423"/>
+      <c r="H106" s="423"/>
+      <c r="J106" s="424"/>
+      <c r="K106" s="424"/>
+      <c r="L106" s="424"/>
+      <c r="M106" s="424"/>
+      <c r="N106" s="424"/>
       <c r="O106" s="39"/>
     </row>
-    <row r="107" spans="2:15" ht="23.25">
-      <c r="C107" s="360"/>
-      <c r="D107" s="360"/>
-      <c r="E107" s="360"/>
-      <c r="F107" s="360"/>
-      <c r="G107" s="360"/>
-      <c r="H107" s="360"/>
-      <c r="J107" s="361"/>
-      <c r="K107" s="361"/>
-      <c r="L107" s="361"/>
-      <c r="M107" s="361"/>
-      <c r="N107" s="361"/>
+    <row r="107" spans="2:15" ht="24" x14ac:dyDescent="0.15">
+      <c r="C107" s="423"/>
+      <c r="D107" s="423"/>
+      <c r="E107" s="423"/>
+      <c r="F107" s="423"/>
+      <c r="G107" s="423"/>
+      <c r="H107" s="423"/>
+      <c r="J107" s="424"/>
+      <c r="K107" s="424"/>
+      <c r="L107" s="424"/>
+      <c r="M107" s="424"/>
+      <c r="N107" s="424"/>
       <c r="O107" s="39"/>
     </row>
-    <row r="108" spans="2:15" ht="23.25">
-      <c r="C108" s="360"/>
-      <c r="D108" s="360"/>
-      <c r="E108" s="360"/>
-      <c r="F108" s="360"/>
-      <c r="G108" s="360"/>
-      <c r="H108" s="360"/>
-      <c r="J108" s="361"/>
-      <c r="K108" s="361"/>
-      <c r="L108" s="361"/>
-      <c r="M108" s="361"/>
-      <c r="N108" s="361"/>
+    <row r="108" spans="2:15" ht="24" x14ac:dyDescent="0.15">
+      <c r="C108" s="423"/>
+      <c r="D108" s="423"/>
+      <c r="E108" s="423"/>
+      <c r="F108" s="423"/>
+      <c r="G108" s="423"/>
+      <c r="H108" s="423"/>
+      <c r="J108" s="424"/>
+      <c r="K108" s="424"/>
+      <c r="L108" s="424"/>
+      <c r="M108" s="424"/>
+      <c r="N108" s="424"/>
       <c r="O108" s="39"/>
     </row>
-    <row r="109" spans="2:15" ht="23.25">
-      <c r="C109" s="360"/>
-      <c r="D109" s="360"/>
-      <c r="E109" s="360"/>
-      <c r="F109" s="360"/>
-      <c r="G109" s="360"/>
-      <c r="H109" s="360"/>
-      <c r="J109" s="361"/>
-      <c r="K109" s="361"/>
-      <c r="L109" s="361"/>
-      <c r="M109" s="361"/>
-      <c r="N109" s="361"/>
+    <row r="109" spans="2:15" ht="24" x14ac:dyDescent="0.15">
+      <c r="C109" s="423"/>
+      <c r="D109" s="423"/>
+      <c r="E109" s="423"/>
+      <c r="F109" s="423"/>
+      <c r="G109" s="423"/>
+      <c r="H109" s="423"/>
+      <c r="J109" s="424"/>
+      <c r="K109" s="424"/>
+      <c r="L109" s="424"/>
+      <c r="M109" s="424"/>
+      <c r="N109" s="424"/>
       <c r="O109" s="39"/>
     </row>
-    <row r="110" spans="2:15" ht="23.25">
-      <c r="C110" s="360"/>
-      <c r="D110" s="360"/>
-      <c r="E110" s="360"/>
-      <c r="F110" s="360"/>
-      <c r="G110" s="360"/>
-      <c r="H110" s="360"/>
-      <c r="J110" s="361"/>
-      <c r="K110" s="361"/>
-      <c r="L110" s="361"/>
-      <c r="M110" s="361"/>
-      <c r="N110" s="361"/>
+    <row r="110" spans="2:15" ht="24" x14ac:dyDescent="0.15">
+      <c r="C110" s="423"/>
+      <c r="D110" s="423"/>
+      <c r="E110" s="423"/>
+      <c r="F110" s="423"/>
+      <c r="G110" s="423"/>
+      <c r="H110" s="423"/>
+      <c r="J110" s="424"/>
+      <c r="K110" s="424"/>
+      <c r="L110" s="424"/>
+      <c r="M110" s="424"/>
+      <c r="N110" s="424"/>
       <c r="O110" s="39"/>
     </row>
-    <row r="111" spans="2:15" ht="23.25">
-      <c r="C111" s="360"/>
-      <c r="D111" s="360"/>
-      <c r="E111" s="360"/>
-      <c r="F111" s="360"/>
-      <c r="G111" s="360"/>
-      <c r="H111" s="360"/>
-      <c r="J111" s="361"/>
-      <c r="K111" s="361"/>
-      <c r="L111" s="361"/>
-      <c r="M111" s="361"/>
-      <c r="N111" s="361"/>
+    <row r="111" spans="2:15" ht="24" x14ac:dyDescent="0.15">
+      <c r="C111" s="423"/>
+      <c r="D111" s="423"/>
+      <c r="E111" s="423"/>
+      <c r="F111" s="423"/>
+      <c r="G111" s="423"/>
+      <c r="H111" s="423"/>
+      <c r="J111" s="424"/>
+      <c r="K111" s="424"/>
+      <c r="L111" s="424"/>
+      <c r="M111" s="424"/>
+      <c r="N111" s="424"/>
       <c r="O111" s="39"/>
     </row>
-    <row r="112" spans="2:15" ht="23.25">
-      <c r="C112" s="360"/>
-      <c r="D112" s="360"/>
-      <c r="E112" s="360"/>
-      <c r="F112" s="360"/>
-      <c r="G112" s="360"/>
-      <c r="H112" s="360"/>
-      <c r="J112" s="361"/>
-      <c r="K112" s="361"/>
-      <c r="L112" s="361"/>
-      <c r="M112" s="361"/>
-      <c r="N112" s="361"/>
+    <row r="112" spans="2:15" ht="24" x14ac:dyDescent="0.15">
+      <c r="C112" s="423"/>
+      <c r="D112" s="423"/>
+      <c r="E112" s="423"/>
+      <c r="F112" s="423"/>
+      <c r="G112" s="423"/>
+      <c r="H112" s="423"/>
+      <c r="J112" s="424"/>
+      <c r="K112" s="424"/>
+      <c r="L112" s="424"/>
+      <c r="M112" s="424"/>
+      <c r="N112" s="424"/>
       <c r="O112" s="39"/>
     </row>
-    <row r="113" spans="3:15" ht="23.25">
-      <c r="C113" s="360"/>
-      <c r="D113" s="360"/>
-      <c r="E113" s="360"/>
-      <c r="F113" s="360"/>
-      <c r="G113" s="360"/>
-      <c r="H113" s="360"/>
-      <c r="J113" s="361"/>
-      <c r="K113" s="361"/>
-      <c r="L113" s="361"/>
-      <c r="M113" s="361"/>
-      <c r="N113" s="361"/>
+    <row r="113" spans="3:15" ht="24" x14ac:dyDescent="0.15">
+      <c r="C113" s="423"/>
+      <c r="D113" s="423"/>
+      <c r="E113" s="423"/>
+      <c r="F113" s="423"/>
+      <c r="G113" s="423"/>
+      <c r="H113" s="423"/>
+      <c r="J113" s="424"/>
+      <c r="K113" s="424"/>
+      <c r="L113" s="424"/>
+      <c r="M113" s="424"/>
+      <c r="N113" s="424"/>
       <c r="O113" s="39"/>
     </row>
-    <row r="114" spans="3:15" ht="23.25">
-      <c r="C114" s="360"/>
-      <c r="D114" s="360"/>
-      <c r="E114" s="360"/>
-      <c r="F114" s="360"/>
-      <c r="G114" s="360"/>
-      <c r="H114" s="360"/>
-      <c r="J114" s="361"/>
-      <c r="K114" s="361"/>
-      <c r="L114" s="361"/>
-      <c r="M114" s="361"/>
-      <c r="N114" s="361"/>
+    <row r="114" spans="3:15" ht="24" x14ac:dyDescent="0.15">
+      <c r="C114" s="423"/>
+      <c r="D114" s="423"/>
+      <c r="E114" s="423"/>
+      <c r="F114" s="423"/>
+      <c r="G114" s="423"/>
+      <c r="H114" s="423"/>
+      <c r="J114" s="424"/>
+      <c r="K114" s="424"/>
+      <c r="L114" s="424"/>
+      <c r="M114" s="424"/>
+      <c r="N114" s="424"/>
       <c r="O114" s="39"/>
     </row>
-    <row r="115" spans="3:15" ht="23.25">
-      <c r="C115" s="360"/>
-      <c r="D115" s="360"/>
-      <c r="E115" s="360"/>
-      <c r="F115" s="360"/>
-      <c r="G115" s="360"/>
-      <c r="H115" s="360"/>
-      <c r="J115" s="361"/>
-      <c r="K115" s="361"/>
-      <c r="L115" s="361"/>
-      <c r="M115" s="361"/>
-      <c r="N115" s="361"/>
+    <row r="115" spans="3:15" ht="24" x14ac:dyDescent="0.15">
+      <c r="C115" s="423"/>
+      <c r="D115" s="423"/>
+      <c r="E115" s="423"/>
+      <c r="F115" s="423"/>
+      <c r="G115" s="423"/>
+      <c r="H115" s="423"/>
+      <c r="J115" s="424"/>
+      <c r="K115" s="424"/>
+      <c r="L115" s="424"/>
+      <c r="M115" s="424"/>
+      <c r="N115" s="424"/>
       <c r="O115" s="39"/>
     </row>
-    <row r="116" spans="3:15" ht="23.25">
-      <c r="C116" s="360"/>
-      <c r="D116" s="360"/>
-      <c r="E116" s="360"/>
-      <c r="F116" s="360"/>
-      <c r="G116" s="360"/>
-      <c r="H116" s="360"/>
-      <c r="J116" s="361"/>
-      <c r="K116" s="361"/>
-      <c r="L116" s="361"/>
-      <c r="M116" s="361"/>
-      <c r="N116" s="361"/>
+    <row r="116" spans="3:15" ht="24" x14ac:dyDescent="0.15">
+      <c r="C116" s="423"/>
+      <c r="D116" s="423"/>
+      <c r="E116" s="423"/>
+      <c r="F116" s="423"/>
+      <c r="G116" s="423"/>
+      <c r="H116" s="423"/>
+      <c r="J116" s="424"/>
+      <c r="K116" s="424"/>
+      <c r="L116" s="424"/>
+      <c r="M116" s="424"/>
+      <c r="N116" s="424"/>
       <c r="O116" s="39"/>
     </row>
-    <row r="117" spans="3:15" ht="23.25">
-      <c r="C117" s="360"/>
-      <c r="D117" s="360"/>
-      <c r="E117" s="360"/>
-      <c r="F117" s="360"/>
-      <c r="G117" s="360"/>
-      <c r="H117" s="360"/>
-      <c r="J117" s="361"/>
-      <c r="K117" s="361"/>
-      <c r="L117" s="361"/>
-      <c r="M117" s="361"/>
-      <c r="N117" s="361"/>
+    <row r="117" spans="3:15" ht="24" x14ac:dyDescent="0.15">
+      <c r="C117" s="423"/>
+      <c r="D117" s="423"/>
+      <c r="E117" s="423"/>
+      <c r="F117" s="423"/>
+      <c r="G117" s="423"/>
+      <c r="H117" s="423"/>
+      <c r="J117" s="424"/>
+      <c r="K117" s="424"/>
+      <c r="L117" s="424"/>
+      <c r="M117" s="424"/>
+      <c r="N117" s="424"/>
       <c r="O117" s="39"/>
     </row>
-    <row r="118" spans="3:15" ht="23.25">
-      <c r="C118" s="360"/>
-      <c r="D118" s="360"/>
-      <c r="E118" s="360"/>
-      <c r="F118" s="360"/>
-      <c r="G118" s="360"/>
-      <c r="H118" s="360"/>
-      <c r="J118" s="361"/>
-      <c r="K118" s="361"/>
-      <c r="L118" s="361"/>
-      <c r="M118" s="361"/>
-      <c r="N118" s="361"/>
+    <row r="118" spans="3:15" ht="24" x14ac:dyDescent="0.15">
+      <c r="C118" s="423"/>
+      <c r="D118" s="423"/>
+      <c r="E118" s="423"/>
+      <c r="F118" s="423"/>
+      <c r="G118" s="423"/>
+      <c r="H118" s="423"/>
+      <c r="J118" s="424"/>
+      <c r="K118" s="424"/>
+      <c r="L118" s="424"/>
+      <c r="M118" s="424"/>
+      <c r="N118" s="424"/>
       <c r="O118" s="39"/>
     </row>
-    <row r="119" spans="3:15" ht="23.25">
-      <c r="C119" s="360"/>
-      <c r="D119" s="360"/>
-      <c r="E119" s="360"/>
-      <c r="F119" s="360"/>
-      <c r="G119" s="360"/>
-      <c r="H119" s="360"/>
-      <c r="J119" s="361"/>
-      <c r="K119" s="361"/>
-      <c r="L119" s="361"/>
-      <c r="M119" s="361"/>
-      <c r="N119" s="361"/>
+    <row r="119" spans="3:15" ht="24" x14ac:dyDescent="0.15">
+      <c r="C119" s="423"/>
+      <c r="D119" s="423"/>
+      <c r="E119" s="423"/>
+      <c r="F119" s="423"/>
+      <c r="G119" s="423"/>
+      <c r="H119" s="423"/>
+      <c r="J119" s="424"/>
+      <c r="K119" s="424"/>
+      <c r="L119" s="424"/>
+      <c r="M119" s="424"/>
+      <c r="N119" s="424"/>
       <c r="O119" s="39"/>
     </row>
-    <row r="120" spans="3:15" ht="23.25">
-      <c r="C120" s="360"/>
-      <c r="D120" s="360"/>
-      <c r="E120" s="360"/>
-      <c r="F120" s="360"/>
-      <c r="G120" s="360"/>
-      <c r="H120" s="360"/>
-      <c r="J120" s="361"/>
-      <c r="K120" s="361"/>
-      <c r="L120" s="361"/>
-      <c r="M120" s="361"/>
-      <c r="N120" s="361"/>
+    <row r="120" spans="3:15" ht="24" x14ac:dyDescent="0.15">
+      <c r="C120" s="423"/>
+      <c r="D120" s="423"/>
+      <c r="E120" s="423"/>
+      <c r="F120" s="423"/>
+      <c r="G120" s="423"/>
+      <c r="H120" s="423"/>
+      <c r="J120" s="424"/>
+      <c r="K120" s="424"/>
+      <c r="L120" s="424"/>
+      <c r="M120" s="424"/>
+      <c r="N120" s="424"/>
       <c r="O120" s="39"/>
     </row>
-    <row r="121" spans="3:15" ht="23.25">
-      <c r="C121" s="360"/>
-      <c r="D121" s="360"/>
-      <c r="E121" s="360"/>
-      <c r="F121" s="360"/>
-      <c r="G121" s="360"/>
-      <c r="H121" s="360"/>
-      <c r="J121" s="361"/>
-      <c r="K121" s="361"/>
-      <c r="L121" s="361"/>
-      <c r="M121" s="361"/>
-      <c r="N121" s="361"/>
+    <row r="121" spans="3:15" ht="24" x14ac:dyDescent="0.15">
+      <c r="C121" s="423"/>
+      <c r="D121" s="423"/>
+      <c r="E121" s="423"/>
+      <c r="F121" s="423"/>
+      <c r="G121" s="423"/>
+      <c r="H121" s="423"/>
+      <c r="J121" s="424"/>
+      <c r="K121" s="424"/>
+      <c r="L121" s="424"/>
+      <c r="M121" s="424"/>
+      <c r="N121" s="424"/>
       <c r="O121" s="39"/>
     </row>
-    <row r="122" spans="3:15" ht="23.25">
-      <c r="C122" s="360"/>
-      <c r="D122" s="360"/>
-      <c r="E122" s="360"/>
-      <c r="F122" s="360"/>
-      <c r="G122" s="360"/>
-      <c r="H122" s="360"/>
-      <c r="J122" s="361"/>
-      <c r="K122" s="361"/>
-      <c r="L122" s="361"/>
-      <c r="M122" s="361"/>
-      <c r="N122" s="361"/>
+    <row r="122" spans="3:15" ht="24" x14ac:dyDescent="0.15">
+      <c r="C122" s="423"/>
+      <c r="D122" s="423"/>
+      <c r="E122" s="423"/>
+      <c r="F122" s="423"/>
+      <c r="G122" s="423"/>
+      <c r="H122" s="423"/>
+      <c r="J122" s="424"/>
+      <c r="K122" s="424"/>
+      <c r="L122" s="424"/>
+      <c r="M122" s="424"/>
+      <c r="N122" s="424"/>
       <c r="O122" s="39"/>
     </row>
-    <row r="123" spans="3:15" ht="23.25">
-      <c r="C123" s="360"/>
-      <c r="D123" s="360"/>
-      <c r="E123" s="360"/>
-      <c r="F123" s="360"/>
-      <c r="G123" s="360"/>
-      <c r="H123" s="360"/>
-      <c r="J123" s="361"/>
-      <c r="K123" s="361"/>
-      <c r="L123" s="361"/>
-      <c r="M123" s="361"/>
-      <c r="N123" s="361"/>
+    <row r="123" spans="3:15" ht="24" x14ac:dyDescent="0.15">
+      <c r="C123" s="423"/>
+      <c r="D123" s="423"/>
+      <c r="E123" s="423"/>
+      <c r="F123" s="423"/>
+      <c r="G123" s="423"/>
+      <c r="H123" s="423"/>
+      <c r="J123" s="424"/>
+      <c r="K123" s="424"/>
+      <c r="L123" s="424"/>
+      <c r="M123" s="424"/>
+      <c r="N123" s="424"/>
       <c r="O123" s="39"/>
     </row>
-    <row r="124" spans="3:15" ht="23.25">
-      <c r="C124" s="360"/>
-      <c r="D124" s="360"/>
-      <c r="E124" s="360"/>
-      <c r="F124" s="360"/>
-      <c r="G124" s="360"/>
-      <c r="H124" s="360"/>
-      <c r="J124" s="361"/>
-      <c r="K124" s="361"/>
-      <c r="L124" s="361"/>
-      <c r="M124" s="361"/>
-      <c r="N124" s="361"/>
+    <row r="124" spans="3:15" ht="24" x14ac:dyDescent="0.15">
+      <c r="C124" s="423"/>
+      <c r="D124" s="423"/>
+      <c r="E124" s="423"/>
+      <c r="F124" s="423"/>
+      <c r="G124" s="423"/>
+      <c r="H124" s="423"/>
+      <c r="J124" s="424"/>
+      <c r="K124" s="424"/>
+      <c r="L124" s="424"/>
+      <c r="M124" s="424"/>
+      <c r="N124" s="424"/>
       <c r="O124" s="39"/>
     </row>
-    <row r="125" spans="3:15" ht="23.25">
-      <c r="C125" s="360"/>
-      <c r="D125" s="360"/>
-      <c r="E125" s="360"/>
-      <c r="F125" s="360"/>
-      <c r="G125" s="360"/>
-      <c r="H125" s="360"/>
-      <c r="J125" s="361"/>
-      <c r="K125" s="361"/>
-      <c r="L125" s="361"/>
-      <c r="M125" s="361"/>
-      <c r="N125" s="361"/>
+    <row r="125" spans="3:15" ht="24" x14ac:dyDescent="0.15">
+      <c r="C125" s="423"/>
+      <c r="D125" s="423"/>
+      <c r="E125" s="423"/>
+      <c r="F125" s="423"/>
+      <c r="G125" s="423"/>
+      <c r="H125" s="423"/>
+      <c r="J125" s="424"/>
+      <c r="K125" s="424"/>
+      <c r="L125" s="424"/>
+      <c r="M125" s="424"/>
+      <c r="N125" s="424"/>
       <c r="O125" s="39"/>
     </row>
-    <row r="126" spans="3:15" ht="23.25">
-      <c r="C126" s="360"/>
-      <c r="D126" s="360"/>
-      <c r="E126" s="360"/>
-      <c r="F126" s="360"/>
-      <c r="G126" s="360"/>
-      <c r="H126" s="360"/>
-      <c r="J126" s="361"/>
-      <c r="K126" s="361"/>
-      <c r="L126" s="361"/>
-      <c r="M126" s="361"/>
-      <c r="N126" s="361"/>
+    <row r="126" spans="3:15" ht="24" x14ac:dyDescent="0.15">
+      <c r="C126" s="423"/>
+      <c r="D126" s="423"/>
+      <c r="E126" s="423"/>
+      <c r="F126" s="423"/>
+      <c r="G126" s="423"/>
+      <c r="H126" s="423"/>
+      <c r="J126" s="424"/>
+      <c r="K126" s="424"/>
+      <c r="L126" s="424"/>
+      <c r="M126" s="424"/>
+      <c r="N126" s="424"/>
       <c r="O126" s="39"/>
     </row>
-    <row r="127" spans="3:15" ht="23.25">
-      <c r="C127" s="360"/>
-      <c r="D127" s="360"/>
-      <c r="E127" s="360"/>
-      <c r="F127" s="360"/>
-      <c r="G127" s="360"/>
-      <c r="H127" s="360"/>
-      <c r="J127" s="361"/>
-      <c r="K127" s="361"/>
-      <c r="L127" s="361"/>
-      <c r="M127" s="361"/>
-      <c r="N127" s="361"/>
+    <row r="127" spans="3:15" ht="24" x14ac:dyDescent="0.15">
+      <c r="C127" s="423"/>
+      <c r="D127" s="423"/>
+      <c r="E127" s="423"/>
+      <c r="F127" s="423"/>
+      <c r="G127" s="423"/>
+      <c r="H127" s="423"/>
+      <c r="J127" s="424"/>
+      <c r="K127" s="424"/>
+      <c r="L127" s="424"/>
+      <c r="M127" s="424"/>
+      <c r="N127" s="424"/>
       <c r="O127" s="39"/>
     </row>
-    <row r="128" spans="3:15" ht="23.25">
-      <c r="C128" s="360"/>
-      <c r="D128" s="360"/>
-      <c r="E128" s="360"/>
-      <c r="F128" s="360"/>
-      <c r="G128" s="360"/>
-      <c r="H128" s="360"/>
-      <c r="J128" s="361"/>
-      <c r="K128" s="361"/>
-      <c r="L128" s="361"/>
-      <c r="M128" s="361"/>
-      <c r="N128" s="361"/>
+    <row r="128" spans="3:15" ht="24" x14ac:dyDescent="0.15">
+      <c r="C128" s="423"/>
+      <c r="D128" s="423"/>
+      <c r="E128" s="423"/>
+      <c r="F128" s="423"/>
+      <c r="G128" s="423"/>
+      <c r="H128" s="423"/>
+      <c r="J128" s="424"/>
+      <c r="K128" s="424"/>
+      <c r="L128" s="424"/>
+      <c r="M128" s="424"/>
+      <c r="N128" s="424"/>
       <c r="O128" s="39"/>
     </row>
-    <row r="129" spans="3:15" ht="23.25">
-      <c r="C129" s="360"/>
-      <c r="D129" s="360"/>
-      <c r="E129" s="360"/>
-      <c r="F129" s="360"/>
-      <c r="G129" s="360"/>
-      <c r="H129" s="360"/>
-      <c r="J129" s="361"/>
-      <c r="K129" s="361"/>
-      <c r="L129" s="361"/>
-      <c r="M129" s="361"/>
-      <c r="N129" s="361"/>
+    <row r="129" spans="3:15" ht="24" x14ac:dyDescent="0.15">
+      <c r="C129" s="423"/>
+      <c r="D129" s="423"/>
+      <c r="E129" s="423"/>
+      <c r="F129" s="423"/>
+      <c r="G129" s="423"/>
+      <c r="H129" s="423"/>
+      <c r="J129" s="424"/>
+      <c r="K129" s="424"/>
+      <c r="L129" s="424"/>
+      <c r="M129" s="424"/>
+      <c r="N129" s="424"/>
       <c r="O129" s="39"/>
     </row>
-    <row r="130" spans="3:15" ht="23.25">
-      <c r="C130" s="360"/>
-      <c r="D130" s="360"/>
-      <c r="E130" s="360"/>
-      <c r="F130" s="360"/>
-      <c r="G130" s="360"/>
-      <c r="H130" s="360"/>
-      <c r="J130" s="361"/>
-      <c r="K130" s="361"/>
-      <c r="L130" s="361"/>
-      <c r="M130" s="361"/>
-      <c r="N130" s="361"/>
+    <row r="130" spans="3:15" ht="24" x14ac:dyDescent="0.15">
+      <c r="C130" s="423"/>
+      <c r="D130" s="423"/>
+      <c r="E130" s="423"/>
+      <c r="F130" s="423"/>
+      <c r="G130" s="423"/>
+      <c r="H130" s="423"/>
+      <c r="J130" s="424"/>
+      <c r="K130" s="424"/>
+      <c r="L130" s="424"/>
+      <c r="M130" s="424"/>
+      <c r="N130" s="424"/>
       <c r="O130" s="39"/>
     </row>
-    <row r="131" spans="3:15" ht="23.25">
-      <c r="C131" s="360"/>
-      <c r="D131" s="360"/>
-      <c r="E131" s="360"/>
-      <c r="F131" s="360"/>
-      <c r="G131" s="360"/>
-      <c r="H131" s="360"/>
-      <c r="J131" s="361"/>
-      <c r="K131" s="361"/>
-      <c r="L131" s="361"/>
-      <c r="M131" s="361"/>
-      <c r="N131" s="361"/>
+    <row r="131" spans="3:15" ht="24" x14ac:dyDescent="0.15">
+      <c r="C131" s="423"/>
+      <c r="D131" s="423"/>
+      <c r="E131" s="423"/>
+      <c r="F131" s="423"/>
+      <c r="G131" s="423"/>
+      <c r="H131" s="423"/>
+      <c r="J131" s="424"/>
+      <c r="K131" s="424"/>
+      <c r="L131" s="424"/>
+      <c r="M131" s="424"/>
+      <c r="N131" s="424"/>
       <c r="O131" s="39"/>
     </row>
-    <row r="132" spans="3:15" ht="23.25">
-      <c r="C132" s="360"/>
-      <c r="D132" s="360"/>
-      <c r="E132" s="360"/>
-      <c r="F132" s="360"/>
-      <c r="G132" s="360"/>
-      <c r="H132" s="360"/>
-      <c r="J132" s="361"/>
-      <c r="K132" s="361"/>
-      <c r="L132" s="361"/>
-      <c r="M132" s="361"/>
-      <c r="N132" s="361"/>
+    <row r="132" spans="3:15" ht="24" x14ac:dyDescent="0.15">
+      <c r="C132" s="423"/>
+      <c r="D132" s="423"/>
+      <c r="E132" s="423"/>
+      <c r="F132" s="423"/>
+      <c r="G132" s="423"/>
+      <c r="H132" s="423"/>
+      <c r="J132" s="424"/>
+      <c r="K132" s="424"/>
+      <c r="L132" s="424"/>
+      <c r="M132" s="424"/>
+      <c r="N132" s="424"/>
       <c r="O132" s="39"/>
     </row>
-    <row r="133" spans="3:15" ht="23.25">
-      <c r="C133" s="360"/>
-      <c r="D133" s="360"/>
-      <c r="E133" s="360"/>
-      <c r="F133" s="360"/>
-      <c r="G133" s="360"/>
-      <c r="H133" s="360"/>
-      <c r="J133" s="361"/>
-      <c r="K133" s="361"/>
-      <c r="L133" s="361"/>
-      <c r="M133" s="361"/>
-      <c r="N133" s="361"/>
+    <row r="133" spans="3:15" ht="24" x14ac:dyDescent="0.15">
+      <c r="C133" s="423"/>
+      <c r="D133" s="423"/>
+      <c r="E133" s="423"/>
+      <c r="F133" s="423"/>
+      <c r="G133" s="423"/>
+      <c r="H133" s="423"/>
+      <c r="J133" s="424"/>
+      <c r="K133" s="424"/>
+      <c r="L133" s="424"/>
+      <c r="M133" s="424"/>
+      <c r="N133" s="424"/>
       <c r="O133" s="39"/>
     </row>
-    <row r="134" spans="3:15" ht="23.25">
-      <c r="C134" s="360"/>
-      <c r="D134" s="360"/>
-      <c r="E134" s="360"/>
-      <c r="F134" s="360"/>
-      <c r="G134" s="360"/>
-      <c r="H134" s="360"/>
-      <c r="J134" s="361"/>
-      <c r="K134" s="361"/>
-      <c r="L134" s="361"/>
-      <c r="M134" s="361"/>
-      <c r="N134" s="361"/>
+    <row r="134" spans="3:15" ht="24" x14ac:dyDescent="0.15">
+      <c r="C134" s="423"/>
+      <c r="D134" s="423"/>
+      <c r="E134" s="423"/>
+      <c r="F134" s="423"/>
+      <c r="G134" s="423"/>
+      <c r="H134" s="423"/>
+      <c r="J134" s="424"/>
+      <c r="K134" s="424"/>
+      <c r="L134" s="424"/>
+      <c r="M134" s="424"/>
+      <c r="N134" s="424"/>
       <c r="O134" s="39"/>
     </row>
-    <row r="135" spans="3:15" ht="23.25">
-      <c r="C135" s="360"/>
-      <c r="D135" s="360"/>
-      <c r="E135" s="360"/>
-      <c r="F135" s="360"/>
-      <c r="G135" s="360"/>
-      <c r="H135" s="360"/>
-      <c r="J135" s="361"/>
-      <c r="K135" s="361"/>
-      <c r="L135" s="361"/>
-      <c r="M135" s="361"/>
-      <c r="N135" s="361"/>
+    <row r="135" spans="3:15" ht="24" x14ac:dyDescent="0.15">
+      <c r="C135" s="423"/>
+      <c r="D135" s="423"/>
+      <c r="E135" s="423"/>
+      <c r="F135" s="423"/>
+      <c r="G135" s="423"/>
+      <c r="H135" s="423"/>
+      <c r="J135" s="424"/>
+      <c r="K135" s="424"/>
+      <c r="L135" s="424"/>
+      <c r="M135" s="424"/>
+      <c r="N135" s="424"/>
       <c r="O135" s="39"/>
     </row>
-    <row r="136" spans="3:15" ht="23.25">
-      <c r="C136" s="360"/>
-      <c r="D136" s="360"/>
-      <c r="E136" s="360"/>
-      <c r="F136" s="360"/>
-      <c r="G136" s="360"/>
-      <c r="H136" s="360"/>
-      <c r="J136" s="361"/>
-      <c r="K136" s="361"/>
-      <c r="L136" s="361"/>
-      <c r="M136" s="361"/>
-      <c r="N136" s="361"/>
+    <row r="136" spans="3:15" ht="24" x14ac:dyDescent="0.15">
+      <c r="C136" s="423"/>
+      <c r="D136" s="423"/>
+      <c r="E136" s="423"/>
+      <c r="F136" s="423"/>
+      <c r="G136" s="423"/>
+      <c r="H136" s="423"/>
+      <c r="J136" s="424"/>
+      <c r="K136" s="424"/>
+      <c r="L136" s="424"/>
+      <c r="M136" s="424"/>
+      <c r="N136" s="424"/>
       <c r="O136" s="39"/>
     </row>
-    <row r="137" spans="3:15" ht="23.25">
-      <c r="C137" s="360"/>
-      <c r="D137" s="360"/>
-      <c r="E137" s="360"/>
-      <c r="F137" s="360"/>
-      <c r="G137" s="360"/>
-      <c r="H137" s="360"/>
-      <c r="J137" s="361"/>
-      <c r="K137" s="361"/>
-      <c r="L137" s="361"/>
-      <c r="M137" s="361"/>
-      <c r="N137" s="361"/>
+    <row r="137" spans="3:15" ht="24" x14ac:dyDescent="0.15">
+      <c r="C137" s="423"/>
+      <c r="D137" s="423"/>
+      <c r="E137" s="423"/>
+      <c r="F137" s="423"/>
+      <c r="G137" s="423"/>
+      <c r="H137" s="423"/>
+      <c r="J137" s="424"/>
+      <c r="K137" s="424"/>
+      <c r="L137" s="424"/>
+      <c r="M137" s="424"/>
+      <c r="N137" s="424"/>
       <c r="O137" s="39"/>
     </row>
-    <row r="138" spans="3:15" ht="23.25">
-      <c r="C138" s="360"/>
-      <c r="D138" s="360"/>
-      <c r="E138" s="360"/>
-      <c r="F138" s="360"/>
-      <c r="G138" s="360"/>
-      <c r="H138" s="360"/>
-      <c r="J138" s="361"/>
-      <c r="K138" s="361"/>
-      <c r="L138" s="361"/>
-      <c r="M138" s="361"/>
-      <c r="N138" s="361"/>
+    <row r="138" spans="3:15" ht="24" x14ac:dyDescent="0.15">
+      <c r="C138" s="423"/>
+      <c r="D138" s="423"/>
+      <c r="E138" s="423"/>
+      <c r="F138" s="423"/>
+      <c r="G138" s="423"/>
+      <c r="H138" s="423"/>
+      <c r="J138" s="424"/>
+      <c r="K138" s="424"/>
+      <c r="L138" s="424"/>
+      <c r="M138" s="424"/>
+      <c r="N138" s="424"/>
       <c r="O138" s="39"/>
     </row>
-    <row r="139" spans="3:15" ht="23.25">
-      <c r="C139" s="360"/>
-      <c r="D139" s="360"/>
-      <c r="E139" s="360"/>
-      <c r="F139" s="360"/>
-      <c r="G139" s="360"/>
-      <c r="H139" s="360"/>
-      <c r="J139" s="361"/>
-      <c r="K139" s="361"/>
-      <c r="L139" s="361"/>
-      <c r="M139" s="361"/>
-      <c r="N139" s="361"/>
+    <row r="139" spans="3:15" ht="24" x14ac:dyDescent="0.15">
+      <c r="C139" s="423"/>
+      <c r="D139" s="423"/>
+      <c r="E139" s="423"/>
+      <c r="F139" s="423"/>
+      <c r="G139" s="423"/>
+      <c r="H139" s="423"/>
+      <c r="J139" s="424"/>
+      <c r="K139" s="424"/>
+      <c r="L139" s="424"/>
+      <c r="M139" s="424"/>
+      <c r="N139" s="424"/>
       <c r="O139" s="39"/>
     </row>
-    <row r="140" spans="3:15" ht="23.25">
-      <c r="C140" s="360"/>
-      <c r="D140" s="360"/>
-      <c r="E140" s="360"/>
-      <c r="F140" s="360"/>
-      <c r="G140" s="360"/>
-      <c r="H140" s="360"/>
-      <c r="J140" s="361"/>
-      <c r="K140" s="361"/>
-      <c r="L140" s="361"/>
-      <c r="M140" s="361"/>
-      <c r="N140" s="361"/>
+    <row r="140" spans="3:15" ht="24" x14ac:dyDescent="0.15">
+      <c r="C140" s="423"/>
+      <c r="D140" s="423"/>
+      <c r="E140" s="423"/>
+      <c r="F140" s="423"/>
+      <c r="G140" s="423"/>
+      <c r="H140" s="423"/>
+      <c r="J140" s="424"/>
+      <c r="K140" s="424"/>
+      <c r="L140" s="424"/>
+      <c r="M140" s="424"/>
+      <c r="N140" s="424"/>
       <c r="O140" s="39"/>
     </row>
-    <row r="141" spans="3:15" ht="23.25">
-      <c r="C141" s="360"/>
-      <c r="D141" s="360"/>
-      <c r="E141" s="360"/>
-      <c r="F141" s="360"/>
-      <c r="G141" s="360"/>
-      <c r="H141" s="360"/>
-      <c r="J141" s="361"/>
-      <c r="K141" s="361"/>
-      <c r="L141" s="361"/>
-      <c r="M141" s="361"/>
-      <c r="N141" s="361"/>
+    <row r="141" spans="3:15" ht="24" x14ac:dyDescent="0.15">
+      <c r="C141" s="423"/>
+      <c r="D141" s="423"/>
+      <c r="E141" s="423"/>
+      <c r="F141" s="423"/>
+      <c r="G141" s="423"/>
+      <c r="H141" s="423"/>
+      <c r="J141" s="424"/>
+      <c r="K141" s="424"/>
+      <c r="L141" s="424"/>
+      <c r="M141" s="424"/>
+      <c r="N141" s="424"/>
       <c r="O141" s="39"/>
     </row>
-    <row r="142" spans="3:15" ht="23.25">
-      <c r="C142" s="360"/>
-      <c r="D142" s="360"/>
-      <c r="E142" s="360"/>
-      <c r="F142" s="360"/>
-      <c r="G142" s="360"/>
-      <c r="H142" s="360"/>
-      <c r="J142" s="361"/>
-      <c r="K142" s="361"/>
-      <c r="L142" s="361"/>
-      <c r="M142" s="361"/>
-      <c r="N142" s="361"/>
+    <row r="142" spans="3:15" ht="24" x14ac:dyDescent="0.15">
+      <c r="C142" s="423"/>
+      <c r="D142" s="423"/>
+      <c r="E142" s="423"/>
+      <c r="F142" s="423"/>
+      <c r="G142" s="423"/>
+      <c r="H142" s="423"/>
+      <c r="J142" s="424"/>
+      <c r="K142" s="424"/>
+      <c r="L142" s="424"/>
+      <c r="M142" s="424"/>
+      <c r="N142" s="424"/>
       <c r="O142" s="39"/>
     </row>
-    <row r="143" spans="3:15" ht="23.25">
-      <c r="C143" s="360"/>
-      <c r="D143" s="360"/>
-      <c r="E143" s="360"/>
-      <c r="F143" s="360"/>
-      <c r="G143" s="360"/>
-      <c r="H143" s="360"/>
-      <c r="J143" s="361"/>
-      <c r="K143" s="361"/>
-      <c r="L143" s="361"/>
-      <c r="M143" s="361"/>
-      <c r="N143" s="361"/>
+    <row r="143" spans="3:15" ht="24" x14ac:dyDescent="0.15">
+      <c r="C143" s="423"/>
+      <c r="D143" s="423"/>
+      <c r="E143" s="423"/>
+      <c r="F143" s="423"/>
+      <c r="G143" s="423"/>
+      <c r="H143" s="423"/>
+      <c r="J143" s="424"/>
+      <c r="K143" s="424"/>
+      <c r="L143" s="424"/>
+      <c r="M143" s="424"/>
+      <c r="N143" s="424"/>
       <c r="O143" s="39"/>
     </row>
-    <row r="144" spans="3:15" ht="23.25">
-      <c r="C144" s="360"/>
-      <c r="D144" s="360"/>
-      <c r="E144" s="360"/>
-      <c r="F144" s="360"/>
-      <c r="G144" s="360"/>
-      <c r="H144" s="360"/>
-      <c r="J144" s="361"/>
-      <c r="K144" s="361"/>
-      <c r="L144" s="361"/>
-      <c r="M144" s="361"/>
-      <c r="N144" s="361"/>
+    <row r="144" spans="3:15" ht="24" x14ac:dyDescent="0.15">
+      <c r="C144" s="423"/>
+      <c r="D144" s="423"/>
+      <c r="E144" s="423"/>
+      <c r="F144" s="423"/>
+      <c r="G144" s="423"/>
+      <c r="H144" s="423"/>
+      <c r="J144" s="424"/>
+      <c r="K144" s="424"/>
+      <c r="L144" s="424"/>
+      <c r="M144" s="424"/>
+      <c r="N144" s="424"/>
       <c r="O144" s="39"/>
     </row>
-    <row r="145" spans="3:15" ht="23.25">
-      <c r="C145" s="360"/>
-      <c r="D145" s="360"/>
-      <c r="E145" s="360"/>
-      <c r="F145" s="360"/>
-      <c r="G145" s="360"/>
-      <c r="H145" s="360"/>
-      <c r="J145" s="361"/>
-      <c r="K145" s="361"/>
-      <c r="L145" s="361"/>
-      <c r="M145" s="361"/>
-      <c r="N145" s="361"/>
+    <row r="145" spans="3:15" ht="24" x14ac:dyDescent="0.15">
+      <c r="C145" s="423"/>
+      <c r="D145" s="423"/>
+      <c r="E145" s="423"/>
+      <c r="F145" s="423"/>
+      <c r="G145" s="423"/>
+      <c r="H145" s="423"/>
+      <c r="J145" s="424"/>
+      <c r="K145" s="424"/>
+      <c r="L145" s="424"/>
+      <c r="M145" s="424"/>
+      <c r="N145" s="424"/>
       <c r="O145" s="39"/>
     </row>
-    <row r="146" spans="3:15" ht="23.25">
-      <c r="C146" s="360"/>
-      <c r="D146" s="360"/>
-      <c r="E146" s="360"/>
-      <c r="F146" s="360"/>
-      <c r="G146" s="360"/>
-      <c r="H146" s="360"/>
-      <c r="J146" s="361"/>
-      <c r="K146" s="361"/>
-      <c r="L146" s="361"/>
-      <c r="M146" s="361"/>
-      <c r="N146" s="361"/>
+    <row r="146" spans="3:15" ht="24" x14ac:dyDescent="0.15">
+      <c r="C146" s="423"/>
+      <c r="D146" s="423"/>
+      <c r="E146" s="423"/>
+      <c r="F146" s="423"/>
+      <c r="G146" s="423"/>
+      <c r="H146" s="423"/>
+      <c r="J146" s="424"/>
+      <c r="K146" s="424"/>
+      <c r="L146" s="424"/>
+      <c r="M146" s="424"/>
+      <c r="N146" s="424"/>
       <c r="O146" s="39"/>
     </row>
-    <row r="147" spans="3:15" ht="23.25">
-      <c r="C147" s="360"/>
-      <c r="D147" s="360"/>
-      <c r="E147" s="360"/>
-      <c r="F147" s="360"/>
-      <c r="G147" s="360"/>
-      <c r="H147" s="360"/>
-      <c r="J147" s="361"/>
-      <c r="K147" s="361"/>
-      <c r="L147" s="361"/>
-      <c r="M147" s="361"/>
-      <c r="N147" s="361"/>
+    <row r="147" spans="3:15" ht="24" x14ac:dyDescent="0.15">
+      <c r="C147" s="423"/>
+      <c r="D147" s="423"/>
+      <c r="E147" s="423"/>
+      <c r="F147" s="423"/>
+      <c r="G147" s="423"/>
+      <c r="H147" s="423"/>
+      <c r="J147" s="424"/>
+      <c r="K147" s="424"/>
+      <c r="L147" s="424"/>
+      <c r="M147" s="424"/>
+      <c r="N147" s="424"/>
       <c r="O147" s="39"/>
     </row>
-    <row r="148" spans="3:15" ht="23.25">
-      <c r="C148" s="360"/>
-      <c r="D148" s="360"/>
-      <c r="E148" s="360"/>
-      <c r="F148" s="360"/>
-      <c r="G148" s="360"/>
-      <c r="H148" s="360"/>
-      <c r="J148" s="361"/>
-      <c r="K148" s="361"/>
-      <c r="L148" s="361"/>
-      <c r="M148" s="361"/>
-      <c r="N148" s="361"/>
+    <row r="148" spans="3:15" ht="24" x14ac:dyDescent="0.15">
+      <c r="C148" s="423"/>
+      <c r="D148" s="423"/>
+      <c r="E148" s="423"/>
+      <c r="F148" s="423"/>
+      <c r="G148" s="423"/>
+      <c r="H148" s="423"/>
+      <c r="J148" s="424"/>
+      <c r="K148" s="424"/>
+      <c r="L148" s="424"/>
+      <c r="M148" s="424"/>
+      <c r="N148" s="424"/>
       <c r="O148" s="39"/>
     </row>
-    <row r="149" spans="3:15" ht="23.25">
-      <c r="C149" s="360"/>
-      <c r="D149" s="360"/>
-      <c r="E149" s="360"/>
-      <c r="F149" s="360"/>
-      <c r="G149" s="360"/>
-      <c r="H149" s="360"/>
-      <c r="J149" s="361"/>
-      <c r="K149" s="361"/>
-      <c r="L149" s="361"/>
-      <c r="M149" s="361"/>
-      <c r="N149" s="361"/>
+    <row r="149" spans="3:15" ht="24" x14ac:dyDescent="0.15">
+      <c r="C149" s="423"/>
+      <c r="D149" s="423"/>
+      <c r="E149" s="423"/>
+      <c r="F149" s="423"/>
+      <c r="G149" s="423"/>
+      <c r="H149" s="423"/>
+      <c r="J149" s="424"/>
+      <c r="K149" s="424"/>
+      <c r="L149" s="424"/>
+      <c r="M149" s="424"/>
+      <c r="N149" s="424"/>
       <c r="O149" s="39"/>
     </row>
-    <row r="150" spans="3:15" ht="23.25">
-      <c r="C150" s="360"/>
-      <c r="D150" s="360"/>
-      <c r="E150" s="360"/>
-      <c r="F150" s="360"/>
-      <c r="G150" s="360"/>
-      <c r="H150" s="360"/>
-      <c r="J150" s="361"/>
-      <c r="K150" s="361"/>
-      <c r="L150" s="361"/>
-      <c r="M150" s="361"/>
-      <c r="N150" s="361"/>
+    <row r="150" spans="3:15" ht="24" x14ac:dyDescent="0.15">
+      <c r="C150" s="423"/>
+      <c r="D150" s="423"/>
+      <c r="E150" s="423"/>
+      <c r="F150" s="423"/>
+      <c r="G150" s="423"/>
+      <c r="H150" s="423"/>
+      <c r="J150" s="424"/>
+      <c r="K150" s="424"/>
+      <c r="L150" s="424"/>
+      <c r="M150" s="424"/>
+      <c r="N150" s="424"/>
       <c r="O150" s="39"/>
     </row>
-    <row r="151" spans="3:15" ht="23.25">
-      <c r="C151" s="360"/>
-      <c r="D151" s="360"/>
-      <c r="E151" s="360"/>
-      <c r="F151" s="360"/>
-      <c r="G151" s="360"/>
-      <c r="H151" s="360"/>
-      <c r="J151" s="361"/>
-      <c r="K151" s="361"/>
-      <c r="L151" s="361"/>
-      <c r="M151" s="361"/>
-      <c r="N151" s="361"/>
+    <row r="151" spans="3:15" ht="24" x14ac:dyDescent="0.15">
+      <c r="C151" s="423"/>
+      <c r="D151" s="423"/>
+      <c r="E151" s="423"/>
+      <c r="F151" s="423"/>
+      <c r="G151" s="423"/>
+      <c r="H151" s="423"/>
+      <c r="J151" s="424"/>
+      <c r="K151" s="424"/>
+      <c r="L151" s="424"/>
+      <c r="M151" s="424"/>
+      <c r="N151" s="424"/>
       <c r="O151" s="39"/>
     </row>
-    <row r="152" spans="3:15" ht="23.25">
-      <c r="C152" s="360"/>
-      <c r="D152" s="360"/>
-      <c r="E152" s="360"/>
-      <c r="F152" s="360"/>
-      <c r="G152" s="360"/>
-      <c r="H152" s="360"/>
-      <c r="J152" s="361"/>
-      <c r="K152" s="361"/>
-      <c r="L152" s="361"/>
-      <c r="M152" s="361"/>
-      <c r="N152" s="361"/>
+    <row r="152" spans="3:15" ht="24" x14ac:dyDescent="0.15">
+      <c r="C152" s="423"/>
+      <c r="D152" s="423"/>
+      <c r="E152" s="423"/>
+      <c r="F152" s="423"/>
+      <c r="G152" s="423"/>
+      <c r="H152" s="423"/>
+      <c r="J152" s="424"/>
+      <c r="K152" s="424"/>
+      <c r="L152" s="424"/>
+      <c r="M152" s="424"/>
+      <c r="N152" s="424"/>
       <c r="O152" s="39"/>
     </row>
-    <row r="153" spans="3:15" ht="23.25">
-      <c r="C153" s="360"/>
-      <c r="D153" s="360"/>
-      <c r="E153" s="360"/>
-      <c r="F153" s="360"/>
-      <c r="G153" s="360"/>
-      <c r="H153" s="360"/>
-      <c r="J153" s="361"/>
-      <c r="K153" s="361"/>
-      <c r="L153" s="361"/>
-      <c r="M153" s="361"/>
-      <c r="N153" s="361"/>
+    <row r="153" spans="3:15" ht="24" x14ac:dyDescent="0.15">
+      <c r="C153" s="423"/>
+      <c r="D153" s="423"/>
+      <c r="E153" s="423"/>
+      <c r="F153" s="423"/>
+      <c r="G153" s="423"/>
+      <c r="H153" s="423"/>
+      <c r="J153" s="424"/>
+      <c r="K153" s="424"/>
+      <c r="L153" s="424"/>
+      <c r="M153" s="424"/>
+      <c r="N153" s="424"/>
       <c r="O153" s="39"/>
     </row>
-    <row r="154" spans="3:15" ht="23.25">
-      <c r="C154" s="360"/>
-      <c r="D154" s="360"/>
-      <c r="E154" s="360"/>
-      <c r="F154" s="360"/>
-      <c r="G154" s="360"/>
-      <c r="H154" s="360"/>
-      <c r="J154" s="361"/>
-      <c r="K154" s="361"/>
-      <c r="L154" s="361"/>
-      <c r="M154" s="361"/>
-      <c r="N154" s="361"/>
+    <row r="154" spans="3:15" ht="24" x14ac:dyDescent="0.15">
+      <c r="C154" s="423"/>
+      <c r="D154" s="423"/>
+      <c r="E154" s="423"/>
+      <c r="F154" s="423"/>
+      <c r="G154" s="423"/>
+      <c r="H154" s="423"/>
+      <c r="J154" s="424"/>
+      <c r="K154" s="424"/>
+      <c r="L154" s="424"/>
+      <c r="M154" s="424"/>
+      <c r="N154" s="424"/>
       <c r="O154" s="39"/>
     </row>
-    <row r="155" spans="3:15" ht="23.25">
-      <c r="C155" s="360"/>
-      <c r="D155" s="360"/>
-      <c r="E155" s="360"/>
-      <c r="F155" s="360"/>
-      <c r="G155" s="360"/>
-      <c r="H155" s="360"/>
-      <c r="J155" s="361"/>
-      <c r="K155" s="361"/>
-      <c r="L155" s="361"/>
-      <c r="M155" s="361"/>
-      <c r="N155" s="361"/>
+    <row r="155" spans="3:15" ht="24" x14ac:dyDescent="0.15">
+      <c r="C155" s="423"/>
+      <c r="D155" s="423"/>
+      <c r="E155" s="423"/>
+      <c r="F155" s="423"/>
+      <c r="G155" s="423"/>
+      <c r="H155" s="423"/>
+      <c r="J155" s="424"/>
+      <c r="K155" s="424"/>
+      <c r="L155" s="424"/>
+      <c r="M155" s="424"/>
+      <c r="N155" s="424"/>
       <c r="O155" s="39"/>
     </row>
-    <row r="156" spans="3:15" ht="23.25">
-      <c r="C156" s="360"/>
-      <c r="D156" s="360"/>
-      <c r="E156" s="360"/>
-      <c r="F156" s="360"/>
-      <c r="G156" s="360"/>
-      <c r="H156" s="360"/>
-      <c r="J156" s="361"/>
-      <c r="K156" s="361"/>
-      <c r="L156" s="361"/>
-      <c r="M156" s="361"/>
-      <c r="N156" s="361"/>
+    <row r="156" spans="3:15" ht="24" x14ac:dyDescent="0.15">
+      <c r="C156" s="423"/>
+      <c r="D156" s="423"/>
+      <c r="E156" s="423"/>
+      <c r="F156" s="423"/>
+      <c r="G156" s="423"/>
+      <c r="H156" s="423"/>
+      <c r="J156" s="424"/>
+      <c r="K156" s="424"/>
+      <c r="L156" s="424"/>
+      <c r="M156" s="424"/>
+      <c r="N156" s="424"/>
       <c r="O156" s="39"/>
     </row>
-    <row r="157" spans="3:15" ht="23.25">
-      <c r="C157" s="360"/>
-      <c r="D157" s="360"/>
-      <c r="E157" s="360"/>
-      <c r="F157" s="360"/>
-      <c r="G157" s="360"/>
-      <c r="H157" s="360"/>
-      <c r="J157" s="361"/>
-      <c r="K157" s="361"/>
-      <c r="L157" s="361"/>
-      <c r="M157" s="361"/>
-      <c r="N157" s="361"/>
+    <row r="157" spans="3:15" ht="24" x14ac:dyDescent="0.15">
+      <c r="C157" s="423"/>
+      <c r="D157" s="423"/>
+      <c r="E157" s="423"/>
+      <c r="F157" s="423"/>
+      <c r="G157" s="423"/>
+      <c r="H157" s="423"/>
+      <c r="J157" s="424"/>
+      <c r="K157" s="424"/>
+      <c r="L157" s="424"/>
+      <c r="M157" s="424"/>
+      <c r="N157" s="424"/>
       <c r="O157" s="39"/>
     </row>
-    <row r="158" spans="3:15" ht="23.25">
-      <c r="C158" s="360"/>
-      <c r="D158" s="360"/>
-      <c r="E158" s="360"/>
-      <c r="F158" s="360"/>
-      <c r="G158" s="360"/>
-      <c r="H158" s="360"/>
-      <c r="J158" s="361"/>
-      <c r="K158" s="361"/>
-      <c r="L158" s="361"/>
-      <c r="M158" s="361"/>
-      <c r="N158" s="361"/>
+    <row r="158" spans="3:15" ht="24" x14ac:dyDescent="0.15">
+      <c r="C158" s="423"/>
+      <c r="D158" s="423"/>
+      <c r="E158" s="423"/>
+      <c r="F158" s="423"/>
+      <c r="G158" s="423"/>
+      <c r="H158" s="423"/>
+      <c r="J158" s="424"/>
+      <c r="K158" s="424"/>
+      <c r="L158" s="424"/>
+      <c r="M158" s="424"/>
+      <c r="N158" s="424"/>
       <c r="O158" s="39"/>
     </row>
-    <row r="159" spans="3:15" ht="23.25">
-      <c r="C159" s="360"/>
-      <c r="D159" s="360"/>
-      <c r="E159" s="360"/>
-      <c r="F159" s="360"/>
-      <c r="G159" s="360"/>
-      <c r="H159" s="360"/>
-      <c r="J159" s="361"/>
-      <c r="K159" s="361"/>
-      <c r="L159" s="361"/>
-      <c r="M159" s="361"/>
-      <c r="N159" s="361"/>
+    <row r="159" spans="3:15" ht="24" x14ac:dyDescent="0.15">
+      <c r="C159" s="423"/>
+      <c r="D159" s="423"/>
+      <c r="E159" s="423"/>
+      <c r="F159" s="423"/>
+      <c r="G159" s="423"/>
+      <c r="H159" s="423"/>
+      <c r="J159" s="424"/>
+      <c r="K159" s="424"/>
+      <c r="L159" s="424"/>
+      <c r="M159" s="424"/>
+      <c r="N159" s="424"/>
       <c r="O159" s="39"/>
     </row>
-    <row r="160" spans="3:15" ht="23.25">
-      <c r="C160" s="360"/>
-      <c r="D160" s="360"/>
-      <c r="E160" s="360"/>
-      <c r="F160" s="360"/>
-      <c r="G160" s="360"/>
-      <c r="H160" s="360"/>
-      <c r="J160" s="361"/>
-      <c r="K160" s="361"/>
-      <c r="L160" s="361"/>
-      <c r="M160" s="361"/>
-      <c r="N160" s="361"/>
+    <row r="160" spans="3:15" ht="24" x14ac:dyDescent="0.15">
+      <c r="C160" s="423"/>
+      <c r="D160" s="423"/>
+      <c r="E160" s="423"/>
+      <c r="F160" s="423"/>
+      <c r="G160" s="423"/>
+      <c r="H160" s="423"/>
+      <c r="J160" s="424"/>
+      <c r="K160" s="424"/>
+      <c r="L160" s="424"/>
+      <c r="M160" s="424"/>
+      <c r="N160" s="424"/>
       <c r="O160" s="39"/>
     </row>
-    <row r="161" spans="3:15" ht="23.25">
-      <c r="C161" s="360"/>
-      <c r="D161" s="360"/>
-      <c r="E161" s="360"/>
-      <c r="F161" s="360"/>
-      <c r="G161" s="360"/>
-      <c r="H161" s="360"/>
-      <c r="J161" s="361"/>
-      <c r="K161" s="361"/>
-      <c r="L161" s="361"/>
-      <c r="M161" s="361"/>
-      <c r="N161" s="361"/>
+    <row r="161" spans="3:15" ht="24" x14ac:dyDescent="0.15">
+      <c r="C161" s="423"/>
+      <c r="D161" s="423"/>
+      <c r="E161" s="423"/>
+      <c r="F161" s="423"/>
+      <c r="G161" s="423"/>
+      <c r="H161" s="423"/>
+      <c r="J161" s="424"/>
+      <c r="K161" s="424"/>
+      <c r="L161" s="424"/>
+      <c r="M161" s="424"/>
+      <c r="N161" s="424"/>
       <c r="O161" s="39"/>
     </row>
-    <row r="162" spans="3:15" ht="23.25">
-      <c r="C162" s="360"/>
-      <c r="D162" s="360"/>
-      <c r="E162" s="360"/>
-      <c r="F162" s="360"/>
-      <c r="G162" s="360"/>
-      <c r="H162" s="360"/>
-      <c r="J162" s="361"/>
-      <c r="K162" s="361"/>
-      <c r="L162" s="361"/>
-      <c r="M162" s="361"/>
-      <c r="N162" s="361"/>
+    <row r="162" spans="3:15" ht="24" x14ac:dyDescent="0.15">
+      <c r="C162" s="423"/>
+      <c r="D162" s="423"/>
+      <c r="E162" s="423"/>
+      <c r="F162" s="423"/>
+      <c r="G162" s="423"/>
+      <c r="H162" s="423"/>
+      <c r="J162" s="424"/>
+      <c r="K162" s="424"/>
+      <c r="L162" s="424"/>
+      <c r="M162" s="424"/>
+      <c r="N162" s="424"/>
       <c r="O162" s="39"/>
     </row>
-    <row r="163" spans="3:15" ht="23.25">
-      <c r="C163" s="360"/>
-      <c r="D163" s="360"/>
-      <c r="E163" s="360"/>
-      <c r="F163" s="360"/>
-      <c r="G163" s="360"/>
-      <c r="H163" s="360"/>
-      <c r="J163" s="361"/>
-      <c r="K163" s="361"/>
-      <c r="L163" s="361"/>
-      <c r="M163" s="361"/>
-      <c r="N163" s="361"/>
+    <row r="163" spans="3:15" ht="24" x14ac:dyDescent="0.15">
+      <c r="C163" s="423"/>
+      <c r="D163" s="423"/>
+      <c r="E163" s="423"/>
+      <c r="F163" s="423"/>
+      <c r="G163" s="423"/>
+      <c r="H163" s="423"/>
+      <c r="J163" s="424"/>
+      <c r="K163" s="424"/>
+      <c r="L163" s="424"/>
+      <c r="M163" s="424"/>
+      <c r="N163" s="424"/>
       <c r="O163" s="39"/>
     </row>
-    <row r="164" spans="3:15" ht="23.25">
-      <c r="C164" s="360"/>
-      <c r="D164" s="360"/>
-      <c r="E164" s="360"/>
-      <c r="F164" s="360"/>
-      <c r="G164" s="360"/>
-      <c r="H164" s="360"/>
-      <c r="J164" s="361"/>
-      <c r="K164" s="361"/>
-      <c r="L164" s="361"/>
-      <c r="M164" s="361"/>
-      <c r="N164" s="361"/>
+    <row r="164" spans="3:15" ht="24" x14ac:dyDescent="0.15">
+      <c r="C164" s="423"/>
+      <c r="D164" s="423"/>
+      <c r="E164" s="423"/>
+      <c r="F164" s="423"/>
+      <c r="G164" s="423"/>
+      <c r="H164" s="423"/>
+      <c r="J164" s="424"/>
+      <c r="K164" s="424"/>
+      <c r="L164" s="424"/>
+      <c r="M164" s="424"/>
+      <c r="N164" s="424"/>
       <c r="O164" s="39"/>
     </row>
-    <row r="165" spans="3:15" ht="6.75" customHeight="1">
-      <c r="C165" s="360"/>
-      <c r="D165" s="360"/>
-      <c r="E165" s="360"/>
-      <c r="F165" s="360"/>
-      <c r="G165" s="360"/>
-      <c r="H165" s="360"/>
-      <c r="J165" s="361"/>
-      <c r="K165" s="361"/>
-      <c r="L165" s="361"/>
-      <c r="M165" s="361"/>
-      <c r="N165" s="361"/>
+    <row r="165" spans="3:15" ht="6.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C165" s="423"/>
+      <c r="D165" s="423"/>
+      <c r="E165" s="423"/>
+      <c r="F165" s="423"/>
+      <c r="G165" s="423"/>
+      <c r="H165" s="423"/>
+      <c r="J165" s="424"/>
+      <c r="K165" s="424"/>
+      <c r="L165" s="424"/>
+      <c r="M165" s="424"/>
+      <c r="N165" s="424"/>
       <c r="O165" s="39"/>
     </row>
-    <row r="166" spans="3:15" ht="23.25" hidden="1">
-      <c r="C166" s="360"/>
-      <c r="D166" s="360"/>
-      <c r="E166" s="360"/>
-      <c r="F166" s="360"/>
-      <c r="G166" s="360"/>
-      <c r="H166" s="360"/>
-      <c r="J166" s="361"/>
-      <c r="K166" s="361"/>
-      <c r="L166" s="361"/>
-      <c r="M166" s="361"/>
-      <c r="N166" s="361"/>
+    <row r="166" spans="3:15" ht="24" hidden="1" x14ac:dyDescent="0.15">
+      <c r="C166" s="423"/>
+      <c r="D166" s="423"/>
+      <c r="E166" s="423"/>
+      <c r="F166" s="423"/>
+      <c r="G166" s="423"/>
+      <c r="H166" s="423"/>
+      <c r="J166" s="424"/>
+      <c r="K166" s="424"/>
+      <c r="L166" s="424"/>
+      <c r="M166" s="424"/>
+      <c r="N166" s="424"/>
       <c r="O166" s="39"/>
     </row>
-    <row r="167" spans="3:15" ht="23.25" hidden="1">
-      <c r="C167" s="360"/>
-      <c r="D167" s="360"/>
-      <c r="E167" s="360"/>
-      <c r="F167" s="360"/>
-      <c r="G167" s="360"/>
-      <c r="H167" s="360"/>
-      <c r="J167" s="361"/>
-      <c r="K167" s="361"/>
-      <c r="L167" s="361"/>
-      <c r="M167" s="361"/>
-      <c r="N167" s="361"/>
+    <row r="167" spans="3:15" ht="24" hidden="1" x14ac:dyDescent="0.15">
+      <c r="C167" s="423"/>
+      <c r="D167" s="423"/>
+      <c r="E167" s="423"/>
+      <c r="F167" s="423"/>
+      <c r="G167" s="423"/>
+      <c r="H167" s="423"/>
+      <c r="J167" s="424"/>
+      <c r="K167" s="424"/>
+      <c r="L167" s="424"/>
+      <c r="M167" s="424"/>
+      <c r="N167" s="424"/>
       <c r="O167" s="39"/>
     </row>
-    <row r="168" spans="3:15" ht="23.25" hidden="1">
-      <c r="C168" s="360"/>
-      <c r="D168" s="360"/>
-      <c r="E168" s="360"/>
-      <c r="F168" s="360"/>
-      <c r="G168" s="360"/>
-      <c r="H168" s="360"/>
-      <c r="J168" s="361"/>
-      <c r="K168" s="361"/>
-      <c r="L168" s="361"/>
-      <c r="M168" s="361"/>
-      <c r="N168" s="361"/>
+    <row r="168" spans="3:15" ht="24" hidden="1" x14ac:dyDescent="0.15">
+      <c r="C168" s="423"/>
+      <c r="D168" s="423"/>
+      <c r="E168" s="423"/>
+      <c r="F168" s="423"/>
+      <c r="G168" s="423"/>
+      <c r="H168" s="423"/>
+      <c r="J168" s="424"/>
+      <c r="K168" s="424"/>
+      <c r="L168" s="424"/>
+      <c r="M168" s="424"/>
+      <c r="N168" s="424"/>
       <c r="O168" s="39"/>
     </row>
-    <row r="169" spans="3:15" ht="23.25" hidden="1">
-      <c r="C169" s="360"/>
-      <c r="D169" s="360"/>
-      <c r="E169" s="360"/>
-      <c r="F169" s="360"/>
-      <c r="G169" s="360"/>
-      <c r="H169" s="360"/>
-      <c r="J169" s="361"/>
-      <c r="K169" s="361"/>
-      <c r="L169" s="361"/>
-      <c r="M169" s="361"/>
-      <c r="N169" s="361"/>
+    <row r="169" spans="3:15" ht="24" hidden="1" x14ac:dyDescent="0.15">
+      <c r="C169" s="423"/>
+      <c r="D169" s="423"/>
+      <c r="E169" s="423"/>
+      <c r="F169" s="423"/>
+      <c r="G169" s="423"/>
+      <c r="H169" s="423"/>
+      <c r="J169" s="424"/>
+      <c r="K169" s="424"/>
+      <c r="L169" s="424"/>
+      <c r="M169" s="424"/>
+      <c r="N169" s="424"/>
       <c r="O169" s="39"/>
     </row>
-    <row r="170" spans="3:15" ht="23.25" hidden="1">
-      <c r="C170" s="360"/>
-      <c r="D170" s="360"/>
-      <c r="E170" s="360"/>
-      <c r="F170" s="360"/>
-      <c r="G170" s="360"/>
-      <c r="H170" s="360"/>
-      <c r="J170" s="361"/>
-      <c r="K170" s="361"/>
-      <c r="L170" s="361"/>
-      <c r="M170" s="361"/>
-      <c r="N170" s="361"/>
+    <row r="170" spans="3:15" ht="24" hidden="1" x14ac:dyDescent="0.15">
+      <c r="C170" s="423"/>
+      <c r="D170" s="423"/>
+      <c r="E170" s="423"/>
+      <c r="F170" s="423"/>
+      <c r="G170" s="423"/>
+      <c r="H170" s="423"/>
+      <c r="J170" s="424"/>
+      <c r="K170" s="424"/>
+      <c r="L170" s="424"/>
+      <c r="M170" s="424"/>
+      <c r="N170" s="424"/>
       <c r="O170" s="39"/>
     </row>
-    <row r="171" spans="3:15" ht="23.25" hidden="1">
-      <c r="C171" s="360"/>
-      <c r="D171" s="360"/>
-      <c r="E171" s="360"/>
-      <c r="F171" s="360"/>
-      <c r="G171" s="360"/>
-      <c r="H171" s="360"/>
-      <c r="J171" s="361"/>
-      <c r="K171" s="361"/>
-      <c r="L171" s="361"/>
-      <c r="M171" s="361"/>
-      <c r="N171" s="361"/>
+    <row r="171" spans="3:15" ht="24" hidden="1" x14ac:dyDescent="0.15">
+      <c r="C171" s="423"/>
+      <c r="D171" s="423"/>
+      <c r="E171" s="423"/>
+      <c r="F171" s="423"/>
+      <c r="G171" s="423"/>
+      <c r="H171" s="423"/>
+      <c r="J171" s="424"/>
+      <c r="K171" s="424"/>
+      <c r="L171" s="424"/>
+      <c r="M171" s="424"/>
+      <c r="N171" s="424"/>
       <c r="O171" s="39"/>
     </row>
-    <row r="172" spans="3:15" ht="23.25">
-      <c r="C172" s="360"/>
-      <c r="D172" s="360"/>
-      <c r="E172" s="360"/>
-      <c r="F172" s="360"/>
-      <c r="G172" s="360"/>
-      <c r="H172" s="360"/>
-      <c r="J172" s="361"/>
-      <c r="K172" s="361"/>
-      <c r="L172" s="361"/>
-      <c r="M172" s="361"/>
-      <c r="N172" s="361"/>
+    <row r="172" spans="3:15" ht="24" x14ac:dyDescent="0.15">
+      <c r="C172" s="423"/>
+      <c r="D172" s="423"/>
+      <c r="E172" s="423"/>
+      <c r="F172" s="423"/>
+      <c r="G172" s="423"/>
+      <c r="H172" s="423"/>
+      <c r="J172" s="424"/>
+      <c r="K172" s="424"/>
+      <c r="L172" s="424"/>
+      <c r="M172" s="424"/>
+      <c r="N172" s="424"/>
       <c r="O172" s="39"/>
     </row>
-    <row r="173" spans="3:15" ht="23.25">
-      <c r="C173" s="360"/>
-      <c r="D173" s="360"/>
-      <c r="E173" s="360"/>
-      <c r="F173" s="360"/>
-      <c r="G173" s="360"/>
-      <c r="H173" s="360"/>
-      <c r="J173" s="361"/>
-      <c r="K173" s="361"/>
-      <c r="L173" s="361"/>
-      <c r="M173" s="361"/>
-      <c r="N173" s="361"/>
+    <row r="173" spans="3:15" ht="24" x14ac:dyDescent="0.15">
+      <c r="C173" s="423"/>
+      <c r="D173" s="423"/>
+      <c r="E173" s="423"/>
+      <c r="F173" s="423"/>
+      <c r="G173" s="423"/>
+      <c r="H173" s="423"/>
+      <c r="J173" s="424"/>
+      <c r="K173" s="424"/>
+      <c r="L173" s="424"/>
+      <c r="M173" s="424"/>
+      <c r="N173" s="424"/>
       <c r="O173" s="39"/>
     </row>
-    <row r="174" spans="3:15" ht="23.25">
-      <c r="C174" s="360"/>
-      <c r="D174" s="360"/>
-      <c r="E174" s="360"/>
-      <c r="F174" s="360"/>
-      <c r="G174" s="360"/>
-      <c r="H174" s="360"/>
-      <c r="J174" s="361"/>
-      <c r="K174" s="361"/>
-      <c r="L174" s="361"/>
-      <c r="M174" s="361"/>
-      <c r="N174" s="361"/>
+    <row r="174" spans="3:15" ht="24" x14ac:dyDescent="0.15">
+      <c r="C174" s="423"/>
+      <c r="D174" s="423"/>
+      <c r="E174" s="423"/>
+      <c r="F174" s="423"/>
+      <c r="G174" s="423"/>
+      <c r="H174" s="423"/>
+      <c r="J174" s="424"/>
+      <c r="K174" s="424"/>
+      <c r="L174" s="424"/>
+      <c r="M174" s="424"/>
+      <c r="N174" s="424"/>
       <c r="O174" s="39"/>
     </row>
-    <row r="175" spans="3:15" ht="23.25">
-      <c r="C175" s="360"/>
-      <c r="D175" s="360"/>
-      <c r="E175" s="360"/>
-      <c r="F175" s="360"/>
-      <c r="G175" s="360"/>
-      <c r="H175" s="360"/>
-      <c r="J175" s="361"/>
-      <c r="K175" s="361"/>
-      <c r="L175" s="361"/>
-      <c r="M175" s="361"/>
-      <c r="N175" s="361"/>
+    <row r="175" spans="3:15" ht="24" x14ac:dyDescent="0.15">
+      <c r="C175" s="423"/>
+      <c r="D175" s="423"/>
+      <c r="E175" s="423"/>
+      <c r="F175" s="423"/>
+      <c r="G175" s="423"/>
+      <c r="H175" s="423"/>
+      <c r="J175" s="424"/>
+      <c r="K175" s="424"/>
+      <c r="L175" s="424"/>
+      <c r="M175" s="424"/>
+      <c r="N175" s="424"/>
       <c r="O175" s="39"/>
     </row>
-    <row r="176" spans="3:15" ht="23.25">
-      <c r="C176" s="360"/>
-      <c r="D176" s="360"/>
-      <c r="E176" s="360"/>
-      <c r="F176" s="360"/>
-      <c r="G176" s="360"/>
-      <c r="H176" s="360"/>
-      <c r="J176" s="361"/>
-      <c r="K176" s="361"/>
-      <c r="L176" s="361"/>
-      <c r="M176" s="361"/>
-      <c r="N176" s="361"/>
+    <row r="176" spans="3:15" ht="24" x14ac:dyDescent="0.15">
+      <c r="C176" s="423"/>
+      <c r="D176" s="423"/>
+      <c r="E176" s="423"/>
+      <c r="F176" s="423"/>
+      <c r="G176" s="423"/>
+      <c r="H176" s="423"/>
+      <c r="J176" s="424"/>
+      <c r="K176" s="424"/>
+      <c r="L176" s="424"/>
+      <c r="M176" s="424"/>
+      <c r="N176" s="424"/>
       <c r="O176" s="39"/>
     </row>
-    <row r="177" spans="3:15" ht="23.25">
-      <c r="C177" s="360"/>
-      <c r="D177" s="360"/>
-      <c r="E177" s="360"/>
-      <c r="F177" s="360"/>
-      <c r="G177" s="360"/>
-      <c r="H177" s="360"/>
-      <c r="J177" s="361"/>
-      <c r="K177" s="361"/>
-      <c r="L177" s="361"/>
-      <c r="M177" s="361"/>
-      <c r="N177" s="361"/>
+    <row r="177" spans="3:15" ht="24" x14ac:dyDescent="0.15">
+      <c r="C177" s="423"/>
+      <c r="D177" s="423"/>
+      <c r="E177" s="423"/>
+      <c r="F177" s="423"/>
+      <c r="G177" s="423"/>
+      <c r="H177" s="423"/>
+      <c r="J177" s="424"/>
+      <c r="K177" s="424"/>
+      <c r="L177" s="424"/>
+      <c r="M177" s="424"/>
+      <c r="N177" s="424"/>
       <c r="O177" s="39"/>
     </row>
-    <row r="178" spans="3:15" ht="23.25">
-      <c r="C178" s="360"/>
-      <c r="D178" s="360"/>
-      <c r="E178" s="360"/>
-      <c r="F178" s="360"/>
-      <c r="G178" s="360"/>
-      <c r="H178" s="360"/>
-      <c r="J178" s="361"/>
-      <c r="K178" s="361"/>
-      <c r="L178" s="361"/>
-      <c r="M178" s="361"/>
-      <c r="N178" s="361"/>
+    <row r="178" spans="3:15" ht="24" x14ac:dyDescent="0.15">
+      <c r="C178" s="423"/>
+      <c r="D178" s="423"/>
+      <c r="E178" s="423"/>
+      <c r="F178" s="423"/>
+      <c r="G178" s="423"/>
+      <c r="H178" s="423"/>
+      <c r="J178" s="424"/>
+      <c r="K178" s="424"/>
+      <c r="L178" s="424"/>
+      <c r="M178" s="424"/>
+      <c r="N178" s="424"/>
       <c r="O178" s="39"/>
     </row>
-    <row r="179" spans="3:15" ht="23.25">
-      <c r="C179" s="360"/>
-      <c r="D179" s="360"/>
-      <c r="E179" s="360"/>
-      <c r="F179" s="360"/>
-      <c r="G179" s="360"/>
-      <c r="H179" s="360"/>
-      <c r="J179" s="361"/>
-      <c r="K179" s="361"/>
-      <c r="L179" s="361"/>
-      <c r="M179" s="361"/>
-      <c r="N179" s="361"/>
+    <row r="179" spans="3:15" ht="24" x14ac:dyDescent="0.15">
+      <c r="C179" s="423"/>
+      <c r="D179" s="423"/>
+      <c r="E179" s="423"/>
+      <c r="F179" s="423"/>
+      <c r="G179" s="423"/>
+      <c r="H179" s="423"/>
+      <c r="J179" s="424"/>
+      <c r="K179" s="424"/>
+      <c r="L179" s="424"/>
+      <c r="M179" s="424"/>
+      <c r="N179" s="424"/>
       <c r="O179" s="39"/>
     </row>
-    <row r="180" spans="3:15" ht="23.25">
-      <c r="C180" s="360"/>
-      <c r="D180" s="360"/>
-      <c r="E180" s="360"/>
-      <c r="F180" s="360"/>
-      <c r="G180" s="360"/>
-      <c r="H180" s="360"/>
-      <c r="J180" s="361"/>
-      <c r="K180" s="361"/>
-      <c r="L180" s="361"/>
-      <c r="M180" s="361"/>
-      <c r="N180" s="361"/>
+    <row r="180" spans="3:15" ht="24" x14ac:dyDescent="0.15">
+      <c r="C180" s="423"/>
+      <c r="D180" s="423"/>
+      <c r="E180" s="423"/>
+      <c r="F180" s="423"/>
+      <c r="G180" s="423"/>
+      <c r="H180" s="423"/>
+      <c r="J180" s="424"/>
+      <c r="K180" s="424"/>
+      <c r="L180" s="424"/>
+      <c r="M180" s="424"/>
+      <c r="N180" s="424"/>
       <c r="O180" s="39"/>
     </row>
-    <row r="181" spans="3:15" ht="23.25">
-      <c r="C181" s="360"/>
-      <c r="D181" s="360"/>
-      <c r="E181" s="360"/>
-      <c r="F181" s="360"/>
-      <c r="G181" s="360"/>
-      <c r="H181" s="360"/>
-      <c r="J181" s="361"/>
-      <c r="K181" s="361"/>
-      <c r="L181" s="361"/>
-      <c r="M181" s="361"/>
-      <c r="N181" s="361"/>
+    <row r="181" spans="3:15" ht="24" x14ac:dyDescent="0.15">
+      <c r="C181" s="423"/>
+      <c r="D181" s="423"/>
+      <c r="E181" s="423"/>
+      <c r="F181" s="423"/>
+      <c r="G181" s="423"/>
+      <c r="H181" s="423"/>
+      <c r="J181" s="424"/>
+      <c r="K181" s="424"/>
+      <c r="L181" s="424"/>
+      <c r="M181" s="424"/>
+      <c r="N181" s="424"/>
       <c r="O181" s="39"/>
     </row>
-    <row r="182" spans="3:15" ht="23.25">
-      <c r="C182" s="360"/>
-      <c r="D182" s="360"/>
-      <c r="E182" s="360"/>
-      <c r="F182" s="360"/>
-      <c r="G182" s="360"/>
-      <c r="H182" s="360"/>
-      <c r="J182" s="361"/>
-      <c r="K182" s="361"/>
-      <c r="L182" s="361"/>
-      <c r="M182" s="361"/>
-      <c r="N182" s="361"/>
+    <row r="182" spans="3:15" ht="24" x14ac:dyDescent="0.15">
+      <c r="C182" s="423"/>
+      <c r="D182" s="423"/>
+      <c r="E182" s="423"/>
+      <c r="F182" s="423"/>
+      <c r="G182" s="423"/>
+      <c r="H182" s="423"/>
+      <c r="J182" s="424"/>
+      <c r="K182" s="424"/>
+      <c r="L182" s="424"/>
+      <c r="M182" s="424"/>
+      <c r="N182" s="424"/>
       <c r="O182" s="39"/>
     </row>
-    <row r="183" spans="3:15" ht="23.25">
-      <c r="C183" s="360"/>
-      <c r="D183" s="360"/>
-      <c r="E183" s="360"/>
-      <c r="F183" s="360"/>
-      <c r="G183" s="360"/>
-      <c r="H183" s="360"/>
-      <c r="J183" s="361"/>
-      <c r="K183" s="361"/>
-      <c r="L183" s="361"/>
-      <c r="M183" s="361"/>
-      <c r="N183" s="361"/>
+    <row r="183" spans="3:15" ht="24" x14ac:dyDescent="0.15">
+      <c r="C183" s="423"/>
+      <c r="D183" s="423"/>
+      <c r="E183" s="423"/>
+      <c r="F183" s="423"/>
+      <c r="G183" s="423"/>
+      <c r="H183" s="423"/>
+      <c r="J183" s="424"/>
+      <c r="K183" s="424"/>
+      <c r="L183" s="424"/>
+      <c r="M183" s="424"/>
+      <c r="N183" s="424"/>
       <c r="O183" s="39"/>
     </row>
-    <row r="184" spans="3:15" ht="23.25">
-      <c r="C184" s="360"/>
-      <c r="D184" s="360"/>
-      <c r="E184" s="360"/>
-      <c r="F184" s="360"/>
-      <c r="G184" s="360"/>
-      <c r="H184" s="360"/>
-      <c r="J184" s="361"/>
-      <c r="K184" s="361"/>
-      <c r="L184" s="361"/>
-      <c r="M184" s="361"/>
-      <c r="N184" s="361"/>
+    <row r="184" spans="3:15" ht="24" x14ac:dyDescent="0.15">
+      <c r="C184" s="423"/>
+      <c r="D184" s="423"/>
+      <c r="E184" s="423"/>
+      <c r="F184" s="423"/>
+      <c r="G184" s="423"/>
+      <c r="H184" s="423"/>
+      <c r="J184" s="424"/>
+      <c r="K184" s="424"/>
+      <c r="L184" s="424"/>
+      <c r="M184" s="424"/>
+      <c r="N184" s="424"/>
       <c r="O184" s="39"/>
     </row>
-    <row r="185" spans="3:15" ht="23.25">
-      <c r="C185" s="360"/>
-      <c r="D185" s="360"/>
-      <c r="E185" s="360"/>
-      <c r="F185" s="360"/>
-      <c r="G185" s="360"/>
-      <c r="H185" s="360"/>
-      <c r="J185" s="361"/>
-      <c r="K185" s="361"/>
-      <c r="L185" s="361"/>
-      <c r="M185" s="361"/>
-      <c r="N185" s="361"/>
+    <row r="185" spans="3:15" ht="24" x14ac:dyDescent="0.15">
+      <c r="C185" s="423"/>
+      <c r="D185" s="423"/>
+      <c r="E185" s="423"/>
+      <c r="F185" s="423"/>
+      <c r="G185" s="423"/>
+      <c r="H185" s="423"/>
+      <c r="J185" s="424"/>
+      <c r="K185" s="424"/>
+      <c r="L185" s="424"/>
+      <c r="M185" s="424"/>
+      <c r="N185" s="424"/>
       <c r="O185" s="39"/>
     </row>
-    <row r="186" spans="3:15" ht="23.25">
-      <c r="C186" s="360"/>
-      <c r="D186" s="360"/>
-      <c r="E186" s="360"/>
-      <c r="F186" s="360"/>
-      <c r="G186" s="360"/>
-      <c r="H186" s="360"/>
-      <c r="J186" s="361"/>
-      <c r="K186" s="361"/>
-      <c r="L186" s="361"/>
-      <c r="M186" s="361"/>
-      <c r="N186" s="361"/>
+    <row r="186" spans="3:15" ht="24" x14ac:dyDescent="0.15">
+      <c r="C186" s="423"/>
+      <c r="D186" s="423"/>
+      <c r="E186" s="423"/>
+      <c r="F186" s="423"/>
+      <c r="G186" s="423"/>
+      <c r="H186" s="423"/>
+      <c r="J186" s="424"/>
+      <c r="K186" s="424"/>
+      <c r="L186" s="424"/>
+      <c r="M186" s="424"/>
+      <c r="N186" s="424"/>
       <c r="O186" s="39"/>
     </row>
-    <row r="187" spans="3:15" ht="23.25">
-      <c r="C187" s="360"/>
-      <c r="D187" s="360"/>
-      <c r="E187" s="360"/>
-      <c r="F187" s="360"/>
-      <c r="G187" s="360"/>
-      <c r="H187" s="360"/>
-      <c r="J187" s="361"/>
-      <c r="K187" s="361"/>
-      <c r="L187" s="361"/>
-      <c r="M187" s="361"/>
-      <c r="N187" s="361"/>
+    <row r="187" spans="3:15" ht="24" x14ac:dyDescent="0.15">
+      <c r="C187" s="423"/>
+      <c r="D187" s="423"/>
+      <c r="E187" s="423"/>
+      <c r="F187" s="423"/>
+      <c r="G187" s="423"/>
+      <c r="H187" s="423"/>
+      <c r="J187" s="424"/>
+      <c r="K187" s="424"/>
+      <c r="L187" s="424"/>
+      <c r="M187" s="424"/>
+      <c r="N187" s="424"/>
       <c r="O187" s="39"/>
     </row>
-    <row r="188" spans="3:15" ht="23.25">
-      <c r="C188" s="360"/>
-      <c r="D188" s="360"/>
-      <c r="E188" s="360"/>
-      <c r="F188" s="360"/>
-      <c r="G188" s="360"/>
-      <c r="H188" s="360"/>
-      <c r="J188" s="361"/>
-      <c r="K188" s="361"/>
-      <c r="L188" s="361"/>
-      <c r="M188" s="361"/>
-      <c r="N188" s="361"/>
+    <row r="188" spans="3:15" ht="24" x14ac:dyDescent="0.15">
+      <c r="C188" s="423"/>
+      <c r="D188" s="423"/>
+      <c r="E188" s="423"/>
+      <c r="F188" s="423"/>
+      <c r="G188" s="423"/>
+      <c r="H188" s="423"/>
+      <c r="J188" s="424"/>
+      <c r="K188" s="424"/>
+      <c r="L188" s="424"/>
+      <c r="M188" s="424"/>
+      <c r="N188" s="424"/>
       <c r="O188" s="39"/>
     </row>
-    <row r="189" spans="3:15" ht="23.25">
-      <c r="C189" s="360"/>
-      <c r="D189" s="360"/>
-      <c r="E189" s="360"/>
-      <c r="F189" s="360"/>
-      <c r="G189" s="360"/>
-      <c r="H189" s="360"/>
-      <c r="J189" s="361"/>
-      <c r="K189" s="361"/>
-      <c r="L189" s="361"/>
-      <c r="M189" s="361"/>
-      <c r="N189" s="361"/>
+    <row r="189" spans="3:15" ht="24" x14ac:dyDescent="0.15">
+      <c r="C189" s="423"/>
+      <c r="D189" s="423"/>
+      <c r="E189" s="423"/>
+      <c r="F189" s="423"/>
+      <c r="G189" s="423"/>
+      <c r="H189" s="423"/>
+      <c r="J189" s="424"/>
+      <c r="K189" s="424"/>
+      <c r="L189" s="424"/>
+      <c r="M189" s="424"/>
+      <c r="N189" s="424"/>
       <c r="O189" s="39"/>
     </row>
-    <row r="190" spans="3:15" ht="23.25">
-      <c r="J190" s="361"/>
-      <c r="K190" s="361"/>
-      <c r="L190" s="361"/>
-      <c r="M190" s="361"/>
-      <c r="N190" s="361"/>
+    <row r="190" spans="3:15" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="J190" s="424"/>
+      <c r="K190" s="424"/>
+      <c r="L190" s="424"/>
+      <c r="M190" s="424"/>
+      <c r="N190" s="424"/>
       <c r="O190" s="39"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
   <mergeCells count="313">
-    <mergeCell ref="F54:G54"/>
-    <mergeCell ref="J49:K49"/>
-    <mergeCell ref="K53:M53"/>
-    <mergeCell ref="Q36:R36"/>
-    <mergeCell ref="Q42:R42"/>
-    <mergeCell ref="Q43:R43"/>
-    <mergeCell ref="Q40:R40"/>
-    <mergeCell ref="Q50:R50"/>
-    <mergeCell ref="Q37:R37"/>
-    <mergeCell ref="Q38:R38"/>
-    <mergeCell ref="J41:L41"/>
-    <mergeCell ref="Q41:R41"/>
-    <mergeCell ref="J47:K47"/>
-    <mergeCell ref="J42:M42"/>
-    <mergeCell ref="Q39:R39"/>
-    <mergeCell ref="J45:K45"/>
-    <mergeCell ref="J39:L39"/>
-    <mergeCell ref="J46:K46"/>
-    <mergeCell ref="J43:N43"/>
-    <mergeCell ref="J40:L40"/>
-    <mergeCell ref="J48:K48"/>
-    <mergeCell ref="J52:P52"/>
-    <mergeCell ref="K54:M54"/>
-    <mergeCell ref="C1:J1"/>
-    <mergeCell ref="J3:P3"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="C6:E6"/>
-    <mergeCell ref="J13:M13"/>
-    <mergeCell ref="C4:E4"/>
-    <mergeCell ref="C13:E13"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="L10:M10"/>
-    <mergeCell ref="C8:E8"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="P11:R11"/>
-    <mergeCell ref="J10:K10"/>
-    <mergeCell ref="J11:K11"/>
-    <mergeCell ref="C10:E10"/>
-    <mergeCell ref="J7:K7"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="J9:K9"/>
-    <mergeCell ref="L11:M11"/>
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="C15:E15"/>
-    <mergeCell ref="C19:E19"/>
-    <mergeCell ref="J20:M20"/>
-    <mergeCell ref="J21:M21"/>
-    <mergeCell ref="T12:U12"/>
-    <mergeCell ref="T13:U13"/>
-    <mergeCell ref="S20:U20"/>
-    <mergeCell ref="T17:U17"/>
-    <mergeCell ref="T18:U18"/>
-    <mergeCell ref="T15:U15"/>
-    <mergeCell ref="T16:U16"/>
-    <mergeCell ref="J17:M17"/>
-    <mergeCell ref="J18:M18"/>
-    <mergeCell ref="J15:M15"/>
-    <mergeCell ref="C16:E16"/>
-    <mergeCell ref="J16:M16"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="C18:E18"/>
-    <mergeCell ref="C17:E17"/>
-    <mergeCell ref="J19:M19"/>
-    <mergeCell ref="T14:U14"/>
-    <mergeCell ref="J14:M14"/>
-    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="J91:O91"/>
+    <mergeCell ref="J90:O90"/>
+    <mergeCell ref="J88:O88"/>
+    <mergeCell ref="J89:O89"/>
+    <mergeCell ref="J86:O86"/>
+    <mergeCell ref="J87:O87"/>
+    <mergeCell ref="C56:D56"/>
+    <mergeCell ref="F56:G56"/>
+    <mergeCell ref="K56:M56"/>
+    <mergeCell ref="O56:P56"/>
+    <mergeCell ref="J85:O85"/>
+    <mergeCell ref="V20:W20"/>
+    <mergeCell ref="C60:F60"/>
+    <mergeCell ref="C55:D55"/>
+    <mergeCell ref="F55:G55"/>
+    <mergeCell ref="K55:M55"/>
+    <mergeCell ref="O55:P55"/>
+    <mergeCell ref="J60:N60"/>
+    <mergeCell ref="F53:G53"/>
+    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="C28:E28"/>
+    <mergeCell ref="C29:E29"/>
+    <mergeCell ref="J22:M22"/>
+    <mergeCell ref="O24:P24"/>
+    <mergeCell ref="J25:M25"/>
+    <mergeCell ref="J26:M26"/>
+    <mergeCell ref="J29:M29"/>
+    <mergeCell ref="J32:M32"/>
+    <mergeCell ref="J24:M24"/>
+    <mergeCell ref="J31:M31"/>
+    <mergeCell ref="J28:M28"/>
+    <mergeCell ref="J30:M30"/>
+    <mergeCell ref="C25:E25"/>
+    <mergeCell ref="C26:E26"/>
+    <mergeCell ref="C30:E30"/>
+    <mergeCell ref="C105:H105"/>
+    <mergeCell ref="C103:H103"/>
+    <mergeCell ref="C104:H104"/>
+    <mergeCell ref="J99:N99"/>
+    <mergeCell ref="J100:N100"/>
+    <mergeCell ref="C106:H106"/>
+    <mergeCell ref="J92:O92"/>
+    <mergeCell ref="J93:O93"/>
+    <mergeCell ref="J95:N95"/>
+    <mergeCell ref="J94:N94"/>
+    <mergeCell ref="J103:N103"/>
+    <mergeCell ref="J101:N101"/>
+    <mergeCell ref="J104:N104"/>
+    <mergeCell ref="J102:N102"/>
+    <mergeCell ref="J105:N105"/>
+    <mergeCell ref="C102:H102"/>
+    <mergeCell ref="J97:N97"/>
+    <mergeCell ref="J96:N96"/>
+    <mergeCell ref="C120:H120"/>
+    <mergeCell ref="J109:N109"/>
+    <mergeCell ref="J111:N111"/>
+    <mergeCell ref="J110:N110"/>
+    <mergeCell ref="J108:N108"/>
+    <mergeCell ref="J106:N106"/>
+    <mergeCell ref="C107:H107"/>
+    <mergeCell ref="C117:H117"/>
+    <mergeCell ref="C112:H112"/>
+    <mergeCell ref="C111:H111"/>
+    <mergeCell ref="J107:N107"/>
+    <mergeCell ref="J113:N113"/>
+    <mergeCell ref="J112:N112"/>
+    <mergeCell ref="C109:H109"/>
+    <mergeCell ref="C119:H119"/>
+    <mergeCell ref="C113:H113"/>
+    <mergeCell ref="C110:H110"/>
+    <mergeCell ref="C108:H108"/>
+    <mergeCell ref="J122:N122"/>
+    <mergeCell ref="J118:N118"/>
+    <mergeCell ref="J114:N114"/>
+    <mergeCell ref="J117:N117"/>
+    <mergeCell ref="J128:N128"/>
+    <mergeCell ref="C125:H125"/>
+    <mergeCell ref="C124:H124"/>
+    <mergeCell ref="C122:H122"/>
+    <mergeCell ref="J123:N123"/>
+    <mergeCell ref="J121:N121"/>
+    <mergeCell ref="C115:H115"/>
+    <mergeCell ref="C114:H114"/>
+    <mergeCell ref="C127:H127"/>
+    <mergeCell ref="J124:N124"/>
+    <mergeCell ref="C118:H118"/>
+    <mergeCell ref="J116:N116"/>
+    <mergeCell ref="C116:H116"/>
+    <mergeCell ref="J119:N119"/>
+    <mergeCell ref="C123:H123"/>
+    <mergeCell ref="J115:N115"/>
+    <mergeCell ref="J120:N120"/>
+    <mergeCell ref="C121:H121"/>
+    <mergeCell ref="J127:N127"/>
+    <mergeCell ref="C128:H128"/>
+    <mergeCell ref="C131:H131"/>
+    <mergeCell ref="C133:H133"/>
+    <mergeCell ref="J129:N129"/>
+    <mergeCell ref="J126:N126"/>
+    <mergeCell ref="J125:N125"/>
+    <mergeCell ref="C126:H126"/>
+    <mergeCell ref="J130:N130"/>
+    <mergeCell ref="J142:N142"/>
+    <mergeCell ref="J138:N138"/>
+    <mergeCell ref="J141:N141"/>
+    <mergeCell ref="J133:N133"/>
+    <mergeCell ref="J132:N132"/>
+    <mergeCell ref="J135:N135"/>
+    <mergeCell ref="C132:H132"/>
+    <mergeCell ref="J137:N137"/>
+    <mergeCell ref="J140:N140"/>
+    <mergeCell ref="J136:N136"/>
+    <mergeCell ref="C137:H137"/>
+    <mergeCell ref="J139:N139"/>
+    <mergeCell ref="C139:H139"/>
+    <mergeCell ref="C140:H140"/>
+    <mergeCell ref="C134:H134"/>
+    <mergeCell ref="C135:H135"/>
+    <mergeCell ref="C138:H138"/>
+    <mergeCell ref="C144:H144"/>
+    <mergeCell ref="C143:H143"/>
+    <mergeCell ref="C145:H145"/>
+    <mergeCell ref="J155:N155"/>
+    <mergeCell ref="C154:H154"/>
+    <mergeCell ref="J149:N149"/>
+    <mergeCell ref="C151:H151"/>
+    <mergeCell ref="C149:H149"/>
+    <mergeCell ref="C148:H148"/>
+    <mergeCell ref="J190:N190"/>
+    <mergeCell ref="J170:N170"/>
+    <mergeCell ref="J176:N176"/>
+    <mergeCell ref="J160:N160"/>
+    <mergeCell ref="J182:N182"/>
+    <mergeCell ref="J183:N183"/>
+    <mergeCell ref="J184:N184"/>
+    <mergeCell ref="J185:N185"/>
+    <mergeCell ref="J186:N186"/>
+    <mergeCell ref="J187:N187"/>
+    <mergeCell ref="J174:N174"/>
+    <mergeCell ref="J162:N162"/>
+    <mergeCell ref="J180:N180"/>
+    <mergeCell ref="J177:N177"/>
+    <mergeCell ref="J168:N168"/>
+    <mergeCell ref="J175:N175"/>
+    <mergeCell ref="J179:N179"/>
+    <mergeCell ref="J166:N166"/>
+    <mergeCell ref="J178:N178"/>
+    <mergeCell ref="J189:N189"/>
+    <mergeCell ref="J172:N172"/>
+    <mergeCell ref="C189:H189"/>
+    <mergeCell ref="J161:N161"/>
+    <mergeCell ref="C169:H169"/>
+    <mergeCell ref="C167:H167"/>
+    <mergeCell ref="C188:H188"/>
+    <mergeCell ref="C185:H185"/>
+    <mergeCell ref="C181:H181"/>
+    <mergeCell ref="C182:H182"/>
+    <mergeCell ref="C187:H187"/>
+    <mergeCell ref="J173:N173"/>
+    <mergeCell ref="C183:H183"/>
+    <mergeCell ref="C179:H179"/>
+    <mergeCell ref="C166:H166"/>
+    <mergeCell ref="C168:H168"/>
+    <mergeCell ref="C173:H173"/>
+    <mergeCell ref="C172:H172"/>
+    <mergeCell ref="C171:H171"/>
+    <mergeCell ref="C164:H164"/>
+    <mergeCell ref="C178:H178"/>
+    <mergeCell ref="J167:N167"/>
+    <mergeCell ref="J169:N169"/>
+    <mergeCell ref="J188:N188"/>
+    <mergeCell ref="J181:N181"/>
+    <mergeCell ref="C162:H162"/>
+    <mergeCell ref="C184:H184"/>
+    <mergeCell ref="C174:H174"/>
+    <mergeCell ref="C186:H186"/>
+    <mergeCell ref="C175:H175"/>
+    <mergeCell ref="C180:H180"/>
+    <mergeCell ref="J157:N157"/>
+    <mergeCell ref="J152:N152"/>
+    <mergeCell ref="C176:H176"/>
+    <mergeCell ref="C177:H177"/>
+    <mergeCell ref="C165:H165"/>
+    <mergeCell ref="C159:H159"/>
+    <mergeCell ref="C160:H160"/>
+    <mergeCell ref="C163:H163"/>
+    <mergeCell ref="J164:N164"/>
+    <mergeCell ref="J163:N163"/>
+    <mergeCell ref="J171:N171"/>
+    <mergeCell ref="C170:H170"/>
+    <mergeCell ref="J165:N165"/>
+    <mergeCell ref="C161:H161"/>
+    <mergeCell ref="J159:N159"/>
+    <mergeCell ref="J158:N158"/>
+    <mergeCell ref="J154:N154"/>
+    <mergeCell ref="C158:H158"/>
+    <mergeCell ref="J156:N156"/>
+    <mergeCell ref="B4:B7"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="B10:B24"/>
+    <mergeCell ref="C61:F61"/>
+    <mergeCell ref="J36:L36"/>
+    <mergeCell ref="J37:L37"/>
+    <mergeCell ref="J38:L38"/>
+    <mergeCell ref="C54:D54"/>
+    <mergeCell ref="J61:N61"/>
+    <mergeCell ref="B58:P58"/>
+    <mergeCell ref="J27:M27"/>
+    <mergeCell ref="C53:D53"/>
+    <mergeCell ref="O53:P53"/>
+    <mergeCell ref="O54:P54"/>
+    <mergeCell ref="B52:G52"/>
+    <mergeCell ref="L50:N50"/>
+    <mergeCell ref="C12:E12"/>
+    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="C34:E34"/>
+    <mergeCell ref="C31:E31"/>
+    <mergeCell ref="C32:E32"/>
+    <mergeCell ref="J33:M33"/>
+    <mergeCell ref="J34:M34"/>
+    <mergeCell ref="C22:E22"/>
     <mergeCell ref="C130:H130"/>
     <mergeCell ref="C129:H129"/>
     <mergeCell ref="C141:H141"/>
@@ -8827,230 +8983,77 @@
     <mergeCell ref="J144:N144"/>
     <mergeCell ref="J151:N151"/>
     <mergeCell ref="J143:N143"/>
-    <mergeCell ref="B4:B7"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="B10:B24"/>
-    <mergeCell ref="C61:F61"/>
-    <mergeCell ref="J36:L36"/>
-    <mergeCell ref="J37:L37"/>
-    <mergeCell ref="J38:L38"/>
-    <mergeCell ref="C54:D54"/>
-    <mergeCell ref="J61:N61"/>
-    <mergeCell ref="B58:P58"/>
-    <mergeCell ref="J27:M27"/>
-    <mergeCell ref="C53:D53"/>
-    <mergeCell ref="O53:P53"/>
-    <mergeCell ref="O54:P54"/>
-    <mergeCell ref="B52:G52"/>
-    <mergeCell ref="L50:N50"/>
-    <mergeCell ref="C12:E12"/>
-    <mergeCell ref="C20:E20"/>
-    <mergeCell ref="C34:E34"/>
-    <mergeCell ref="C31:E31"/>
-    <mergeCell ref="C32:E32"/>
-    <mergeCell ref="J33:M33"/>
-    <mergeCell ref="J34:M34"/>
-    <mergeCell ref="C22:E22"/>
-    <mergeCell ref="C184:H184"/>
-    <mergeCell ref="C174:H174"/>
-    <mergeCell ref="C186:H186"/>
-    <mergeCell ref="C175:H175"/>
-    <mergeCell ref="C180:H180"/>
-    <mergeCell ref="J157:N157"/>
-    <mergeCell ref="J152:N152"/>
-    <mergeCell ref="C176:H176"/>
-    <mergeCell ref="C177:H177"/>
-    <mergeCell ref="C165:H165"/>
-    <mergeCell ref="C159:H159"/>
-    <mergeCell ref="C160:H160"/>
-    <mergeCell ref="C163:H163"/>
-    <mergeCell ref="J164:N164"/>
-    <mergeCell ref="J163:N163"/>
-    <mergeCell ref="J171:N171"/>
-    <mergeCell ref="C170:H170"/>
-    <mergeCell ref="J165:N165"/>
-    <mergeCell ref="C161:H161"/>
-    <mergeCell ref="J159:N159"/>
-    <mergeCell ref="J158:N158"/>
-    <mergeCell ref="J154:N154"/>
-    <mergeCell ref="C158:H158"/>
-    <mergeCell ref="J156:N156"/>
-    <mergeCell ref="C189:H189"/>
-    <mergeCell ref="J161:N161"/>
-    <mergeCell ref="C169:H169"/>
-    <mergeCell ref="C167:H167"/>
-    <mergeCell ref="C188:H188"/>
-    <mergeCell ref="C185:H185"/>
-    <mergeCell ref="C181:H181"/>
-    <mergeCell ref="C182:H182"/>
-    <mergeCell ref="C187:H187"/>
-    <mergeCell ref="J173:N173"/>
-    <mergeCell ref="C183:H183"/>
-    <mergeCell ref="C179:H179"/>
-    <mergeCell ref="C166:H166"/>
-    <mergeCell ref="C168:H168"/>
-    <mergeCell ref="C173:H173"/>
-    <mergeCell ref="C172:H172"/>
-    <mergeCell ref="C171:H171"/>
-    <mergeCell ref="C164:H164"/>
-    <mergeCell ref="C178:H178"/>
-    <mergeCell ref="J167:N167"/>
-    <mergeCell ref="J169:N169"/>
-    <mergeCell ref="J188:N188"/>
-    <mergeCell ref="J181:N181"/>
-    <mergeCell ref="C162:H162"/>
-    <mergeCell ref="J190:N190"/>
-    <mergeCell ref="J170:N170"/>
-    <mergeCell ref="J176:N176"/>
-    <mergeCell ref="J160:N160"/>
-    <mergeCell ref="J182:N182"/>
-    <mergeCell ref="J183:N183"/>
-    <mergeCell ref="J184:N184"/>
-    <mergeCell ref="J185:N185"/>
-    <mergeCell ref="J186:N186"/>
-    <mergeCell ref="J187:N187"/>
-    <mergeCell ref="J174:N174"/>
-    <mergeCell ref="J162:N162"/>
-    <mergeCell ref="J180:N180"/>
-    <mergeCell ref="J177:N177"/>
-    <mergeCell ref="J168:N168"/>
-    <mergeCell ref="J175:N175"/>
-    <mergeCell ref="J179:N179"/>
-    <mergeCell ref="J166:N166"/>
-    <mergeCell ref="J178:N178"/>
-    <mergeCell ref="J189:N189"/>
-    <mergeCell ref="J172:N172"/>
-    <mergeCell ref="C144:H144"/>
-    <mergeCell ref="C143:H143"/>
-    <mergeCell ref="C145:H145"/>
-    <mergeCell ref="J155:N155"/>
-    <mergeCell ref="C154:H154"/>
-    <mergeCell ref="J149:N149"/>
-    <mergeCell ref="C151:H151"/>
-    <mergeCell ref="C149:H149"/>
-    <mergeCell ref="C148:H148"/>
-    <mergeCell ref="C131:H131"/>
-    <mergeCell ref="C133:H133"/>
-    <mergeCell ref="J129:N129"/>
-    <mergeCell ref="J126:N126"/>
-    <mergeCell ref="J125:N125"/>
-    <mergeCell ref="C126:H126"/>
-    <mergeCell ref="J130:N130"/>
-    <mergeCell ref="J142:N142"/>
-    <mergeCell ref="J138:N138"/>
-    <mergeCell ref="J141:N141"/>
-    <mergeCell ref="J133:N133"/>
-    <mergeCell ref="J132:N132"/>
-    <mergeCell ref="J135:N135"/>
-    <mergeCell ref="C132:H132"/>
-    <mergeCell ref="J137:N137"/>
-    <mergeCell ref="J140:N140"/>
-    <mergeCell ref="J136:N136"/>
-    <mergeCell ref="C137:H137"/>
-    <mergeCell ref="J139:N139"/>
-    <mergeCell ref="C139:H139"/>
-    <mergeCell ref="C140:H140"/>
-    <mergeCell ref="C134:H134"/>
-    <mergeCell ref="C135:H135"/>
-    <mergeCell ref="C138:H138"/>
-    <mergeCell ref="J122:N122"/>
-    <mergeCell ref="J118:N118"/>
-    <mergeCell ref="J114:N114"/>
-    <mergeCell ref="J117:N117"/>
-    <mergeCell ref="J128:N128"/>
-    <mergeCell ref="C125:H125"/>
-    <mergeCell ref="C124:H124"/>
-    <mergeCell ref="C122:H122"/>
-    <mergeCell ref="J123:N123"/>
-    <mergeCell ref="J121:N121"/>
-    <mergeCell ref="C115:H115"/>
-    <mergeCell ref="C114:H114"/>
-    <mergeCell ref="C127:H127"/>
-    <mergeCell ref="J124:N124"/>
-    <mergeCell ref="C118:H118"/>
-    <mergeCell ref="J116:N116"/>
-    <mergeCell ref="C116:H116"/>
-    <mergeCell ref="J119:N119"/>
-    <mergeCell ref="C123:H123"/>
-    <mergeCell ref="J115:N115"/>
-    <mergeCell ref="J120:N120"/>
-    <mergeCell ref="C121:H121"/>
-    <mergeCell ref="J127:N127"/>
-    <mergeCell ref="C128:H128"/>
-    <mergeCell ref="C120:H120"/>
-    <mergeCell ref="J109:N109"/>
-    <mergeCell ref="J111:N111"/>
-    <mergeCell ref="J110:N110"/>
-    <mergeCell ref="J108:N108"/>
-    <mergeCell ref="J106:N106"/>
-    <mergeCell ref="C107:H107"/>
-    <mergeCell ref="C117:H117"/>
-    <mergeCell ref="C112:H112"/>
-    <mergeCell ref="C111:H111"/>
-    <mergeCell ref="J107:N107"/>
-    <mergeCell ref="J113:N113"/>
-    <mergeCell ref="J112:N112"/>
-    <mergeCell ref="C109:H109"/>
-    <mergeCell ref="C119:H119"/>
-    <mergeCell ref="C113:H113"/>
-    <mergeCell ref="C110:H110"/>
-    <mergeCell ref="C108:H108"/>
-    <mergeCell ref="C105:H105"/>
-    <mergeCell ref="C103:H103"/>
-    <mergeCell ref="C104:H104"/>
-    <mergeCell ref="J99:N99"/>
-    <mergeCell ref="J100:N100"/>
-    <mergeCell ref="C106:H106"/>
-    <mergeCell ref="J92:O92"/>
-    <mergeCell ref="J93:O93"/>
-    <mergeCell ref="J95:N95"/>
-    <mergeCell ref="J94:N94"/>
-    <mergeCell ref="J103:N103"/>
-    <mergeCell ref="J101:N101"/>
-    <mergeCell ref="J104:N104"/>
-    <mergeCell ref="J102:N102"/>
-    <mergeCell ref="J105:N105"/>
-    <mergeCell ref="C102:H102"/>
-    <mergeCell ref="J97:N97"/>
-    <mergeCell ref="J96:N96"/>
-    <mergeCell ref="V20:W20"/>
-    <mergeCell ref="C60:F60"/>
-    <mergeCell ref="C55:D55"/>
-    <mergeCell ref="F55:G55"/>
-    <mergeCell ref="K55:M55"/>
-    <mergeCell ref="O55:P55"/>
-    <mergeCell ref="J60:N60"/>
-    <mergeCell ref="F53:G53"/>
-    <mergeCell ref="C24:E24"/>
-    <mergeCell ref="C28:E28"/>
-    <mergeCell ref="C29:E29"/>
-    <mergeCell ref="J22:M22"/>
-    <mergeCell ref="O24:P24"/>
-    <mergeCell ref="J25:M25"/>
-    <mergeCell ref="J26:M26"/>
-    <mergeCell ref="J29:M29"/>
-    <mergeCell ref="J32:M32"/>
-    <mergeCell ref="J24:M24"/>
-    <mergeCell ref="J31:M31"/>
-    <mergeCell ref="J28:M28"/>
-    <mergeCell ref="J30:M30"/>
-    <mergeCell ref="C25:E25"/>
-    <mergeCell ref="C26:E26"/>
-    <mergeCell ref="C30:E30"/>
-    <mergeCell ref="J91:O91"/>
-    <mergeCell ref="J90:O90"/>
-    <mergeCell ref="J88:O88"/>
-    <mergeCell ref="J89:O89"/>
-    <mergeCell ref="J86:O86"/>
-    <mergeCell ref="J87:O87"/>
-    <mergeCell ref="C56:D56"/>
-    <mergeCell ref="F56:G56"/>
-    <mergeCell ref="K56:M56"/>
-    <mergeCell ref="O56:P56"/>
-    <mergeCell ref="J85:O85"/>
+    <mergeCell ref="C15:E15"/>
+    <mergeCell ref="C19:E19"/>
+    <mergeCell ref="J20:M20"/>
+    <mergeCell ref="J21:M21"/>
+    <mergeCell ref="T12:U12"/>
+    <mergeCell ref="T13:U13"/>
+    <mergeCell ref="S20:U20"/>
+    <mergeCell ref="T17:U17"/>
+    <mergeCell ref="T18:U18"/>
+    <mergeCell ref="T15:U15"/>
+    <mergeCell ref="T16:U16"/>
+    <mergeCell ref="J17:M17"/>
+    <mergeCell ref="J18:M18"/>
+    <mergeCell ref="J15:M15"/>
+    <mergeCell ref="C16:E16"/>
+    <mergeCell ref="J16:M16"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="C18:E18"/>
+    <mergeCell ref="C17:E17"/>
+    <mergeCell ref="J19:M19"/>
+    <mergeCell ref="T14:U14"/>
+    <mergeCell ref="J14:M14"/>
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="C1:J1"/>
+    <mergeCell ref="J3:P3"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="J13:M13"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="L10:M10"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="P11:R11"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="J11:K11"/>
+    <mergeCell ref="C10:E10"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="L11:M11"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="F54:G54"/>
+    <mergeCell ref="J49:K49"/>
+    <mergeCell ref="K53:M53"/>
+    <mergeCell ref="Q36:R36"/>
+    <mergeCell ref="Q42:R42"/>
+    <mergeCell ref="Q43:R43"/>
+    <mergeCell ref="Q40:R40"/>
+    <mergeCell ref="Q50:R50"/>
+    <mergeCell ref="Q37:R37"/>
+    <mergeCell ref="Q38:R38"/>
+    <mergeCell ref="J41:L41"/>
+    <mergeCell ref="Q41:R41"/>
+    <mergeCell ref="J47:K47"/>
+    <mergeCell ref="J42:M42"/>
+    <mergeCell ref="Q39:R39"/>
+    <mergeCell ref="J45:K45"/>
+    <mergeCell ref="J39:L39"/>
+    <mergeCell ref="J46:K46"/>
+    <mergeCell ref="J43:N43"/>
+    <mergeCell ref="J40:L40"/>
+    <mergeCell ref="J48:K48"/>
+    <mergeCell ref="J52:P52"/>
+    <mergeCell ref="K54:M54"/>
   </mergeCells>
   <phoneticPr fontId="38" alignment="center"/>
-  <conditionalFormatting sqref="A58:A59 A1:A50">
+  <conditionalFormatting sqref="A1:A50 A58:A59">
     <cfRule type="expression" dxfId="10" priority="6250">
       <formula>MOD(ROW(),2)</formula>
     </cfRule>
@@ -9096,242 +9099,242 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AE72"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="20.42578125" customWidth="1"/>
-    <col min="2" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="10.7109375" customWidth="1"/>
-    <col min="7" max="8" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.28515625" customWidth="1"/>
-    <col min="10" max="10" width="11.7109375" customWidth="1"/>
+    <col min="1" max="1" width="20.359375" customWidth="1"/>
+    <col min="2" max="3" width="11.0546875" customWidth="1"/>
+    <col min="4" max="4" width="11.19140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="10.65234375" customWidth="1"/>
+    <col min="7" max="8" width="11.19140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.32421875" customWidth="1"/>
+    <col min="10" max="10" width="11.73046875" customWidth="1"/>
     <col min="11" max="11" width="12" customWidth="1"/>
-    <col min="12" max="12" width="11.28515625" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" customWidth="1"/>
-    <col min="14" max="14" width="13.7109375" customWidth="1"/>
-    <col min="15" max="15" width="12.42578125" customWidth="1"/>
-    <col min="16" max="16" width="11.7109375" customWidth="1"/>
-    <col min="17" max="17" width="11.5703125" customWidth="1"/>
-    <col min="18" max="18" width="13.7109375" customWidth="1"/>
-    <col min="19" max="19" width="13.140625" customWidth="1"/>
-    <col min="20" max="20" width="16" customWidth="1"/>
-    <col min="21" max="21" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" customWidth="1"/>
-    <col min="23" max="23" width="13.85546875" customWidth="1"/>
-    <col min="24" max="24" width="11" customWidth="1"/>
+    <col min="12" max="12" width="11.32421875" customWidth="1"/>
+    <col min="13" max="13" width="14.29296875" customWidth="1"/>
+    <col min="14" max="14" width="13.75390625" customWidth="1"/>
+    <col min="15" max="15" width="12.40625" customWidth="1"/>
+    <col min="16" max="16" width="11.73046875" customWidth="1"/>
+    <col min="17" max="17" width="11.59375" customWidth="1"/>
+    <col min="18" max="18" width="13.75390625" customWidth="1"/>
+    <col min="19" max="19" width="13.078125" customWidth="1"/>
+    <col min="20" max="20" width="16.046875" customWidth="1"/>
+    <col min="21" max="21" width="13.484375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5625" customWidth="1"/>
+    <col min="23" max="23" width="13.88671875" customWidth="1"/>
+    <col min="24" max="24" width="11.0546875" customWidth="1"/>
     <col min="25" max="26" width="12" customWidth="1"/>
-    <col min="27" max="27" width="13.85546875" customWidth="1"/>
-    <col min="28" max="28" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="13.85546875" customWidth="1"/>
-    <col min="30" max="30" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.28515625" customWidth="1"/>
+    <col min="27" max="27" width="13.88671875" customWidth="1"/>
+    <col min="28" max="28" width="11.19140625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="13.88671875" customWidth="1"/>
+    <col min="30" max="30" width="11.19140625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.29296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="22.5">
+    <row r="1" spans="1:31" ht="21.75" x14ac:dyDescent="0.25">
       <c r="A1" s="211"/>
-      <c r="B1" s="565" t="s">
+      <c r="B1" s="464" t="s">
         <v>90</v>
       </c>
-      <c r="C1" s="565"/>
-      <c r="D1" s="565"/>
-      <c r="E1" s="565"/>
-      <c r="F1" s="565"/>
-      <c r="G1" s="565"/>
-      <c r="H1" s="565"/>
-      <c r="I1" s="565"/>
-      <c r="J1" s="565"/>
-      <c r="K1" s="565"/>
-      <c r="L1" s="565"/>
-      <c r="M1" s="565"/>
-      <c r="N1" s="565"/>
-      <c r="O1" s="565"/>
-      <c r="P1" s="565"/>
-      <c r="Q1" s="565"/>
-      <c r="R1" s="565"/>
-      <c r="S1" s="565"/>
-      <c r="T1" s="565"/>
-      <c r="U1" s="565"/>
-      <c r="V1" s="565"/>
-      <c r="W1" s="565"/>
-      <c r="X1" s="565"/>
+      <c r="C1" s="464"/>
+      <c r="D1" s="464"/>
+      <c r="E1" s="464"/>
+      <c r="F1" s="464"/>
+      <c r="G1" s="464"/>
+      <c r="H1" s="464"/>
+      <c r="I1" s="464"/>
+      <c r="J1" s="464"/>
+      <c r="K1" s="464"/>
+      <c r="L1" s="464"/>
+      <c r="M1" s="464"/>
+      <c r="N1" s="464"/>
+      <c r="O1" s="464"/>
+      <c r="P1" s="464"/>
+      <c r="Q1" s="464"/>
+      <c r="R1" s="464"/>
+      <c r="S1" s="464"/>
+      <c r="T1" s="464"/>
+      <c r="U1" s="464"/>
+      <c r="V1" s="464"/>
+      <c r="W1" s="464"/>
+      <c r="X1" s="464"/>
       <c r="Y1" s="212"/>
       <c r="Z1" s="212"/>
       <c r="AA1" s="213" t="s">
         <v>24</v>
       </c>
-      <c r="AB1" s="566" t="s">
+      <c r="AB1" s="465" t="s">
         <v>237</v>
       </c>
-      <c r="AC1" s="566"/>
-      <c r="AD1" s="566"/>
-      <c r="AE1" s="566"/>
-    </row>
-    <row r="2" spans="1:31" ht="20.25" customHeight="1">
-      <c r="A2" s="554" t="s">
+      <c r="AC1" s="465"/>
+      <c r="AD1" s="465"/>
+      <c r="AE1" s="465"/>
+    </row>
+    <row r="2" spans="1:31" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="466" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="568" t="s">
+      <c r="B2" s="469" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="569"/>
-      <c r="D2" s="569"/>
-      <c r="E2" s="569"/>
-      <c r="F2" s="569"/>
-      <c r="G2" s="569"/>
-      <c r="H2" s="569"/>
-      <c r="I2" s="569"/>
-      <c r="J2" s="569"/>
-      <c r="K2" s="569"/>
-      <c r="L2" s="569"/>
-      <c r="M2" s="569"/>
-      <c r="N2" s="569"/>
-      <c r="O2" s="569"/>
-      <c r="P2" s="569"/>
-      <c r="Q2" s="569"/>
-      <c r="R2" s="569"/>
-      <c r="S2" s="569"/>
-      <c r="T2" s="569"/>
-      <c r="U2" s="569"/>
-      <c r="V2" s="569"/>
-      <c r="W2" s="570"/>
-      <c r="X2" s="571"/>
-      <c r="Y2" s="572"/>
-      <c r="Z2" s="572"/>
-      <c r="AA2" s="572"/>
-      <c r="AB2" s="572"/>
-      <c r="AC2" s="572"/>
-      <c r="AD2" s="573"/>
-      <c r="AE2" s="574" t="s">
+      <c r="C2" s="470"/>
+      <c r="D2" s="470"/>
+      <c r="E2" s="470"/>
+      <c r="F2" s="470"/>
+      <c r="G2" s="470"/>
+      <c r="H2" s="470"/>
+      <c r="I2" s="470"/>
+      <c r="J2" s="470"/>
+      <c r="K2" s="470"/>
+      <c r="L2" s="470"/>
+      <c r="M2" s="470"/>
+      <c r="N2" s="470"/>
+      <c r="O2" s="470"/>
+      <c r="P2" s="470"/>
+      <c r="Q2" s="470"/>
+      <c r="R2" s="470"/>
+      <c r="S2" s="470"/>
+      <c r="T2" s="470"/>
+      <c r="U2" s="470"/>
+      <c r="V2" s="470"/>
+      <c r="W2" s="471"/>
+      <c r="X2" s="472"/>
+      <c r="Y2" s="473"/>
+      <c r="Z2" s="473"/>
+      <c r="AA2" s="473"/>
+      <c r="AB2" s="473"/>
+      <c r="AC2" s="473"/>
+      <c r="AD2" s="474"/>
+      <c r="AE2" s="475" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="3" spans="1:31" ht="15.75" customHeight="1">
-      <c r="A3" s="567"/>
-      <c r="B3" s="551" t="s">
+    <row r="3" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="467"/>
+      <c r="B3" s="478" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="553"/>
-      <c r="D3" s="552"/>
-      <c r="E3" s="551" t="s">
+      <c r="C3" s="479"/>
+      <c r="D3" s="480"/>
+      <c r="E3" s="478" t="s">
         <v>28</v>
       </c>
-      <c r="F3" s="553"/>
-      <c r="G3" s="553"/>
-      <c r="H3" s="553"/>
-      <c r="I3" s="553"/>
-      <c r="J3" s="553"/>
-      <c r="K3" s="553"/>
-      <c r="L3" s="553"/>
-      <c r="M3" s="553"/>
-      <c r="N3" s="553"/>
-      <c r="O3" s="553"/>
-      <c r="P3" s="553"/>
-      <c r="Q3" s="553"/>
-      <c r="R3" s="552"/>
+      <c r="F3" s="479"/>
+      <c r="G3" s="479"/>
+      <c r="H3" s="479"/>
+      <c r="I3" s="479"/>
+      <c r="J3" s="479"/>
+      <c r="K3" s="479"/>
+      <c r="L3" s="479"/>
+      <c r="M3" s="479"/>
+      <c r="N3" s="479"/>
+      <c r="O3" s="479"/>
+      <c r="P3" s="479"/>
+      <c r="Q3" s="479"/>
+      <c r="R3" s="480"/>
       <c r="S3" s="225"/>
       <c r="T3" s="225"/>
-      <c r="U3" s="577" t="s">
+      <c r="U3" s="481" t="s">
         <v>62</v>
       </c>
-      <c r="V3" s="578"/>
-      <c r="W3" s="579"/>
-      <c r="X3" s="586" t="s">
+      <c r="V3" s="482"/>
+      <c r="W3" s="483"/>
+      <c r="X3" s="490" t="s">
         <v>64</v>
       </c>
-      <c r="Y3" s="587"/>
-      <c r="Z3" s="587"/>
-      <c r="AA3" s="588"/>
-      <c r="AB3" s="586" t="s">
+      <c r="Y3" s="491"/>
+      <c r="Z3" s="491"/>
+      <c r="AA3" s="492"/>
+      <c r="AB3" s="490" t="s">
         <v>65</v>
       </c>
-      <c r="AC3" s="587"/>
-      <c r="AD3" s="588"/>
-      <c r="AE3" s="575"/>
-    </row>
-    <row r="4" spans="1:31" ht="18.75" customHeight="1">
-      <c r="A4" s="567"/>
-      <c r="B4" s="554" t="s">
+      <c r="AC3" s="491"/>
+      <c r="AD3" s="492"/>
+      <c r="AE3" s="476"/>
+    </row>
+    <row r="4" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="467"/>
+      <c r="B4" s="466" t="s">
         <v>61</v>
       </c>
-      <c r="C4" s="554" t="s">
-        <v>2</v>
-      </c>
-      <c r="D4" s="554" t="s">
+      <c r="C4" s="466" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="466" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="551" t="s">
+      <c r="E4" s="478" t="s">
         <v>30</v>
       </c>
-      <c r="F4" s="553"/>
-      <c r="G4" s="553"/>
-      <c r="H4" s="553"/>
-      <c r="I4" s="553"/>
-      <c r="J4" s="553"/>
-      <c r="K4" s="553"/>
-      <c r="L4" s="553"/>
-      <c r="M4" s="552"/>
-      <c r="N4" s="551"/>
-      <c r="O4" s="553"/>
-      <c r="P4" s="553"/>
-      <c r="Q4" s="553"/>
-      <c r="R4" s="552"/>
+      <c r="F4" s="479"/>
+      <c r="G4" s="479"/>
+      <c r="H4" s="479"/>
+      <c r="I4" s="479"/>
+      <c r="J4" s="479"/>
+      <c r="K4" s="479"/>
+      <c r="L4" s="479"/>
+      <c r="M4" s="480"/>
+      <c r="N4" s="478"/>
+      <c r="O4" s="479"/>
+      <c r="P4" s="479"/>
+      <c r="Q4" s="479"/>
+      <c r="R4" s="480"/>
       <c r="S4" s="226"/>
       <c r="T4" s="226"/>
-      <c r="U4" s="580"/>
-      <c r="V4" s="581"/>
-      <c r="W4" s="582"/>
-      <c r="X4" s="556" t="s">
+      <c r="U4" s="484"/>
+      <c r="V4" s="485"/>
+      <c r="W4" s="486"/>
+      <c r="X4" s="493" t="s">
         <v>31</v>
       </c>
-      <c r="Y4" s="557"/>
-      <c r="Z4" s="558"/>
-      <c r="AA4" s="562" t="s">
+      <c r="Y4" s="494"/>
+      <c r="Z4" s="495"/>
+      <c r="AA4" s="499" t="s">
         <v>32</v>
       </c>
-      <c r="AB4" s="562" t="s">
+      <c r="AB4" s="499" t="s">
         <v>31</v>
       </c>
-      <c r="AC4" s="562" t="s">
+      <c r="AC4" s="499" t="s">
         <v>84</v>
       </c>
-      <c r="AD4" s="562" t="s">
+      <c r="AD4" s="499" t="s">
         <v>32</v>
       </c>
-      <c r="AE4" s="575"/>
-    </row>
-    <row r="5" spans="1:31" ht="28.5" customHeight="1">
-      <c r="A5" s="567"/>
-      <c r="B5" s="567"/>
-      <c r="C5" s="567"/>
-      <c r="D5" s="567"/>
-      <c r="E5" s="551" t="s">
+      <c r="AE4" s="476"/>
+    </row>
+    <row r="5" spans="1:31" ht="28.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="467"/>
+      <c r="B5" s="467"/>
+      <c r="C5" s="467"/>
+      <c r="D5" s="467"/>
+      <c r="E5" s="478" t="s">
         <v>33</v>
       </c>
-      <c r="F5" s="552"/>
-      <c r="G5" s="551" t="s">
+      <c r="F5" s="480"/>
+      <c r="G5" s="478" t="s">
         <v>34</v>
       </c>
-      <c r="H5" s="552"/>
-      <c r="I5" s="551" t="s">
+      <c r="H5" s="480"/>
+      <c r="I5" s="478" t="s">
         <v>69</v>
       </c>
-      <c r="J5" s="553"/>
-      <c r="K5" s="552"/>
+      <c r="J5" s="479"/>
+      <c r="K5" s="480"/>
       <c r="L5" s="227" t="s">
         <v>88</v>
       </c>
-      <c r="M5" s="554" t="s">
+      <c r="M5" s="466" t="s">
         <v>35</v>
       </c>
-      <c r="N5" s="551"/>
-      <c r="O5" s="553"/>
-      <c r="P5" s="553"/>
-      <c r="Q5" s="552"/>
+      <c r="N5" s="478"/>
+      <c r="O5" s="479"/>
+      <c r="P5" s="479"/>
+      <c r="Q5" s="480"/>
       <c r="R5" s="228" t="s">
         <v>47</v>
       </c>
@@ -9341,23 +9344,23 @@
       <c r="T5" s="228" t="s">
         <v>76</v>
       </c>
-      <c r="U5" s="583"/>
-      <c r="V5" s="584"/>
-      <c r="W5" s="585"/>
-      <c r="X5" s="559"/>
-      <c r="Y5" s="560"/>
-      <c r="Z5" s="561"/>
-      <c r="AA5" s="563"/>
-      <c r="AB5" s="563"/>
-      <c r="AC5" s="563"/>
-      <c r="AD5" s="563"/>
-      <c r="AE5" s="575"/>
-    </row>
-    <row r="6" spans="1:31" ht="17.25" customHeight="1">
-      <c r="A6" s="555"/>
-      <c r="B6" s="555"/>
-      <c r="C6" s="555"/>
-      <c r="D6" s="555"/>
+      <c r="U5" s="487"/>
+      <c r="V5" s="488"/>
+      <c r="W5" s="489"/>
+      <c r="X5" s="496"/>
+      <c r="Y5" s="497"/>
+      <c r="Z5" s="498"/>
+      <c r="AA5" s="500"/>
+      <c r="AB5" s="500"/>
+      <c r="AC5" s="500"/>
+      <c r="AD5" s="500"/>
+      <c r="AE5" s="476"/>
+    </row>
+    <row r="6" spans="1:31" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="468"/>
+      <c r="B6" s="468"/>
+      <c r="C6" s="468"/>
+      <c r="D6" s="468"/>
       <c r="E6" s="228" t="s">
         <v>61</v>
       </c>
@@ -9382,7 +9385,7 @@
       <c r="L6" s="228" t="s">
         <v>77</v>
       </c>
-      <c r="M6" s="555"/>
+      <c r="M6" s="468"/>
       <c r="N6" s="228" t="s">
         <v>36</v>
       </c>
@@ -9422,13 +9425,13 @@
       <c r="Z6" s="230" t="s">
         <v>150</v>
       </c>
-      <c r="AA6" s="564"/>
-      <c r="AB6" s="564"/>
-      <c r="AC6" s="564"/>
-      <c r="AD6" s="564"/>
-      <c r="AE6" s="576"/>
-    </row>
-    <row r="7" spans="1:31" ht="33.75" customHeight="1">
+      <c r="AA6" s="501"/>
+      <c r="AB6" s="501"/>
+      <c r="AC6" s="501"/>
+      <c r="AD6" s="501"/>
+      <c r="AE6" s="477"/>
+    </row>
+    <row r="7" spans="1:31" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="236">
         <v>46113</v>
       </c>
@@ -9529,7 +9532,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="8" spans="1:31" ht="33.75" customHeight="1">
+    <row r="8" spans="1:31" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="236">
         <v>46143</v>
       </c>
@@ -9630,7 +9633,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="9" spans="1:31" ht="33.75" customHeight="1">
+    <row r="9" spans="1:31" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="236">
         <v>46174</v>
       </c>
@@ -9731,7 +9734,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="10" spans="1:31" ht="33.75" customHeight="1">
+    <row r="10" spans="1:31" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="236">
         <v>46204</v>
       </c>
@@ -9832,7 +9835,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="11" spans="1:31" ht="33.75" customHeight="1">
+    <row r="11" spans="1:31" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="236">
         <v>46235</v>
       </c>
@@ -9933,7 +9936,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="12" spans="1:31" ht="35.25" customHeight="1">
+    <row r="12" spans="1:31" ht="35.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="250" t="s">
         <v>5</v>
       </c>
@@ -10058,206 +10061,206 @@
         <v>1858</v>
       </c>
     </row>
-    <row r="13" spans="1:31" ht="22.5">
-      <c r="A13" s="532" t="s">
+    <row r="13" spans="1:31" ht="21.75" x14ac:dyDescent="0.15">
+      <c r="A13" s="502" t="s">
         <v>171</v>
       </c>
-      <c r="B13" s="532"/>
-      <c r="C13" s="532"/>
-      <c r="D13" s="532"/>
-      <c r="E13" s="532"/>
-      <c r="F13" s="532"/>
-      <c r="G13" s="532"/>
-      <c r="H13" s="532"/>
-      <c r="I13" s="532"/>
-      <c r="J13" s="532"/>
-      <c r="K13" s="532"/>
-      <c r="L13" s="532"/>
-      <c r="M13" s="532"/>
-      <c r="N13" s="532"/>
-      <c r="O13" s="532"/>
-      <c r="P13" s="532"/>
-      <c r="Q13" s="532"/>
-      <c r="R13" s="532"/>
-      <c r="S13" s="532"/>
-      <c r="T13" s="532"/>
-      <c r="U13" s="532"/>
-      <c r="V13" s="532"/>
-      <c r="W13" s="532"/>
-      <c r="X13" s="532"/>
-      <c r="Y13" s="532"/>
-      <c r="Z13" s="532"/>
-      <c r="AA13" s="532"/>
-      <c r="AB13" s="532"/>
-      <c r="AC13" s="532"/>
-      <c r="AD13" s="532"/>
-      <c r="AE13" s="532"/>
-    </row>
-    <row r="14" spans="1:31" ht="26.25" customHeight="1">
-      <c r="A14" s="520" t="s">
+      <c r="B13" s="502"/>
+      <c r="C13" s="502"/>
+      <c r="D13" s="502"/>
+      <c r="E13" s="502"/>
+      <c r="F13" s="502"/>
+      <c r="G13" s="502"/>
+      <c r="H13" s="502"/>
+      <c r="I13" s="502"/>
+      <c r="J13" s="502"/>
+      <c r="K13" s="502"/>
+      <c r="L13" s="502"/>
+      <c r="M13" s="502"/>
+      <c r="N13" s="502"/>
+      <c r="O13" s="502"/>
+      <c r="P13" s="502"/>
+      <c r="Q13" s="502"/>
+      <c r="R13" s="502"/>
+      <c r="S13" s="502"/>
+      <c r="T13" s="502"/>
+      <c r="U13" s="502"/>
+      <c r="V13" s="502"/>
+      <c r="W13" s="502"/>
+      <c r="X13" s="502"/>
+      <c r="Y13" s="502"/>
+      <c r="Z13" s="502"/>
+      <c r="AA13" s="502"/>
+      <c r="AB13" s="502"/>
+      <c r="AC13" s="502"/>
+      <c r="AD13" s="502"/>
+      <c r="AE13" s="502"/>
+    </row>
+    <row r="14" spans="1:31" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="503" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="533" t="s">
+      <c r="B14" s="506" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="534"/>
-      <c r="D14" s="534"/>
-      <c r="E14" s="534"/>
-      <c r="F14" s="534"/>
-      <c r="G14" s="534"/>
-      <c r="H14" s="534"/>
-      <c r="I14" s="534"/>
-      <c r="J14" s="534"/>
-      <c r="K14" s="534"/>
-      <c r="L14" s="534"/>
-      <c r="M14" s="534"/>
-      <c r="N14" s="534"/>
-      <c r="O14" s="534"/>
-      <c r="P14" s="534"/>
-      <c r="Q14" s="534"/>
-      <c r="R14" s="534"/>
-      <c r="S14" s="534"/>
-      <c r="T14" s="534"/>
-      <c r="U14" s="534"/>
-      <c r="V14" s="534"/>
-      <c r="W14" s="535"/>
-      <c r="X14" s="533" t="s">
+      <c r="C14" s="507"/>
+      <c r="D14" s="507"/>
+      <c r="E14" s="507"/>
+      <c r="F14" s="507"/>
+      <c r="G14" s="507"/>
+      <c r="H14" s="507"/>
+      <c r="I14" s="507"/>
+      <c r="J14" s="507"/>
+      <c r="K14" s="507"/>
+      <c r="L14" s="507"/>
+      <c r="M14" s="507"/>
+      <c r="N14" s="507"/>
+      <c r="O14" s="507"/>
+      <c r="P14" s="507"/>
+      <c r="Q14" s="507"/>
+      <c r="R14" s="507"/>
+      <c r="S14" s="507"/>
+      <c r="T14" s="507"/>
+      <c r="U14" s="507"/>
+      <c r="V14" s="507"/>
+      <c r="W14" s="508"/>
+      <c r="X14" s="506" t="s">
         <v>27</v>
       </c>
-      <c r="Y14" s="534"/>
-      <c r="Z14" s="534"/>
-      <c r="AA14" s="534"/>
-      <c r="AB14" s="534"/>
-      <c r="AC14" s="534"/>
-      <c r="AD14" s="535"/>
-      <c r="AE14" s="536" t="s">
+      <c r="Y14" s="507"/>
+      <c r="Z14" s="507"/>
+      <c r="AA14" s="507"/>
+      <c r="AB14" s="507"/>
+      <c r="AC14" s="507"/>
+      <c r="AD14" s="508"/>
+      <c r="AE14" s="509" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="15" spans="1:31" ht="24.75" customHeight="1">
-      <c r="A15" s="521"/>
-      <c r="B15" s="533" t="s">
+    <row r="15" spans="1:31" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="504"/>
+      <c r="B15" s="506" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="534"/>
-      <c r="D15" s="535"/>
-      <c r="E15" s="533" t="s">
+      <c r="C15" s="507"/>
+      <c r="D15" s="508"/>
+      <c r="E15" s="506" t="s">
         <v>28</v>
       </c>
-      <c r="F15" s="534"/>
-      <c r="G15" s="534"/>
-      <c r="H15" s="534"/>
-      <c r="I15" s="534"/>
-      <c r="J15" s="534"/>
-      <c r="K15" s="534"/>
-      <c r="L15" s="534"/>
-      <c r="M15" s="534"/>
-      <c r="N15" s="534"/>
-      <c r="O15" s="534"/>
-      <c r="P15" s="534"/>
-      <c r="Q15" s="534"/>
-      <c r="R15" s="535"/>
+      <c r="F15" s="507"/>
+      <c r="G15" s="507"/>
+      <c r="H15" s="507"/>
+      <c r="I15" s="507"/>
+      <c r="J15" s="507"/>
+      <c r="K15" s="507"/>
+      <c r="L15" s="507"/>
+      <c r="M15" s="507"/>
+      <c r="N15" s="507"/>
+      <c r="O15" s="507"/>
+      <c r="P15" s="507"/>
+      <c r="Q15" s="507"/>
+      <c r="R15" s="508"/>
       <c r="S15" s="231"/>
       <c r="T15" s="231"/>
-      <c r="U15" s="539" t="s">
+      <c r="U15" s="512" t="s">
         <v>63</v>
       </c>
-      <c r="V15" s="540"/>
-      <c r="W15" s="541"/>
-      <c r="X15" s="523" t="s">
+      <c r="V15" s="513"/>
+      <c r="W15" s="514"/>
+      <c r="X15" s="521" t="s">
         <v>64</v>
       </c>
-      <c r="Y15" s="525"/>
-      <c r="Z15" s="525"/>
-      <c r="AA15" s="524"/>
-      <c r="AB15" s="523" t="s">
+      <c r="Y15" s="522"/>
+      <c r="Z15" s="522"/>
+      <c r="AA15" s="523"/>
+      <c r="AB15" s="521" t="s">
         <v>65</v>
       </c>
-      <c r="AC15" s="525"/>
-      <c r="AD15" s="524"/>
-      <c r="AE15" s="537"/>
-    </row>
-    <row r="16" spans="1:31" ht="25.5" customHeight="1">
-      <c r="A16" s="521"/>
-      <c r="B16" s="520" t="s">
+      <c r="AC15" s="522"/>
+      <c r="AD15" s="523"/>
+      <c r="AE15" s="510"/>
+    </row>
+    <row r="16" spans="1:31" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="504"/>
+      <c r="B16" s="503" t="s">
         <v>61</v>
       </c>
-      <c r="C16" s="520" t="s">
-        <v>2</v>
-      </c>
-      <c r="D16" s="520" t="s">
+      <c r="C16" s="503" t="s">
+        <v>2</v>
+      </c>
+      <c r="D16" s="503" t="s">
         <v>29</v>
       </c>
-      <c r="E16" s="548" t="s">
+      <c r="E16" s="524" t="s">
         <v>30</v>
       </c>
-      <c r="F16" s="549"/>
-      <c r="G16" s="549"/>
-      <c r="H16" s="549"/>
-      <c r="I16" s="549"/>
-      <c r="J16" s="549"/>
-      <c r="K16" s="549"/>
-      <c r="L16" s="549"/>
-      <c r="M16" s="550"/>
-      <c r="N16" s="523"/>
-      <c r="O16" s="525"/>
-      <c r="P16" s="525"/>
-      <c r="Q16" s="525"/>
-      <c r="R16" s="524"/>
+      <c r="F16" s="525"/>
+      <c r="G16" s="525"/>
+      <c r="H16" s="525"/>
+      <c r="I16" s="525"/>
+      <c r="J16" s="525"/>
+      <c r="K16" s="525"/>
+      <c r="L16" s="525"/>
+      <c r="M16" s="526"/>
+      <c r="N16" s="521"/>
+      <c r="O16" s="522"/>
+      <c r="P16" s="522"/>
+      <c r="Q16" s="522"/>
+      <c r="R16" s="523"/>
       <c r="S16" s="231"/>
       <c r="T16" s="231"/>
-      <c r="U16" s="542"/>
-      <c r="V16" s="543"/>
-      <c r="W16" s="544"/>
-      <c r="X16" s="526" t="s">
+      <c r="U16" s="515"/>
+      <c r="V16" s="516"/>
+      <c r="W16" s="517"/>
+      <c r="X16" s="527" t="s">
         <v>31</v>
       </c>
-      <c r="Y16" s="527"/>
-      <c r="Z16" s="528"/>
-      <c r="AA16" s="520" t="s">
+      <c r="Y16" s="528"/>
+      <c r="Z16" s="529"/>
+      <c r="AA16" s="503" t="s">
         <v>32</v>
       </c>
-      <c r="AB16" s="520" t="s">
+      <c r="AB16" s="503" t="s">
         <v>31</v>
       </c>
-      <c r="AC16" s="520" t="s">
+      <c r="AC16" s="503" t="s">
         <v>84</v>
       </c>
-      <c r="AD16" s="520" t="s">
+      <c r="AD16" s="503" t="s">
         <v>32</v>
       </c>
-      <c r="AE16" s="537"/>
-    </row>
-    <row r="17" spans="1:31" ht="33.75" customHeight="1">
-      <c r="A17" s="521"/>
-      <c r="B17" s="521"/>
-      <c r="C17" s="521"/>
-      <c r="D17" s="521"/>
-      <c r="E17" s="523" t="s">
+      <c r="AE16" s="510"/>
+    </row>
+    <row r="17" spans="1:31" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A17" s="504"/>
+      <c r="B17" s="504"/>
+      <c r="C17" s="504"/>
+      <c r="D17" s="504"/>
+      <c r="E17" s="521" t="s">
         <v>33</v>
       </c>
-      <c r="F17" s="524"/>
-      <c r="G17" s="523" t="s">
+      <c r="F17" s="523"/>
+      <c r="G17" s="521" t="s">
         <v>34</v>
       </c>
-      <c r="H17" s="524"/>
-      <c r="I17" s="523" t="s">
+      <c r="H17" s="523"/>
+      <c r="I17" s="521" t="s">
         <v>69</v>
       </c>
-      <c r="J17" s="525"/>
-      <c r="K17" s="524"/>
+      <c r="J17" s="522"/>
+      <c r="K17" s="523"/>
       <c r="L17" s="232" t="s">
         <v>88</v>
       </c>
-      <c r="M17" s="520" t="s">
+      <c r="M17" s="503" t="s">
         <v>35</v>
       </c>
-      <c r="N17" s="523" t="s">
+      <c r="N17" s="521" t="s">
         <v>48</v>
       </c>
-      <c r="O17" s="525"/>
-      <c r="P17" s="525"/>
-      <c r="Q17" s="524"/>
+      <c r="O17" s="522"/>
+      <c r="P17" s="522"/>
+      <c r="Q17" s="523"/>
       <c r="R17" s="233" t="s">
         <v>47</v>
       </c>
@@ -10267,23 +10270,23 @@
       <c r="T17" s="233" t="s">
         <v>76</v>
       </c>
-      <c r="U17" s="545"/>
-      <c r="V17" s="546"/>
-      <c r="W17" s="547"/>
-      <c r="X17" s="529"/>
-      <c r="Y17" s="530"/>
-      <c r="Z17" s="531"/>
-      <c r="AA17" s="521"/>
-      <c r="AB17" s="521"/>
-      <c r="AC17" s="521"/>
-      <c r="AD17" s="521"/>
-      <c r="AE17" s="537"/>
-    </row>
-    <row r="18" spans="1:31" ht="28.5" customHeight="1">
-      <c r="A18" s="522"/>
-      <c r="B18" s="522"/>
-      <c r="C18" s="522"/>
-      <c r="D18" s="522"/>
+      <c r="U17" s="518"/>
+      <c r="V17" s="519"/>
+      <c r="W17" s="520"/>
+      <c r="X17" s="530"/>
+      <c r="Y17" s="531"/>
+      <c r="Z17" s="532"/>
+      <c r="AA17" s="504"/>
+      <c r="AB17" s="504"/>
+      <c r="AC17" s="504"/>
+      <c r="AD17" s="504"/>
+      <c r="AE17" s="510"/>
+    </row>
+    <row r="18" spans="1:31" ht="28.5" customHeight="1" x14ac:dyDescent="0.1">
+      <c r="A18" s="505"/>
+      <c r="B18" s="505"/>
+      <c r="C18" s="505"/>
+      <c r="D18" s="505"/>
       <c r="E18" s="233" t="s">
         <v>61</v>
       </c>
@@ -10306,7 +10309,7 @@
         <v>83</v>
       </c>
       <c r="L18" s="233"/>
-      <c r="M18" s="522"/>
+      <c r="M18" s="505"/>
       <c r="N18" s="233" t="s">
         <v>151</v>
       </c>
@@ -10346,13 +10349,13 @@
       <c r="Z18" s="233" t="s">
         <v>150</v>
       </c>
-      <c r="AA18" s="522"/>
-      <c r="AB18" s="522"/>
-      <c r="AC18" s="522"/>
-      <c r="AD18" s="522"/>
-      <c r="AE18" s="538"/>
-    </row>
-    <row r="19" spans="1:31" s="215" customFormat="1" ht="54" customHeight="1">
+      <c r="AA18" s="505"/>
+      <c r="AB18" s="505"/>
+      <c r="AC18" s="505"/>
+      <c r="AD18" s="505"/>
+      <c r="AE18" s="511"/>
+    </row>
+    <row r="19" spans="1:31" s="215" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="214" t="s">
         <v>170</v>
       </c>
@@ -10453,7 +10456,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:31" s="215" customFormat="1" ht="54" customHeight="1">
+    <row r="20" spans="1:31" s="215" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="214" t="s">
         <v>173</v>
       </c>
@@ -10554,7 +10557,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="1:31" s="215" customFormat="1" ht="54" customHeight="1">
+    <row r="21" spans="1:31" s="215" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="214" t="s">
         <v>172</v>
       </c>
@@ -10655,7 +10658,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="22" spans="1:31" s="215" customFormat="1" ht="54" customHeight="1">
+    <row r="22" spans="1:31" s="215" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="214" t="s">
         <v>165</v>
       </c>
@@ -10756,7 +10759,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:31" s="215" customFormat="1" ht="54" customHeight="1">
+    <row r="23" spans="1:31" s="215" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="214" t="s">
         <v>176</v>
       </c>
@@ -10857,7 +10860,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:31" s="215" customFormat="1" ht="54" customHeight="1">
+    <row r="24" spans="1:31" s="215" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="214" t="s">
         <v>178</v>
       </c>
@@ -10958,7 +10961,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="25" spans="1:31" s="215" customFormat="1" ht="54" customHeight="1">
+    <row r="25" spans="1:31" s="215" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="214" t="s">
         <v>177</v>
       </c>
@@ -11059,7 +11062,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="1:31" s="215" customFormat="1" ht="54" customHeight="1">
+    <row r="26" spans="1:31" s="215" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="214" t="s">
         <v>179</v>
       </c>
@@ -11160,7 +11163,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:31" s="215" customFormat="1" ht="54" customHeight="1">
+    <row r="27" spans="1:31" s="215" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="214" t="s">
         <v>184</v>
       </c>
@@ -11261,7 +11264,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="28" spans="1:31" s="215" customFormat="1" ht="54" customHeight="1">
+    <row r="28" spans="1:31" s="215" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="214" t="s">
         <v>186</v>
       </c>
@@ -11362,7 +11365,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="1:31" s="215" customFormat="1" ht="54" customHeight="1">
+    <row r="29" spans="1:31" s="215" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="214" t="s">
         <v>185</v>
       </c>
@@ -11463,7 +11466,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="30" spans="1:31" s="215" customFormat="1" ht="54" customHeight="1">
+    <row r="30" spans="1:31" s="215" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="214" t="s">
         <v>191</v>
       </c>
@@ -11564,7 +11567,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="1:31" s="215" customFormat="1" ht="54" customHeight="1">
+    <row r="31" spans="1:31" s="215" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="214" t="s">
         <v>195</v>
       </c>
@@ -11665,7 +11668,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="32" spans="1:31" s="215" customFormat="1" ht="54" customHeight="1">
+    <row r="32" spans="1:31" s="215" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="214" t="s">
         <v>194</v>
       </c>
@@ -11766,7 +11769,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="33" spans="1:31" s="215" customFormat="1" ht="54" customHeight="1">
+    <row r="33" spans="1:31" s="215" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="214" t="s">
         <v>196</v>
       </c>
@@ -11867,7 +11870,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="34" spans="1:31" s="215" customFormat="1" ht="54" customHeight="1">
+    <row r="34" spans="1:31" s="215" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="214" t="s">
         <v>197</v>
       </c>
@@ -11968,7 +11971,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="35" spans="1:31" s="215" customFormat="1" ht="54" customHeight="1">
+    <row r="35" spans="1:31" s="215" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="214" t="s">
         <v>205</v>
       </c>
@@ -12069,7 +12072,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="36" spans="1:31" s="215" customFormat="1" ht="54" customHeight="1">
+    <row r="36" spans="1:31" s="215" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="214" t="s">
         <v>212</v>
       </c>
@@ -12170,7 +12173,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="37" spans="1:31" s="215" customFormat="1" ht="54" customHeight="1">
+    <row r="37" spans="1:31" s="215" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="214" t="s">
         <v>214</v>
       </c>
@@ -12271,7 +12274,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="38" spans="1:31" s="215" customFormat="1" ht="54" customHeight="1">
+    <row r="38" spans="1:31" s="215" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="214" t="s">
         <v>219</v>
       </c>
@@ -12372,7 +12375,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="39" spans="1:31" s="215" customFormat="1" ht="54" customHeight="1">
+    <row r="39" spans="1:31" s="215" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="214" t="s">
         <v>218</v>
       </c>
@@ -12473,7 +12476,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="40" spans="1:31" s="215" customFormat="1" ht="54" customHeight="1">
+    <row r="40" spans="1:31" s="215" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="214" t="s">
         <v>216</v>
       </c>
@@ -12574,7 +12577,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="41" spans="1:31" s="215" customFormat="1" ht="54" customHeight="1">
+    <row r="41" spans="1:31" s="215" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="214" t="s">
         <v>228</v>
       </c>
@@ -12675,7 +12678,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="42" spans="1:31" s="215" customFormat="1" ht="54" customHeight="1">
+    <row r="42" spans="1:31" s="215" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="214" t="s">
         <v>237</v>
       </c>
@@ -12776,7 +12779,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="43" spans="1:31" ht="56.25" customHeight="1">
+    <row r="43" spans="1:31" ht="56.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="260" t="s">
         <v>5</v>
       </c>
@@ -12901,7 +12904,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="44" spans="1:31" ht="69" customHeight="1">
+    <row r="44" spans="1:31" ht="69" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="262" t="s">
         <v>39</v>
       </c>
@@ -13026,7 +13029,7 @@
         <v>14.125</v>
       </c>
     </row>
-    <row r="45" spans="1:31" ht="48.75" customHeight="1">
+    <row r="45" spans="1:31" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="185" t="s">
         <v>54</v>
       </c>
@@ -13088,7 +13091,7 @@
       <c r="AD45" s="26"/>
       <c r="AE45" s="26"/>
     </row>
-    <row r="46" spans="1:31" ht="42.75" customHeight="1">
+    <row r="46" spans="1:31" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="185" t="s">
         <v>55</v>
       </c>
@@ -13143,7 +13146,7 @@
       <c r="AD46" s="34"/>
       <c r="AE46" s="34"/>
     </row>
-    <row r="47" spans="1:31" ht="56.25" customHeight="1">
+    <row r="47" spans="1:31" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="186" t="s">
         <v>53</v>
       </c>
@@ -13235,7 +13238,7 @@
       <c r="AD47" s="187"/>
       <c r="AE47" s="188"/>
     </row>
-    <row r="48" spans="1:31" ht="23.25">
+    <row r="48" spans="1:31" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A48" s="189" t="s">
         <v>159</v>
       </c>
@@ -13275,7 +13278,7 @@
       <c r="AD48" s="195"/>
       <c r="AE48" s="195"/>
     </row>
-    <row r="49" spans="1:31" ht="23.25">
+    <row r="49" spans="1:31" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A49" s="189" t="s">
         <v>198</v>
       </c>
@@ -13316,7 +13319,7 @@
       <c r="AD49" s="195"/>
       <c r="AE49" s="195"/>
     </row>
-    <row r="50" spans="1:31" ht="23.25">
+    <row r="50" spans="1:31" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A50" s="189"/>
       <c r="B50" s="190"/>
       <c r="C50" s="190"/>
@@ -13349,112 +13352,112 @@
       <c r="AD50" s="195"/>
       <c r="AE50" s="195"/>
     </row>
-    <row r="51" spans="1:31" ht="35.25" customHeight="1">
-      <c r="A51" s="494" t="s">
+    <row r="51" spans="1:31" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="533" t="s">
         <v>87</v>
       </c>
-      <c r="B51" s="495"/>
-      <c r="C51" s="495"/>
-      <c r="D51" s="495"/>
-      <c r="E51" s="495"/>
-      <c r="F51" s="495"/>
-      <c r="G51" s="496"/>
-      <c r="H51" s="497" t="s">
+      <c r="B51" s="534"/>
+      <c r="C51" s="534"/>
+      <c r="D51" s="534"/>
+      <c r="E51" s="534"/>
+      <c r="F51" s="534"/>
+      <c r="G51" s="535"/>
+      <c r="H51" s="536" t="s">
         <v>241</v>
       </c>
-      <c r="I51" s="497"/>
-      <c r="J51" s="518" t="s">
+      <c r="I51" s="536"/>
+      <c r="J51" s="562" t="s">
         <v>242</v>
       </c>
-      <c r="K51" s="463" t="s">
+      <c r="K51" s="576" t="s">
         <v>204</v>
       </c>
       <c r="L51" s="196"/>
       <c r="M51" s="196"/>
-      <c r="N51" s="498" t="s">
+      <c r="N51" s="537" t="s">
         <v>240</v>
       </c>
-      <c r="O51" s="498"/>
-      <c r="P51" s="498"/>
-      <c r="Q51" s="498"/>
-      <c r="R51" s="498"/>
-      <c r="S51" s="498"/>
-      <c r="T51" s="498"/>
-      <c r="U51" s="498"/>
-      <c r="V51" s="498"/>
-      <c r="W51" s="498"/>
-      <c r="X51" s="498"/>
-      <c r="Y51" s="498"/>
-      <c r="Z51" s="498"/>
-      <c r="AA51" s="498"/>
+      <c r="O51" s="537"/>
+      <c r="P51" s="537"/>
+      <c r="Q51" s="537"/>
+      <c r="R51" s="537"/>
+      <c r="S51" s="537"/>
+      <c r="T51" s="537"/>
+      <c r="U51" s="537"/>
+      <c r="V51" s="537"/>
+      <c r="W51" s="537"/>
+      <c r="X51" s="537"/>
+      <c r="Y51" s="537"/>
+      <c r="Z51" s="537"/>
+      <c r="AA51" s="537"/>
       <c r="AB51" s="105"/>
       <c r="AC51" s="105"/>
       <c r="AD51" s="105"/>
       <c r="AE51" s="197"/>
     </row>
-    <row r="52" spans="1:31" ht="53.25" customHeight="1">
-      <c r="A52" s="494"/>
-      <c r="B52" s="496"/>
-      <c r="C52" s="499" t="s">
+    <row r="52" spans="1:31" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="533"/>
+      <c r="B52" s="535"/>
+      <c r="C52" s="538" t="s">
         <v>85</v>
       </c>
-      <c r="D52" s="500"/>
-      <c r="E52" s="499" t="s">
+      <c r="D52" s="539"/>
+      <c r="E52" s="538" t="s">
         <v>86</v>
       </c>
-      <c r="F52" s="500"/>
+      <c r="F52" s="539"/>
       <c r="G52" s="320" t="s">
         <v>227</v>
       </c>
-      <c r="H52" s="497"/>
-      <c r="I52" s="497"/>
-      <c r="J52" s="519"/>
-      <c r="K52" s="464"/>
+      <c r="H52" s="536"/>
+      <c r="I52" s="536"/>
+      <c r="J52" s="563"/>
+      <c r="K52" s="577"/>
       <c r="L52" s="196"/>
       <c r="M52" s="196"/>
-      <c r="N52" s="501" t="s">
+      <c r="N52" s="540" t="s">
         <v>52</v>
       </c>
-      <c r="O52" s="502"/>
-      <c r="P52" s="503"/>
-      <c r="Q52" s="510" t="s">
+      <c r="O52" s="541"/>
+      <c r="P52" s="542"/>
+      <c r="Q52" s="549" t="s">
         <v>51</v>
       </c>
-      <c r="R52" s="511"/>
-      <c r="S52" s="511"/>
-      <c r="T52" s="511"/>
-      <c r="U52" s="511"/>
-      <c r="V52" s="511"/>
-      <c r="W52" s="511"/>
-      <c r="X52" s="511"/>
-      <c r="Y52" s="511"/>
-      <c r="Z52" s="511"/>
-      <c r="AA52" s="512"/>
+      <c r="R52" s="550"/>
+      <c r="S52" s="550"/>
+      <c r="T52" s="550"/>
+      <c r="U52" s="550"/>
+      <c r="V52" s="550"/>
+      <c r="W52" s="550"/>
+      <c r="X52" s="550"/>
+      <c r="Y52" s="550"/>
+      <c r="Z52" s="550"/>
+      <c r="AA52" s="551"/>
       <c r="AB52" s="105"/>
       <c r="AC52" s="105"/>
       <c r="AD52" s="105"/>
       <c r="AE52" s="197"/>
     </row>
-    <row r="53" spans="1:31" ht="51" customHeight="1">
-      <c r="A53" s="513" t="s">
+    <row r="53" spans="1:31" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="552" t="s">
         <v>152</v>
       </c>
-      <c r="B53" s="514"/>
-      <c r="C53" s="488">
+      <c r="B53" s="553"/>
+      <c r="C53" s="554">
         <v>26</v>
       </c>
-      <c r="D53" s="489"/>
-      <c r="E53" s="488">
+      <c r="D53" s="555"/>
+      <c r="E53" s="554">
         <v>5</v>
       </c>
-      <c r="F53" s="489"/>
+      <c r="F53" s="555"/>
       <c r="G53" s="199">
         <v>1</v>
       </c>
-      <c r="H53" s="490">
+      <c r="H53" s="564">
         <v>26</v>
       </c>
-      <c r="I53" s="490"/>
+      <c r="I53" s="564"/>
       <c r="J53" s="327">
         <v>8</v>
       </c>
@@ -13463,38 +13466,38 @@
       </c>
       <c r="L53" s="196"/>
       <c r="M53" s="196"/>
-      <c r="N53" s="504"/>
-      <c r="O53" s="505"/>
-      <c r="P53" s="506"/>
-      <c r="Q53" s="491" t="s">
+      <c r="N53" s="543"/>
+      <c r="O53" s="544"/>
+      <c r="P53" s="545"/>
+      <c r="Q53" s="557" t="s">
         <v>40</v>
       </c>
-      <c r="R53" s="492"/>
-      <c r="S53" s="492"/>
-      <c r="T53" s="492"/>
-      <c r="U53" s="493"/>
-      <c r="V53" s="491" t="s">
+      <c r="R53" s="558"/>
+      <c r="S53" s="558"/>
+      <c r="T53" s="558"/>
+      <c r="U53" s="559"/>
+      <c r="V53" s="557" t="s">
         <v>41</v>
       </c>
-      <c r="W53" s="493"/>
-      <c r="X53" s="491" t="s">
+      <c r="W53" s="559"/>
+      <c r="X53" s="557" t="s">
         <v>37</v>
       </c>
-      <c r="Y53" s="492"/>
-      <c r="Z53" s="492"/>
-      <c r="AA53" s="493"/>
+      <c r="Y53" s="558"/>
+      <c r="Z53" s="558"/>
+      <c r="AA53" s="559"/>
       <c r="AB53" s="105"/>
       <c r="AC53" s="105"/>
       <c r="AD53" s="105"/>
       <c r="AE53" s="197"/>
     </row>
-    <row r="54" spans="1:31" ht="23.25">
-      <c r="A54" s="515"/>
-      <c r="B54" s="515"/>
-      <c r="C54" s="515"/>
-      <c r="D54" s="515"/>
-      <c r="E54" s="515"/>
-      <c r="F54" s="515"/>
+    <row r="54" spans="1:31" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A54" s="556"/>
+      <c r="B54" s="556"/>
+      <c r="C54" s="556"/>
+      <c r="D54" s="556"/>
+      <c r="E54" s="556"/>
+      <c r="F54" s="556"/>
       <c r="G54" s="200"/>
       <c r="H54" s="196"/>
       <c r="I54" s="196"/>
@@ -13502,15 +13505,15 @@
       <c r="K54" s="196"/>
       <c r="L54" s="196"/>
       <c r="M54" s="196"/>
-      <c r="N54" s="507"/>
-      <c r="O54" s="508"/>
-      <c r="P54" s="509"/>
-      <c r="Q54" s="491" t="s">
+      <c r="N54" s="546"/>
+      <c r="O54" s="547"/>
+      <c r="P54" s="548"/>
+      <c r="Q54" s="557" t="s">
         <v>42</v>
       </c>
-      <c r="R54" s="492"/>
-      <c r="S54" s="492"/>
-      <c r="T54" s="493"/>
+      <c r="R54" s="558"/>
+      <c r="S54" s="558"/>
+      <c r="T54" s="559"/>
       <c r="U54" s="184" t="s">
         <v>43</v>
       </c>
@@ -13520,10 +13523,10 @@
       <c r="W54" s="201" t="s">
         <v>43</v>
       </c>
-      <c r="X54" s="516" t="s">
+      <c r="X54" s="560" t="s">
         <v>42</v>
       </c>
-      <c r="Y54" s="517"/>
+      <c r="Y54" s="561"/>
       <c r="Z54" s="202"/>
       <c r="AA54" s="201" t="s">
         <v>43</v>
@@ -13533,33 +13536,33 @@
       <c r="AD54" s="105"/>
       <c r="AE54" s="197"/>
     </row>
-    <row r="55" spans="1:31" ht="23.25">
-      <c r="A55" s="481"/>
-      <c r="B55" s="481"/>
-      <c r="C55" s="482"/>
-      <c r="D55" s="482"/>
-      <c r="E55" s="482"/>
+    <row r="55" spans="1:31" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A55" s="589"/>
+      <c r="B55" s="589"/>
+      <c r="C55" s="565"/>
+      <c r="D55" s="565"/>
+      <c r="E55" s="565"/>
       <c r="F55" s="203"/>
       <c r="G55" s="204"/>
-      <c r="H55" s="473" t="s">
+      <c r="H55" s="566" t="s">
         <v>44</v>
       </c>
-      <c r="I55" s="474"/>
-      <c r="J55" s="474"/>
-      <c r="K55" s="474"/>
-      <c r="L55" s="474"/>
-      <c r="M55" s="475"/>
-      <c r="N55" s="483">
+      <c r="I55" s="567"/>
+      <c r="J55" s="567"/>
+      <c r="K55" s="567"/>
+      <c r="L55" s="567"/>
+      <c r="M55" s="568"/>
+      <c r="N55" s="569">
         <v>8.6</v>
       </c>
-      <c r="O55" s="484"/>
-      <c r="P55" s="485"/>
-      <c r="Q55" s="486">
+      <c r="O55" s="570"/>
+      <c r="P55" s="571"/>
+      <c r="Q55" s="572">
         <v>10</v>
       </c>
-      <c r="R55" s="487"/>
-      <c r="S55" s="487"/>
-      <c r="T55" s="487"/>
+      <c r="R55" s="573"/>
+      <c r="S55" s="573"/>
+      <c r="T55" s="573"/>
       <c r="U55" s="205">
         <v>4.5</v>
       </c>
@@ -13569,11 +13572,11 @@
       <c r="W55" s="207">
         <v>8.75</v>
       </c>
-      <c r="X55" s="467">
+      <c r="X55" s="574">
         <f>Q55+V55</f>
         <v>26</v>
       </c>
-      <c r="Y55" s="468"/>
+      <c r="Y55" s="575"/>
       <c r="Z55" s="208"/>
       <c r="AA55" s="207">
         <f>U55+W55</f>
@@ -13584,33 +13587,33 @@
       <c r="AD55" s="105"/>
       <c r="AE55" s="197"/>
     </row>
-    <row r="56" spans="1:31" ht="23.25">
-      <c r="A56" s="471"/>
-      <c r="B56" s="471"/>
-      <c r="C56" s="472"/>
-      <c r="D56" s="472"/>
-      <c r="E56" s="472"/>
-      <c r="F56" s="472"/>
+    <row r="56" spans="1:31" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A56" s="582"/>
+      <c r="B56" s="582"/>
+      <c r="C56" s="583"/>
+      <c r="D56" s="583"/>
+      <c r="E56" s="583"/>
+      <c r="F56" s="583"/>
       <c r="G56" s="204"/>
-      <c r="H56" s="473" t="s">
+      <c r="H56" s="566" t="s">
         <v>45</v>
       </c>
-      <c r="I56" s="474"/>
-      <c r="J56" s="474"/>
-      <c r="K56" s="474"/>
-      <c r="L56" s="474"/>
-      <c r="M56" s="475"/>
-      <c r="N56" s="476">
+      <c r="I56" s="567"/>
+      <c r="J56" s="567"/>
+      <c r="K56" s="567"/>
+      <c r="L56" s="567"/>
+      <c r="M56" s="568"/>
+      <c r="N56" s="584">
         <v>2.99</v>
       </c>
-      <c r="O56" s="477"/>
-      <c r="P56" s="478"/>
-      <c r="Q56" s="479">
-        <v>0</v>
-      </c>
-      <c r="R56" s="480"/>
-      <c r="S56" s="480"/>
-      <c r="T56" s="480"/>
+      <c r="O56" s="585"/>
+      <c r="P56" s="586"/>
+      <c r="Q56" s="587">
+        <v>0</v>
+      </c>
+      <c r="R56" s="588"/>
+      <c r="S56" s="588"/>
+      <c r="T56" s="588"/>
       <c r="U56" s="209">
         <v>0</v>
       </c>
@@ -13620,11 +13623,11 @@
       <c r="W56" s="207">
         <v>0.7</v>
       </c>
-      <c r="X56" s="467">
+      <c r="X56" s="574">
         <f>Q56+V56</f>
         <v>3</v>
       </c>
-      <c r="Y56" s="468"/>
+      <c r="Y56" s="575"/>
       <c r="Z56" s="208"/>
       <c r="AA56" s="207">
         <f>U56+W56</f>
@@ -13635,13 +13638,13 @@
       <c r="AD56" s="105"/>
       <c r="AE56" s="197"/>
     </row>
-    <row r="57" spans="1:31" ht="20.25">
-      <c r="A57" s="469"/>
-      <c r="B57" s="469"/>
-      <c r="C57" s="470"/>
-      <c r="D57" s="470"/>
-      <c r="E57" s="470"/>
-      <c r="F57" s="470"/>
+    <row r="57" spans="1:31" ht="20.25" x14ac:dyDescent="0.15">
+      <c r="A57" s="580"/>
+      <c r="B57" s="580"/>
+      <c r="C57" s="581"/>
+      <c r="D57" s="581"/>
+      <c r="E57" s="581"/>
+      <c r="F57" s="581"/>
       <c r="G57" s="173"/>
       <c r="H57" s="172"/>
       <c r="I57" s="172"/>
@@ -13660,34 +13663,34 @@
       <c r="AC57" s="35"/>
       <c r="AE57" s="24"/>
     </row>
-    <row r="58" spans="1:31" ht="20.25">
+    <row r="58" spans="1:31" ht="20.25" x14ac:dyDescent="0.15">
       <c r="B58" s="174"/>
       <c r="AE58" s="24"/>
     </row>
-    <row r="59" spans="1:31" ht="26.25">
-      <c r="A59" s="465" t="s">
+    <row r="59" spans="1:31" ht="25.5" x14ac:dyDescent="0.3">
+      <c r="A59" s="578" t="s">
         <v>153</v>
       </c>
-      <c r="B59" s="465"/>
-      <c r="C59" s="465"/>
-      <c r="D59" s="465"/>
-      <c r="E59" s="465"/>
-      <c r="F59" s="465"/>
-      <c r="G59" s="465"/>
-      <c r="H59" s="465"/>
-      <c r="I59" s="465"/>
-      <c r="J59" s="465"/>
-      <c r="K59" s="465"/>
-      <c r="L59" s="465"/>
-      <c r="M59" s="465"/>
-      <c r="N59" s="466" t="str">
+      <c r="B59" s="578"/>
+      <c r="C59" s="578"/>
+      <c r="D59" s="578"/>
+      <c r="E59" s="578"/>
+      <c r="F59" s="578"/>
+      <c r="G59" s="578"/>
+      <c r="H59" s="578"/>
+      <c r="I59" s="578"/>
+      <c r="J59" s="578"/>
+      <c r="K59" s="578"/>
+      <c r="L59" s="578"/>
+      <c r="M59" s="578"/>
+      <c r="N59" s="579" t="str">
         <f>AB1</f>
         <v>24.09.2026</v>
       </c>
-      <c r="O59" s="466"/>
-      <c r="P59" s="466"/>
-      <c r="Q59" s="466"/>
-      <c r="R59" s="466"/>
+      <c r="O59" s="579"/>
+      <c r="P59" s="579"/>
+      <c r="Q59" s="579"/>
+      <c r="R59" s="579"/>
       <c r="S59" s="183"/>
       <c r="T59" s="183"/>
       <c r="U59" s="36"/>
@@ -13700,33 +13703,33 @@
       </c>
       <c r="AE59" s="24"/>
     </row>
-    <row r="60" spans="1:31">
+    <row r="60" spans="1:31" x14ac:dyDescent="0.15">
       <c r="AE60" s="24"/>
     </row>
-    <row r="61" spans="1:31" ht="26.25">
-      <c r="A61" s="465" t="s">
+    <row r="61" spans="1:31" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A61" s="578" t="s">
         <v>154</v>
       </c>
-      <c r="B61" s="465"/>
-      <c r="C61" s="465"/>
-      <c r="D61" s="465"/>
-      <c r="E61" s="465"/>
-      <c r="F61" s="465"/>
-      <c r="G61" s="465"/>
-      <c r="H61" s="465"/>
-      <c r="I61" s="465"/>
-      <c r="J61" s="465"/>
-      <c r="K61" s="465"/>
-      <c r="L61" s="465"/>
-      <c r="M61" s="465"/>
-      <c r="N61" s="466" t="str">
+      <c r="B61" s="578"/>
+      <c r="C61" s="578"/>
+      <c r="D61" s="578"/>
+      <c r="E61" s="578"/>
+      <c r="F61" s="578"/>
+      <c r="G61" s="578"/>
+      <c r="H61" s="578"/>
+      <c r="I61" s="578"/>
+      <c r="J61" s="578"/>
+      <c r="K61" s="578"/>
+      <c r="L61" s="578"/>
+      <c r="M61" s="578"/>
+      <c r="N61" s="579" t="str">
         <f>AB1</f>
         <v>24.09.2026</v>
       </c>
-      <c r="O61" s="466"/>
-      <c r="P61" s="466"/>
-      <c r="Q61" s="466"/>
-      <c r="R61" s="466"/>
+      <c r="O61" s="579"/>
+      <c r="P61" s="579"/>
+      <c r="Q61" s="579"/>
+      <c r="R61" s="579"/>
       <c r="S61" s="175"/>
       <c r="T61" s="175"/>
       <c r="U61" s="36"/>
@@ -13736,39 +13739,116 @@
       </c>
       <c r="AE61" s="24"/>
     </row>
-    <row r="62" spans="1:31">
+    <row r="62" spans="1:31" x14ac:dyDescent="0.15">
       <c r="U62" s="41"/>
       <c r="AE62" s="24"/>
     </row>
-    <row r="63" spans="1:31">
+    <row r="63" spans="1:31" x14ac:dyDescent="0.15">
       <c r="AE63" s="24"/>
     </row>
-    <row r="64" spans="1:31">
+    <row r="64" spans="1:31" x14ac:dyDescent="0.15">
       <c r="AE64" s="24"/>
     </row>
-    <row r="65" spans="11:31">
+    <row r="65" spans="11:31" x14ac:dyDescent="0.15">
       <c r="AE65" s="24"/>
     </row>
-    <row r="66" spans="11:31">
+    <row r="66" spans="11:31" x14ac:dyDescent="0.15">
       <c r="AE66" s="24"/>
     </row>
-    <row r="67" spans="11:31">
+    <row r="67" spans="11:31" x14ac:dyDescent="0.15">
       <c r="AE67" s="24"/>
     </row>
-    <row r="70" spans="11:31">
+    <row r="70" spans="11:31" x14ac:dyDescent="0.15">
       <c r="K70" s="269"/>
       <c r="L70" s="269"/>
     </row>
-    <row r="71" spans="11:31">
+    <row r="71" spans="11:31" x14ac:dyDescent="0.15">
       <c r="K71" s="269"/>
       <c r="L71" s="269"/>
     </row>
-    <row r="72" spans="11:31">
+    <row r="72" spans="11:31" x14ac:dyDescent="0.15">
       <c r="K72" s="269"/>
       <c r="L72" s="269"/>
     </row>
   </sheetData>
   <mergeCells count="93">
+    <mergeCell ref="K51:K52"/>
+    <mergeCell ref="A61:M61"/>
+    <mergeCell ref="N61:R61"/>
+    <mergeCell ref="X56:Y56"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="C57:D57"/>
+    <mergeCell ref="E57:F57"/>
+    <mergeCell ref="A59:M59"/>
+    <mergeCell ref="N59:R59"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="C56:D56"/>
+    <mergeCell ref="E56:F56"/>
+    <mergeCell ref="H56:M56"/>
+    <mergeCell ref="N56:P56"/>
+    <mergeCell ref="Q56:T56"/>
+    <mergeCell ref="A55:B55"/>
+    <mergeCell ref="C55:E55"/>
+    <mergeCell ref="H55:M55"/>
+    <mergeCell ref="N55:P55"/>
+    <mergeCell ref="Q55:T55"/>
+    <mergeCell ref="X55:Y55"/>
+    <mergeCell ref="E53:F53"/>
+    <mergeCell ref="H53:I53"/>
+    <mergeCell ref="Q53:U53"/>
+    <mergeCell ref="V53:W53"/>
+    <mergeCell ref="X53:AA53"/>
+    <mergeCell ref="A51:G51"/>
+    <mergeCell ref="H51:I52"/>
+    <mergeCell ref="N51:AA51"/>
+    <mergeCell ref="A52:B52"/>
+    <mergeCell ref="C52:D52"/>
+    <mergeCell ref="E52:F52"/>
+    <mergeCell ref="N52:P54"/>
+    <mergeCell ref="Q52:AA52"/>
+    <mergeCell ref="A53:B53"/>
+    <mergeCell ref="C53:D53"/>
+    <mergeCell ref="A54:B54"/>
+    <mergeCell ref="C54:D54"/>
+    <mergeCell ref="E54:F54"/>
+    <mergeCell ref="Q54:T54"/>
+    <mergeCell ref="X54:Y54"/>
+    <mergeCell ref="J51:J52"/>
+    <mergeCell ref="AB16:AB18"/>
+    <mergeCell ref="AC16:AC18"/>
+    <mergeCell ref="AD16:AD18"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="I17:K17"/>
+    <mergeCell ref="M17:M18"/>
+    <mergeCell ref="N17:Q17"/>
+    <mergeCell ref="X16:Z17"/>
+    <mergeCell ref="A13:AE13"/>
+    <mergeCell ref="A14:A18"/>
+    <mergeCell ref="B14:W14"/>
+    <mergeCell ref="X14:AD14"/>
+    <mergeCell ref="AE14:AE18"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="E15:R15"/>
+    <mergeCell ref="U15:W17"/>
+    <mergeCell ref="X15:AA15"/>
+    <mergeCell ref="AB15:AD15"/>
+    <mergeCell ref="B16:B18"/>
+    <mergeCell ref="C16:C18"/>
+    <mergeCell ref="D16:D18"/>
+    <mergeCell ref="E16:M16"/>
+    <mergeCell ref="N16:R16"/>
+    <mergeCell ref="AA16:AA18"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="M5:M6"/>
+    <mergeCell ref="N5:Q5"/>
+    <mergeCell ref="X4:Z5"/>
+    <mergeCell ref="AA4:AA6"/>
+    <mergeCell ref="AB4:AB6"/>
+    <mergeCell ref="AC4:AC6"/>
+    <mergeCell ref="AD4:AD6"/>
     <mergeCell ref="B1:X1"/>
     <mergeCell ref="AB1:AE1"/>
     <mergeCell ref="A2:A6"/>
@@ -13785,83 +13865,6 @@
     <mergeCell ref="D4:D6"/>
     <mergeCell ref="E4:M4"/>
     <mergeCell ref="N4:R4"/>
-    <mergeCell ref="X4:Z5"/>
-    <mergeCell ref="AA4:AA6"/>
-    <mergeCell ref="AB4:AB6"/>
-    <mergeCell ref="AC4:AC6"/>
-    <mergeCell ref="AD4:AD6"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="I5:K5"/>
-    <mergeCell ref="M5:M6"/>
-    <mergeCell ref="N5:Q5"/>
-    <mergeCell ref="A13:AE13"/>
-    <mergeCell ref="A14:A18"/>
-    <mergeCell ref="B14:W14"/>
-    <mergeCell ref="X14:AD14"/>
-    <mergeCell ref="AE14:AE18"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="E15:R15"/>
-    <mergeCell ref="U15:W17"/>
-    <mergeCell ref="X15:AA15"/>
-    <mergeCell ref="AB15:AD15"/>
-    <mergeCell ref="B16:B18"/>
-    <mergeCell ref="C16:C18"/>
-    <mergeCell ref="D16:D18"/>
-    <mergeCell ref="E16:M16"/>
-    <mergeCell ref="N16:R16"/>
-    <mergeCell ref="AA16:AA18"/>
-    <mergeCell ref="AB16:AB18"/>
-    <mergeCell ref="AC16:AC18"/>
-    <mergeCell ref="AD16:AD18"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="I17:K17"/>
-    <mergeCell ref="M17:M18"/>
-    <mergeCell ref="N17:Q17"/>
-    <mergeCell ref="X16:Z17"/>
-    <mergeCell ref="A51:G51"/>
-    <mergeCell ref="H51:I52"/>
-    <mergeCell ref="N51:AA51"/>
-    <mergeCell ref="A52:B52"/>
-    <mergeCell ref="C52:D52"/>
-    <mergeCell ref="E52:F52"/>
-    <mergeCell ref="N52:P54"/>
-    <mergeCell ref="Q52:AA52"/>
-    <mergeCell ref="A53:B53"/>
-    <mergeCell ref="C53:D53"/>
-    <mergeCell ref="A54:B54"/>
-    <mergeCell ref="C54:D54"/>
-    <mergeCell ref="E54:F54"/>
-    <mergeCell ref="Q54:T54"/>
-    <mergeCell ref="X54:Y54"/>
-    <mergeCell ref="J51:J52"/>
-    <mergeCell ref="E53:F53"/>
-    <mergeCell ref="H53:I53"/>
-    <mergeCell ref="Q53:U53"/>
-    <mergeCell ref="V53:W53"/>
-    <mergeCell ref="X53:AA53"/>
-    <mergeCell ref="C55:E55"/>
-    <mergeCell ref="H55:M55"/>
-    <mergeCell ref="N55:P55"/>
-    <mergeCell ref="Q55:T55"/>
-    <mergeCell ref="X55:Y55"/>
-    <mergeCell ref="K51:K52"/>
-    <mergeCell ref="A61:M61"/>
-    <mergeCell ref="N61:R61"/>
-    <mergeCell ref="X56:Y56"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="C57:D57"/>
-    <mergeCell ref="E57:F57"/>
-    <mergeCell ref="A59:M59"/>
-    <mergeCell ref="N59:R59"/>
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="C56:D56"/>
-    <mergeCell ref="E56:F56"/>
-    <mergeCell ref="H56:M56"/>
-    <mergeCell ref="N56:P56"/>
-    <mergeCell ref="Q56:T56"/>
-    <mergeCell ref="A55:B55"/>
   </mergeCells>
   <pageMargins left="0.38" right="0.27" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="25" orientation="portrait" verticalDpi="0" r:id="rId1"/>
